--- a/upload/contratos.xlsx
+++ b/upload/contratos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AC$596</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AC$601</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC596"/>
+  <dimension ref="A1:AC601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1922,11 +1922,11 @@
         <v>44778</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>46117</v>
+        <v>46099</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Paralisado</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1986,10 +1986,10 @@
         <v>420</v>
       </c>
       <c r="T13" t="n">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="U13" t="n">
-        <v>1340</v>
+        <v>1322</v>
       </c>
       <c r="V13" t="n">
         <v>1257285.84</v>
@@ -2273,7 +2273,7 @@
         <v>44524</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46145</v>
+        <v>46154</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1262</v>
+        <v>1271</v>
       </c>
       <c r="U16" t="n">
-        <v>1622</v>
+        <v>1631</v>
       </c>
       <c r="V16" t="n">
         <v>1452371.99</v>
@@ -7383,19 +7383,19 @@
         <v>65069077.71</v>
       </c>
       <c r="Y59" t="n">
-        <v>58929090.2</v>
+        <v>59045135.03</v>
       </c>
       <c r="Z59" t="n">
-        <v>53825381.58</v>
+        <v>53965887.89</v>
       </c>
       <c r="AA59" t="n">
-        <v>112754471.78</v>
+        <v>113011022.92</v>
       </c>
       <c r="AB59" t="n">
-        <v>6139987.51</v>
+        <v>6023942.68</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.9056389344049918</v>
+        <v>0.9074223441916985</v>
       </c>
     </row>
     <row r="60">
@@ -12200,7 +12200,7 @@
         <v>44850</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>46103</v>
+        <v>46112</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -12264,10 +12264,10 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="U101" t="n">
-        <v>1254</v>
+        <v>1263</v>
       </c>
       <c r="V101" t="n">
         <v>1365885.84</v>
@@ -15906,19 +15906,19 @@
         <v>24865514.03</v>
       </c>
       <c r="Y132" t="n">
-        <v>19326094.83</v>
+        <v>19863600.32</v>
       </c>
       <c r="Z132" t="n">
-        <v>1904605.97</v>
+        <v>1987435.56</v>
       </c>
       <c r="AA132" t="n">
-        <v>21230700.8</v>
+        <v>21851035.88</v>
       </c>
       <c r="AB132" t="n">
-        <v>5539419.2</v>
+        <v>5001913.71</v>
       </c>
       <c r="AC132" t="n">
-        <v>0.7772248265884732</v>
+        <v>0.7988413308502194</v>
       </c>
     </row>
     <row r="133">
@@ -20156,7 +20156,7 @@
         <v>45103</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>46201</v>
+        <v>46210</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -20220,10 +20220,10 @@
         <v>240</v>
       </c>
       <c r="T169" t="n">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="U169" t="n">
-        <v>1099</v>
+        <v>1108</v>
       </c>
       <c r="V169" t="n">
         <v>20645773.23</v>
@@ -24017,7 +24017,7 @@
         <v>44767</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>46201</v>
+        <v>46210</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -24081,10 +24081,10 @@
         <v>0</v>
       </c>
       <c r="T202" t="n">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="U202" t="n">
-        <v>1435</v>
+        <v>1444</v>
       </c>
       <c r="V202" t="n">
         <v>2519553.4</v>
@@ -26819,7 +26819,7 @@
         <v>44810</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>46122</v>
+        <v>46131</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -26883,10 +26883,10 @@
         <v>0</v>
       </c>
       <c r="T226" t="n">
-        <v>1132</v>
+        <v>1141</v>
       </c>
       <c r="U226" t="n">
-        <v>1313</v>
+        <v>1322</v>
       </c>
       <c r="V226" t="n">
         <v>1559477.28</v>
@@ -28457,7 +28457,7 @@
         <v>44579</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>46318</v>
+        <v>46327</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -28521,10 +28521,10 @@
         <v>180</v>
       </c>
       <c r="T240" t="n">
-        <v>1200</v>
+        <v>1209</v>
       </c>
       <c r="U240" t="n">
-        <v>1740</v>
+        <v>1749</v>
       </c>
       <c r="V240" t="n">
         <v>1175120.88</v>
@@ -33827,11 +33827,11 @@
         <v>45084</v>
       </c>
       <c r="F286" s="3" t="n">
-        <v>46119</v>
+        <v>45994</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Paralisado</t>
+          <t>Encerrado</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -33891,10 +33891,10 @@
         <v>0</v>
       </c>
       <c r="T286" t="n">
-        <v>466</v>
+        <v>341</v>
       </c>
       <c r="U286" t="n">
-        <v>1036</v>
+        <v>911</v>
       </c>
       <c r="V286" t="n">
         <v>2090968.9</v>
@@ -37097,11 +37097,11 @@
         <v>45384</v>
       </c>
       <c r="F314" s="3" t="n">
-        <v>46099</v>
+        <v>46125</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Paralisado</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -37161,10 +37161,10 @@
         <v>330</v>
       </c>
       <c r="T314" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="U314" t="n">
-        <v>716</v>
+        <v>742</v>
       </c>
       <c r="V314" t="n">
         <v>2816620.4</v>
@@ -38580,19 +38580,19 @@
         <v>70591515.05</v>
       </c>
       <c r="Y326" t="n">
-        <v>30909420.18</v>
+        <v>31067942.92</v>
       </c>
       <c r="Z326" t="n">
-        <v>1583394.89</v>
+        <v>1590984.64</v>
       </c>
       <c r="AA326" t="n">
-        <v>32492815.07</v>
+        <v>32658927.56</v>
       </c>
       <c r="AB326" t="n">
-        <v>39682094.87</v>
+        <v>39523572.13</v>
       </c>
       <c r="AC326" t="n">
-        <v>0.4378631080251904</v>
+        <v>0.4401087425024744</v>
       </c>
     </row>
     <row r="327">
@@ -38735,7 +38735,7 @@
         <v>45082</v>
       </c>
       <c r="F328" s="3" t="n">
-        <v>46186</v>
+        <v>46195</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
@@ -38799,10 +38799,10 @@
         <v>0</v>
       </c>
       <c r="T328" t="n">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="U328" t="n">
-        <v>1105</v>
+        <v>1114</v>
       </c>
       <c r="V328" t="n">
         <v>3606475.63</v>
@@ -41973,19 +41973,19 @@
         <v>3270756.85</v>
       </c>
       <c r="Y355" t="n">
-        <v>723506.99</v>
+        <v>725981.9399999999</v>
       </c>
       <c r="Z355" t="n">
-        <v>74787.22</v>
+        <v>75168.59</v>
       </c>
       <c r="AA355" t="n">
-        <v>798294.21</v>
+        <v>801150.53</v>
       </c>
       <c r="AB355" t="n">
-        <v>2547249.86</v>
+        <v>2544774.91</v>
       </c>
       <c r="AC355" t="n">
-        <v>0.2212047618275262</v>
+        <v>0.2219614521330132</v>
       </c>
     </row>
     <row r="356">
@@ -42479,7 +42479,7 @@
         <v>45236</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>46115</v>
+        <v>46124</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -42543,10 +42543,10 @@
         <v>480</v>
       </c>
       <c r="T360" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="U360" t="n">
-        <v>880</v>
+        <v>889</v>
       </c>
       <c r="V360" t="n">
         <v>5042730.21</v>
@@ -43143,19 +43143,19 @@
         <v>6173972.84</v>
       </c>
       <c r="Y365" t="n">
-        <v>2401356.31</v>
+        <v>2560383.73</v>
       </c>
       <c r="Z365" t="n">
-        <v>299509.79</v>
+        <v>324015.91</v>
       </c>
       <c r="AA365" t="n">
-        <v>2700866.1</v>
+        <v>2884399.64</v>
       </c>
       <c r="AB365" t="n">
-        <v>3772616.53</v>
+        <v>3613589.11</v>
       </c>
       <c r="AC365" t="n">
-        <v>0.3889483112789333</v>
+        <v>0.4147060242007802</v>
       </c>
     </row>
     <row r="366">
@@ -43260,25 +43260,25 @@
         <v>4004374.41</v>
       </c>
       <c r="Y366" t="n">
-        <v>170950.14</v>
+        <v>178536.39</v>
       </c>
       <c r="Z366" t="n">
-        <v>26343.39</v>
+        <v>27512.43</v>
       </c>
       <c r="AA366" t="n">
-        <v>197293.53</v>
+        <v>206048.82</v>
       </c>
       <c r="AB366" t="n">
-        <v>3833424.27</v>
+        <v>3825838.02</v>
       </c>
       <c r="AC366" t="n">
-        <v>0.04269084818170137</v>
+        <v>0.04458533886195722</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>DO-001/2021-ANO 2</t>
+          <t>DO-001/2021- B</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -43377,19 +43377,19 @@
         <v>2949000</v>
       </c>
       <c r="Y367" t="n">
-        <v>2496053.43</v>
+        <v>2586657.84</v>
       </c>
       <c r="Z367" t="n">
-        <v>586504.63</v>
+        <v>612009.77</v>
       </c>
       <c r="AA367" t="n">
-        <v>3082558.06</v>
+        <v>3198667.61</v>
       </c>
       <c r="AB367" t="n">
-        <v>452946.57</v>
+        <v>362342.16</v>
       </c>
       <c r="AC367" t="n">
-        <v>0.8464067243133265</v>
+        <v>0.877130498474059</v>
       </c>
     </row>
     <row r="368">
@@ -43728,19 +43728,19 @@
         <v>8240827.41</v>
       </c>
       <c r="Y370" t="n">
-        <v>1497276.52</v>
+        <v>1507542.69</v>
       </c>
       <c r="Z370" t="n">
-        <v>173580.03</v>
+        <v>175162.04</v>
       </c>
       <c r="AA370" t="n">
-        <v>1670856.55</v>
+        <v>1682704.73</v>
       </c>
       <c r="AB370" t="n">
-        <v>6743550.89</v>
+        <v>6733284.72</v>
       </c>
       <c r="AC370" t="n">
-        <v>0.181690071337145</v>
+        <v>0.1829358406621454</v>
       </c>
     </row>
     <row r="371">
@@ -45170,11 +45170,11 @@
         <v>45237</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>46106</v>
+        <v>46117</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Paralisado</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -45234,10 +45234,10 @@
         <v>510</v>
       </c>
       <c r="T383" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U383" t="n">
-        <v>870</v>
+        <v>881</v>
       </c>
       <c r="V383" t="n">
         <v>4065559.6</v>
@@ -45249,19 +45249,19 @@
         <v>4065559.6</v>
       </c>
       <c r="Y383" t="n">
-        <v>1216772.69</v>
+        <v>1266033.65</v>
       </c>
       <c r="Z383" t="n">
-        <v>136090.36</v>
+        <v>143681.45</v>
       </c>
       <c r="AA383" t="n">
-        <v>1352863.05</v>
+        <v>1409715.1</v>
       </c>
       <c r="AB383" t="n">
-        <v>2848786.91</v>
+        <v>2799525.95</v>
       </c>
       <c r="AC383" t="n">
-        <v>0.2992878741711227</v>
+        <v>0.3114045235002827</v>
       </c>
     </row>
     <row r="384">
@@ -48791,11 +48791,11 @@
         <v>45386</v>
       </c>
       <c r="F414" s="3" t="n">
-        <v>46105</v>
+        <v>46116</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Paralisado</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -48855,10 +48855,10 @@
         <v>0</v>
       </c>
       <c r="T414" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U414" t="n">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="V414" t="n">
         <v>65748419.13</v>
@@ -51008,7 +51008,7 @@
         <v>45355</v>
       </c>
       <c r="F433" s="3" t="n">
-        <v>46104</v>
+        <v>46113</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         <v>330</v>
       </c>
       <c r="T433" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="U433" t="n">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="V433" t="n">
         <v>5820891.54</v>
@@ -52023,19 +52023,19 @@
         <v>29715772.52</v>
       </c>
       <c r="Y441" t="n">
-        <v>22736464.34</v>
+        <v>23090287.3</v>
       </c>
       <c r="Z441" t="n">
-        <v>1130138.3</v>
+        <v>1177613.07</v>
       </c>
       <c r="AA441" t="n">
-        <v>23866602.64</v>
+        <v>24267900.37</v>
       </c>
       <c r="AB441" t="n">
-        <v>6979308.18</v>
+        <v>6625485.22</v>
       </c>
       <c r="AC441" t="n">
-        <v>0.7651311883174963</v>
+        <v>0.7770380959963009</v>
       </c>
     </row>
     <row r="442">
@@ -52257,19 +52257,19 @@
         <v>34071020.86</v>
       </c>
       <c r="Y443" t="n">
-        <v>13992302.74</v>
+        <v>14926675.21</v>
       </c>
       <c r="Z443" t="n">
-        <v>2237298.47</v>
+        <v>2396358.14</v>
       </c>
       <c r="AA443" t="n">
-        <v>16229601.21</v>
+        <v>17323033.35</v>
       </c>
       <c r="AB443" t="n">
-        <v>20078718.12</v>
+        <v>19144345.65</v>
       </c>
       <c r="AC443" t="n">
-        <v>0.4106804664731141</v>
+        <v>0.4381047245791272</v>
       </c>
     </row>
     <row r="444">
@@ -52763,11 +52763,11 @@
         <v>45722</v>
       </c>
       <c r="F448" s="3" t="n">
-        <v>46081</v>
+        <v>46120</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Paralisado</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -52827,10 +52827,10 @@
         <v>0</v>
       </c>
       <c r="T448" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="U448" t="n">
-        <v>360</v>
+        <v>399</v>
       </c>
       <c r="V448" t="n">
         <v>1922644.28</v>
@@ -54480,19 +54480,19 @@
         <v>50256753.54</v>
       </c>
       <c r="Y462" t="n">
-        <v>39257997.13</v>
+        <v>40609650.97</v>
       </c>
       <c r="Z462" t="n">
-        <v>1387247.2</v>
+        <v>1467687.93</v>
       </c>
       <c r="AA462" t="n">
-        <v>40645244.33</v>
+        <v>42077338.9</v>
       </c>
       <c r="AB462" t="n">
-        <v>10998756.41</v>
+        <v>9647102.57</v>
       </c>
       <c r="AC462" t="n">
-        <v>0.7811486887777989</v>
+        <v>0.8080436580066449</v>
       </c>
     </row>
     <row r="463">
@@ -55767,19 +55767,19 @@
         <v>47556790.26</v>
       </c>
       <c r="Y473" t="n">
-        <v>30046325.33</v>
+        <v>31001351.31</v>
       </c>
       <c r="Z473" t="n">
-        <v>1241995.65</v>
+        <v>1306191.62</v>
       </c>
       <c r="AA473" t="n">
-        <v>31288320.98</v>
+        <v>32307542.93</v>
       </c>
       <c r="AB473" t="n">
-        <v>17510464.93</v>
+        <v>16555438.95</v>
       </c>
       <c r="AC473" t="n">
-        <v>0.6317988486130435</v>
+        <v>0.6518806492303419</v>
       </c>
     </row>
     <row r="474">
@@ -56150,7 +56150,7 @@
         <v>45573</v>
       </c>
       <c r="F477" s="3" t="n">
-        <v>46174</v>
+        <v>46183</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
@@ -56214,10 +56214,10 @@
         <v>0</v>
       </c>
       <c r="T477" t="n">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="U477" t="n">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="V477" t="n">
         <v>3876550</v>
@@ -57633,19 +57633,19 @@
         <v>61821473.21</v>
       </c>
       <c r="Y489" t="n">
-        <v>45821274.56</v>
+        <v>46257291.3</v>
       </c>
       <c r="Z489" t="n">
-        <v>1373475.56</v>
+        <v>1387864.19</v>
       </c>
       <c r="AA489" t="n">
-        <v>47194750.12</v>
+        <v>47645155.49</v>
       </c>
       <c r="AB489" t="n">
-        <v>16000198.65</v>
+        <v>15564181.91</v>
       </c>
       <c r="AC489" t="n">
-        <v>0.7411870371375772</v>
+        <v>0.7482398735932679</v>
       </c>
     </row>
     <row r="490">
@@ -58256,7 +58256,7 @@
         <v>45653</v>
       </c>
       <c r="F495" s="3" t="n">
-        <v>46109</v>
+        <v>46118</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
@@ -58320,10 +58320,10 @@
         <v>0</v>
       </c>
       <c r="T495" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="U495" t="n">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="V495" t="n">
         <v>21305007.22</v>
@@ -58611,7 +58611,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -58686,19 +58686,19 @@
         <v>42281241.69</v>
       </c>
       <c r="Y498" t="n">
-        <v>38538663.15</v>
+        <v>40491145.19</v>
       </c>
       <c r="Z498" t="n">
-        <v>1634358.53</v>
+        <v>1737807.72</v>
       </c>
       <c r="AA498" t="n">
-        <v>40173021.68</v>
+        <v>42228952.91</v>
       </c>
       <c r="AB498" t="n">
-        <v>3742578.54</v>
+        <v>1790096.5</v>
       </c>
       <c r="AC498" t="n">
-        <v>0.9114837126250915</v>
+        <v>0.9576621587150933</v>
       </c>
     </row>
     <row r="499">
@@ -59154,19 +59154,19 @@
         <v>5774752.44</v>
       </c>
       <c r="Y502" t="n">
-        <v>1576702.74</v>
+        <v>1744569.6</v>
       </c>
       <c r="Z502" t="n">
-        <v>56247.51</v>
+        <v>66890.25999999999</v>
       </c>
       <c r="AA502" t="n">
-        <v>1632950.25</v>
+        <v>1811459.86</v>
       </c>
       <c r="AB502" t="n">
-        <v>4198049.7</v>
+        <v>4030182.84</v>
       </c>
       <c r="AC502" t="n">
-        <v>0.2730338237668246</v>
+        <v>0.3021029244328957</v>
       </c>
     </row>
     <row r="503">
@@ -59739,19 +59739,19 @@
         <v>5947278.86</v>
       </c>
       <c r="Y507" t="n">
-        <v>2993959.86</v>
+        <v>3734042.86</v>
       </c>
       <c r="Z507" t="n">
-        <v>122752.33</v>
+        <v>177666.48</v>
       </c>
       <c r="AA507" t="n">
-        <v>3116712.19</v>
+        <v>3911709.34</v>
       </c>
       <c r="AB507" t="n">
-        <v>2953319</v>
+        <v>2213236</v>
       </c>
       <c r="AC507" t="n">
-        <v>0.5034167609218176</v>
+        <v>0.627857369378506</v>
       </c>
     </row>
     <row r="508">
@@ -59781,7 +59781,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -59856,19 +59856,19 @@
         <v>14460009.16</v>
       </c>
       <c r="Y508" t="n">
-        <v>8747448.59</v>
+        <v>10322430.28</v>
       </c>
       <c r="Z508" t="n">
-        <v>688392</v>
+        <v>876565.33</v>
       </c>
       <c r="AA508" t="n">
-        <v>9435840.59</v>
+        <v>11198995.61</v>
       </c>
       <c r="AB508" t="n">
-        <v>5712560.57</v>
+        <v>4137578.88</v>
       </c>
       <c r="AC508" t="n">
-        <v>0.6049407364275833</v>
+        <v>0.7138605630039587</v>
       </c>
     </row>
     <row r="509">
@@ -60128,7 +60128,7 @@
         <v>45715</v>
       </c>
       <c r="F511" s="3" t="n">
-        <v>46110</v>
+        <v>46263</v>
       </c>
       <c r="G511" t="inlineStr">
         <is>
@@ -60189,13 +60189,13 @@
         <v>212</v>
       </c>
       <c r="S511" t="n">
-        <v>153</v>
+        <v>306</v>
       </c>
       <c r="T511" t="n">
         <v>31</v>
       </c>
       <c r="U511" t="n">
-        <v>396</v>
+        <v>549</v>
       </c>
       <c r="V511" t="n">
         <v>924684.42</v>
@@ -60558,19 +60558,19 @@
         <v>9659997.08</v>
       </c>
       <c r="Y514" t="n">
-        <v>104456.58</v>
+        <v>153335</v>
       </c>
       <c r="Z514" t="n">
-        <v>9662.219999999999</v>
+        <v>14183.47</v>
       </c>
       <c r="AA514" t="n">
-        <v>114118.8</v>
+        <v>167518.47</v>
       </c>
       <c r="AB514" t="n">
-        <v>9555540.5</v>
+        <v>9506662.08</v>
       </c>
       <c r="AC514" t="n">
-        <v>0.01081331382762695</v>
+        <v>0.01587319320390519</v>
       </c>
     </row>
     <row r="515">
@@ -61377,19 +61377,19 @@
         <v>42794139.74</v>
       </c>
       <c r="Y521" t="n">
-        <v>24626355.83</v>
+        <v>34319619.39</v>
       </c>
       <c r="Z521" t="n">
-        <v>228610.44</v>
+        <v>452643.71</v>
       </c>
       <c r="AA521" t="n">
-        <v>24854966.27</v>
+        <v>34772263.1</v>
       </c>
       <c r="AB521" t="n">
-        <v>18167783.91</v>
+        <v>8474520.35</v>
       </c>
       <c r="AC521" t="n">
-        <v>0.5754609388018977</v>
+        <v>0.8019700734379104</v>
       </c>
     </row>
     <row r="522">
@@ -61728,19 +61728,19 @@
         <v>28955069.4</v>
       </c>
       <c r="Y524" t="n">
-        <v>12191198.01</v>
+        <v>14314001.61</v>
       </c>
       <c r="Z524" t="n">
-        <v>281590.16</v>
+        <v>337730.55</v>
       </c>
       <c r="AA524" t="n">
-        <v>12472788.17</v>
+        <v>14651732.16</v>
       </c>
       <c r="AB524" t="n">
-        <v>16763871.39</v>
+        <v>14641067.79</v>
       </c>
       <c r="AC524" t="n">
-        <v>0.4210384662383161</v>
+        <v>0.4943521775844889</v>
       </c>
     </row>
     <row r="525">
@@ -61845,19 +61845,19 @@
         <v>13934048.38</v>
       </c>
       <c r="Y525" t="n">
-        <v>4072181.76</v>
+        <v>4685070</v>
       </c>
       <c r="Z525" t="n">
-        <v>1125476.8</v>
+        <v>1294868.36</v>
       </c>
       <c r="AA525" t="n">
-        <v>5197658.56</v>
+        <v>5979938.36</v>
       </c>
       <c r="AB525" t="n">
-        <v>9861866.619999999</v>
+        <v>9248978.380000001</v>
       </c>
       <c r="AC525" t="n">
-        <v>0.292246850947133</v>
+        <v>0.3362317879364217</v>
       </c>
     </row>
     <row r="526">
@@ -61962,19 +61962,19 @@
         <v>9104897.539999999</v>
       </c>
       <c r="Y526" t="n">
-        <v>2264927.88</v>
+        <v>2625143.15</v>
       </c>
       <c r="Z526" t="n">
-        <v>626679.2</v>
+        <v>726351.11</v>
       </c>
       <c r="AA526" t="n">
-        <v>2891607.08</v>
+        <v>3351494.26</v>
       </c>
       <c r="AB526" t="n">
-        <v>6839969.66</v>
+        <v>6479754.39</v>
       </c>
       <c r="AC526" t="n">
-        <v>0.2487592935614737</v>
+        <v>0.2883220968129642</v>
       </c>
     </row>
     <row r="527">
@@ -62079,19 +62079,19 @@
         <v>10364111.47</v>
       </c>
       <c r="Y527" t="n">
-        <v>2249322.37</v>
+        <v>2579642.02</v>
       </c>
       <c r="Z527" t="n">
-        <v>622123.54</v>
+        <v>713477.2</v>
       </c>
       <c r="AA527" t="n">
-        <v>2871445.91</v>
+        <v>3293119.22</v>
       </c>
       <c r="AB527" t="n">
-        <v>8114789.1</v>
+        <v>7784469.45</v>
       </c>
       <c r="AC527" t="n">
-        <v>0.2170299283745546</v>
+        <v>0.2489014159551489</v>
       </c>
     </row>
     <row r="528">
@@ -62196,19 +62196,19 @@
         <v>15276741.09</v>
       </c>
       <c r="Y528" t="n">
-        <v>3665515.93</v>
+        <v>4187262.13</v>
       </c>
       <c r="Z528" t="n">
-        <v>1012888.24</v>
+        <v>1157069.81</v>
       </c>
       <c r="AA528" t="n">
-        <v>4678404.17</v>
+        <v>5344331.94</v>
       </c>
       <c r="AB528" t="n">
-        <v>11611225.16</v>
+        <v>11089478.96</v>
       </c>
       <c r="AC528" t="n">
-        <v>0.2399409604709089</v>
+        <v>0.2740939383165261</v>
       </c>
     </row>
     <row r="529">
@@ -62702,7 +62702,7 @@
         <v>45880</v>
       </c>
       <c r="F533" s="3" t="n">
-        <v>46119</v>
+        <v>46149</v>
       </c>
       <c r="G533" t="inlineStr">
         <is>
@@ -62763,13 +62763,13 @@
         <v>240</v>
       </c>
       <c r="S533" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="T533" t="n">
         <v>0</v>
       </c>
       <c r="U533" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="V533" t="n">
         <v>2380000</v>
@@ -62781,19 +62781,19 @@
         <v>2876761.94</v>
       </c>
       <c r="Y533" t="n">
-        <v>1971628.84</v>
+        <v>2383339.88</v>
       </c>
       <c r="Z533" t="n">
-        <v>82353.46000000001</v>
+        <v>99049.57000000001</v>
       </c>
       <c r="AA533" t="n">
-        <v>2053982.3</v>
+        <v>2482389.45</v>
       </c>
       <c r="AB533" t="n">
-        <v>905133.1</v>
+        <v>493422.06</v>
       </c>
       <c r="AC533" t="n">
-        <v>0.6853639199634295</v>
+        <v>0.828480051428934</v>
       </c>
     </row>
     <row r="534">
@@ -63360,19 +63360,19 @@
         <v>51814575.44</v>
       </c>
       <c r="Y538" t="n">
-        <v>5285927.92</v>
+        <v>5982264.67</v>
       </c>
       <c r="Z538" t="n">
-        <v>55132.21</v>
+        <v>74117.67999999999</v>
       </c>
       <c r="AA538" t="n">
-        <v>5341060.13</v>
+        <v>6056382.35</v>
       </c>
       <c r="AB538" t="n">
-        <v>46528647.52</v>
+        <v>45832310.77</v>
       </c>
       <c r="AC538" t="n">
-        <v>0.1020162352989069</v>
+        <v>0.1154552482424046</v>
       </c>
     </row>
     <row r="539">
@@ -64524,19 +64524,19 @@
         <v>5978999.99</v>
       </c>
       <c r="Y548" t="n">
-        <v>2046657.96</v>
+        <v>2550950.75</v>
       </c>
       <c r="Z548" t="n">
-        <v>0</v>
+        <v>2027.55</v>
       </c>
       <c r="AA548" t="n">
-        <v>2046657.96</v>
+        <v>2552978.3</v>
       </c>
       <c r="AB548" t="n">
-        <v>3932342.03</v>
+        <v>3428049.24</v>
       </c>
       <c r="AC548" t="n">
-        <v>0.3423077376522959</v>
+        <v>0.4266517401348917</v>
       </c>
     </row>
     <row r="549">
@@ -64992,19 +64992,19 @@
         <v>9218472.49</v>
       </c>
       <c r="Y552" t="n">
-        <v>631344.74</v>
+        <v>829896.92</v>
       </c>
       <c r="Z552" t="n">
-        <v>18249.81</v>
+        <v>25417.53</v>
       </c>
       <c r="AA552" t="n">
-        <v>649594.55</v>
+        <v>855314.45</v>
       </c>
       <c r="AB552" t="n">
-        <v>8587127.75</v>
+        <v>8388575.57</v>
       </c>
       <c r="AC552" t="n">
-        <v>0.06848691479904823</v>
+        <v>0.09002542676134839</v>
       </c>
     </row>
     <row r="553">
@@ -65343,19 +65343,19 @@
         <v>7056321.74</v>
       </c>
       <c r="Y555" t="n">
-        <v>368557.95</v>
+        <v>457787.93</v>
       </c>
       <c r="Z555" t="n">
-        <v>9226.82</v>
+        <v>12448.02</v>
       </c>
       <c r="AA555" t="n">
-        <v>377784.77</v>
+        <v>470235.95</v>
       </c>
       <c r="AB555" t="n">
-        <v>6687763.79</v>
+        <v>6598533.81</v>
       </c>
       <c r="AC555" t="n">
-        <v>0.0522308879300053</v>
+        <v>0.06487628354656062</v>
       </c>
     </row>
     <row r="556">
@@ -65928,19 +65928,19 @@
         <v>2086583.52</v>
       </c>
       <c r="Y560" t="n">
-        <v>85060.98</v>
+        <v>120945.94</v>
       </c>
       <c r="Z560" t="n">
-        <v>5367.33</v>
+        <v>7631.67</v>
       </c>
       <c r="AA560" t="n">
-        <v>90428.31</v>
+        <v>128577.61</v>
       </c>
       <c r="AB560" t="n">
-        <v>2001522.54</v>
+        <v>1965637.58</v>
       </c>
       <c r="AC560" t="n">
-        <v>0.04076567229860993</v>
+        <v>0.05796362275496166</v>
       </c>
     </row>
     <row r="561">
@@ -66747,19 +66747,19 @@
         <v>27994383.03</v>
       </c>
       <c r="Y567" t="n">
-        <v>745082.63</v>
+        <v>1555732.35</v>
       </c>
       <c r="Z567" t="n">
-        <v>158757.19</v>
+        <v>331506.92</v>
       </c>
       <c r="AA567" t="n">
-        <v>903839.8199999999</v>
+        <v>1887239.27</v>
       </c>
       <c r="AB567" t="n">
-        <v>27249300.4</v>
+        <v>26438650.68</v>
       </c>
       <c r="AC567" t="n">
-        <v>0.02661543314605423</v>
+        <v>0.05557301792766104</v>
       </c>
     </row>
     <row r="568">
@@ -67566,19 +67566,19 @@
         <v>14929346.95</v>
       </c>
       <c r="Y574" t="n">
-        <v>239923.68</v>
+        <v>551298.7</v>
       </c>
       <c r="Z574" t="n">
-        <v>51524.34</v>
+        <v>118361.5</v>
       </c>
       <c r="AA574" t="n">
-        <v>291448.02</v>
+        <v>669660.2</v>
       </c>
       <c r="AB574" t="n">
-        <v>14689423.27</v>
+        <v>14378048.25</v>
       </c>
       <c r="AC574" t="n">
-        <v>0.01607060783057225</v>
+        <v>0.0369271811986391</v>
       </c>
     </row>
     <row r="575">
@@ -67683,19 +67683,19 @@
         <v>18749931.77</v>
       </c>
       <c r="Y575" t="n">
-        <v>1373218.42</v>
+        <v>2160121.29</v>
       </c>
       <c r="Z575" t="n">
-        <v>291480.71</v>
+        <v>458510.34</v>
       </c>
       <c r="AA575" t="n">
-        <v>1664699.13</v>
+        <v>2618631.63</v>
       </c>
       <c r="AB575" t="n">
-        <v>17376713.35</v>
+        <v>16589810.48</v>
       </c>
       <c r="AC575" t="n">
-        <v>0.07323858224365154</v>
+        <v>0.1152068880301851</v>
       </c>
     </row>
     <row r="576">
@@ -67911,19 +67911,19 @@
         <v>3187539.16</v>
       </c>
       <c r="Y577" t="n">
-        <v>0</v>
+        <v>82179.63</v>
       </c>
       <c r="Z577" t="n">
-        <v>0</v>
+        <v>2621.53</v>
       </c>
       <c r="AA577" t="n">
-        <v>0</v>
+        <v>84801.16</v>
       </c>
       <c r="AB577" t="n">
-        <v>3187539.16</v>
+        <v>3105359.53</v>
       </c>
       <c r="AC577" t="n">
-        <v>0</v>
+        <v>0.02578152796717327</v>
       </c>
     </row>
     <row r="578">
@@ -68028,19 +68028,19 @@
         <v>4324285.68</v>
       </c>
       <c r="Y578" t="n">
-        <v>0</v>
+        <v>70934.85000000001</v>
       </c>
       <c r="Z578" t="n">
-        <v>0</v>
+        <v>2262.82</v>
       </c>
       <c r="AA578" t="n">
-        <v>0</v>
+        <v>73197.67</v>
       </c>
       <c r="AB578" t="n">
-        <v>4324285.68</v>
+        <v>4253350.83</v>
       </c>
       <c r="AC578" t="n">
-        <v>0</v>
+        <v>0.01640383065533265</v>
       </c>
     </row>
     <row r="579">
@@ -68613,19 +68613,19 @@
         <v>3028048.96</v>
       </c>
       <c r="Y583" t="n">
-        <v>0</v>
+        <v>151508.22</v>
       </c>
       <c r="Z583" t="n">
-        <v>0</v>
+        <v>4833.11</v>
       </c>
       <c r="AA583" t="n">
-        <v>0</v>
+        <v>156341.33</v>
       </c>
       <c r="AB583" t="n">
-        <v>3028048.96</v>
+        <v>2876540.74</v>
       </c>
       <c r="AC583" t="n">
-        <v>0</v>
+        <v>0.05003493074299565</v>
       </c>
     </row>
     <row r="584">
@@ -68705,7 +68705,7 @@
       </c>
       <c r="Q584" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Manga</t>
+          <t xml:space="preserve"> Obra 1 - Manga, Matias Cardoso</t>
         </is>
       </c>
       <c r="R584" t="n">
@@ -69303,19 +69303,19 @@
         <v>14398046.07</v>
       </c>
       <c r="Y589" t="n">
-        <v>0</v>
+        <v>318583.52</v>
       </c>
       <c r="Z589" t="n">
-        <v>0</v>
+        <v>30598.96</v>
       </c>
       <c r="AA589" t="n">
-        <v>0</v>
+        <v>349182.48</v>
       </c>
       <c r="AB589" t="n">
-        <v>14398046.07</v>
+        <v>14079462.55</v>
       </c>
       <c r="AC589" t="n">
-        <v>0</v>
+        <v>0.02212685793968987</v>
       </c>
     </row>
     <row r="590">
@@ -69888,41 +69888,35 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>PO</t>
+          <t>DC-9497471/2026</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>130160600325</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>SERVIÇOS ESPECIAIS DE APOIO À COORDENAÇÃO E APOIO TÉCNICO NO PLANEJAMENTO, MONITORAMENTO E AVALIAÇÃO DO PORTIFÓLIO DE EMPREENDIMENTOS DO DER-MG</t>
+          <t>MELHORAMENTO E PAVIMENTAÇÃO DA INTERSEÇÃO DE ACESSO AO PRESÍDIO DE ITURAMA, NA VIA MUNICIPAL - EXTENSÃO 2,000KM</t>
         </is>
       </c>
       <c r="D595" s="3" t="n">
-        <v>45589</v>
-      </c>
-      <c r="E595" s="3" t="n">
-        <v>45628</v>
-      </c>
-      <c r="F595" s="3" t="n">
-        <v>46722</v>
+        <v>46098</v>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>A Iniciar</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYSTRA ENGENHARIA E  CONSULTORIA LTDA </t>
+          <t>CONSTRUTORA ITUSANE DE ITURAMA LTDA</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>52635422000307</t>
+          <t>24290865000106</t>
         </is>
       </c>
       <c r="J595" t="inlineStr">
@@ -69932,7 +69926,7 @@
       </c>
       <c r="K595" t="inlineStr">
         <is>
-          <t>ASSESSORIA DE GESTÃO ESTRATÉGICA</t>
+          <t xml:space="preserve">DIRETORIA DE CONSTRUÇÃO E OBRAS RODOVIÁRIAS </t>
         </is>
       </c>
       <c r="L595" t="inlineStr">
@@ -69947,16 +69941,26 @@
       </c>
       <c r="N595" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Melhoramento e Pavimentação</t>
         </is>
       </c>
       <c r="O595" t="inlineStr">
         <is>
-          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+          <t>Obra Rodoviária</t>
+        </is>
+      </c>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Melhoramento e Pavimentação da interseção de acesso ao Presídio de Iturama, na via Municipal - Extensão 2,000km</t>
+        </is>
+      </c>
+      <c r="Q595" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Iturama</t>
         </is>
       </c>
       <c r="R595" t="n">
-        <v>1095</v>
+        <v>0</v>
       </c>
       <c r="S595" t="n">
         <v>0</v>
@@ -69965,16 +69969,16 @@
         <v>0</v>
       </c>
       <c r="U595" t="n">
-        <v>1095</v>
+        <v>0</v>
       </c>
       <c r="V595" t="n">
-        <v>5774752.44</v>
+        <v>3700000</v>
       </c>
       <c r="W595" t="n">
         <v>0</v>
       </c>
       <c r="X595" t="n">
-        <v>5774752.44</v>
+        <v>3700000</v>
       </c>
       <c r="Y595" t="n">
         <v>0</v>
@@ -69986,7 +69990,7 @@
         <v>0</v>
       </c>
       <c r="AB595" t="n">
-        <v>5774752.44</v>
+        <v>3700000</v>
       </c>
       <c r="AC595" t="n">
         <v>0</v>
@@ -69995,106 +69999,669 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
+          <t>DC-9495596/2026</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>230152003025</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>PONTE SOBRE O RIO SÃO JOÃO, RODOVIA MG-430, NO TRECHO IGARATINGA - ENTR. MG-252</t>
+        </is>
+      </c>
+      <c r="D596" s="3" t="n">
+        <v>46080</v>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>A Iniciar</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>S3 CONSTRUTORA LTDA</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>23785668000197</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIRETORIA DE CONSTRUÇÃO E OBRAS RODOVIÁRIAS </t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO GLOBAL</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>OAE</t>
+        </is>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária</t>
+        </is>
+      </c>
+      <c r="P596" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Projeto executivo de engenharia e execução das obras Encabeçamento e ponte sobre o Rio São João, Rodovia MG-430, no trecho Igaratinga - Entr. MG-252</t>
+        </is>
+      </c>
+      <c r="Q596" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Igaratinga</t>
+        </is>
+      </c>
+      <c r="R596" t="n">
+        <v>0</v>
+      </c>
+      <c r="S596" t="n">
+        <v>0</v>
+      </c>
+      <c r="T596" t="n">
+        <v>0</v>
+      </c>
+      <c r="U596" t="n">
+        <v>0</v>
+      </c>
+      <c r="V596" t="n">
+        <v>12246076.65</v>
+      </c>
+      <c r="W596" t="n">
+        <v>0</v>
+      </c>
+      <c r="X596" t="n">
+        <v>12246076.65</v>
+      </c>
+      <c r="Y596" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z596" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA596" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB596" t="n">
+        <v>12246076.65</v>
+      </c>
+      <c r="AC596" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>DM-005/2024-A</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>230176203623</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+        </is>
+      </c>
+      <c r="D597" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="E597" s="3" t="n">
+        <v>46099</v>
+      </c>
+      <c r="F597" s="3" t="n">
+        <v>46829</v>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>ETHOS ENGENHARIA DE INFR  S A</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>19758779000137</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>Manutenção e Conservação</t>
+        </is>
+      </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="P597" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - MANUTENÇÃO E CONSERVAÇÃO - 25ª URG</t>
+        </is>
+      </c>
+      <c r="Q597" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Campina Verde, Campo Florido, Comendador Gomes, Conceição das Alagoas, Conquista, Delta, Frutal, Itapagipe, Iturama, Nova Ponte, Pirajuba, Planura, Sacramento, São Francisco de Sales, Uberaba, Uberlândia, Veríssimo, Água Comprida</t>
+        </is>
+      </c>
+      <c r="R597" t="n">
+        <v>731</v>
+      </c>
+      <c r="S597" t="n">
+        <v>0</v>
+      </c>
+      <c r="T597" t="n">
+        <v>0</v>
+      </c>
+      <c r="U597" t="n">
+        <v>731</v>
+      </c>
+      <c r="V597" t="n">
+        <v>32998445.8</v>
+      </c>
+      <c r="W597" t="n">
+        <v>0</v>
+      </c>
+      <c r="X597" t="n">
+        <v>32998445.8</v>
+      </c>
+      <c r="Y597" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z597" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA597" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB597" t="n">
+        <v>32998445.8</v>
+      </c>
+      <c r="AC597" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>DM-9497685/2026</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>230176202325</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>RECUPERAÇÃO FUNCIONAL MG-275, CAPELA NOVA - ENTRº BR-040 (CARANDAÍ)</t>
+        </is>
+      </c>
+      <c r="D598" s="3" t="n">
+        <v>46101</v>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>A Iniciar</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>CONSORCIO LCM/AGR RODOVIA MG-275</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>65530726000181</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>Recuperação Funcional do Pavimento</t>
+        </is>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária</t>
+        </is>
+      </c>
+      <c r="P598" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Recuperação funcional MG-275, Capela Nova - Entrº BR-040 (Carandaí)</t>
+        </is>
+      </c>
+      <c r="Q598" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Barbacena, Capela Nova, Carandaí</t>
+        </is>
+      </c>
+      <c r="R598" t="n">
+        <v>0</v>
+      </c>
+      <c r="S598" t="n">
+        <v>0</v>
+      </c>
+      <c r="T598" t="n">
+        <v>0</v>
+      </c>
+      <c r="U598" t="n">
+        <v>0</v>
+      </c>
+      <c r="V598" t="n">
+        <v>14264750.82</v>
+      </c>
+      <c r="W598" t="n">
+        <v>0</v>
+      </c>
+      <c r="X598" t="n">
+        <v>14264750.82</v>
+      </c>
+      <c r="Y598" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z598" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA598" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB598" t="n">
+        <v>14264750.82</v>
+      </c>
+      <c r="AC598" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>DO-001/2021- C</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Não Disponível</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>SOLUÇÃO INFORMATIZADA PARA A LAVRATURA E IMPRESSÃO DE AUTOS DE INFRAÇÃO DE TRÂNSITO.</t>
+        </is>
+      </c>
+      <c r="D599" s="3" t="n">
+        <v>45195</v>
+      </c>
+      <c r="E599" s="3" t="n">
+        <v>46110</v>
+      </c>
+      <c r="F599" s="3" t="n">
+        <v>46474</v>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>GCT GERENCIAMENTO E CONTROLE DE TRANSITO LTDA</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>01466431000100</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>PREGÃO ELETRÔNICO</t>
+        </is>
+      </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>NÃO DISPONÍVEL</t>
+        </is>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>Prestação de Serviços de Informática</t>
+        </is>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="P599" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 2 - Prestação de Serviços de natureza continuada de Fornecimento de Solução Informatizada para a lavratura e impressão de Autos de Infração de Trânsito.</t>
+        </is>
+      </c>
+      <c r="Q599" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 2 - Belo Horizonte, Minas Gerais</t>
+        </is>
+      </c>
+      <c r="R599" t="n">
+        <v>365</v>
+      </c>
+      <c r="S599" t="n">
+        <v>0</v>
+      </c>
+      <c r="T599" t="n">
+        <v>0</v>
+      </c>
+      <c r="U599" t="n">
+        <v>365</v>
+      </c>
+      <c r="V599" t="n">
+        <v>2949000</v>
+      </c>
+      <c r="W599" t="n">
+        <v>0</v>
+      </c>
+      <c r="X599" t="n">
+        <v>2949000</v>
+      </c>
+      <c r="Y599" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z599" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA599" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB599" t="n">
+        <v>2949000</v>
+      </c>
+      <c r="AC599" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Não Disponível</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>SERVIÇOS ESPECIAIS DE APOIO À COORDENAÇÃO E APOIO TÉCNICO NO PLANEJAMENTO, MONITORAMENTO E AVALIAÇÃO DO PORTIFÓLIO DE EMPREENDIMENTOS DO DER-MG</t>
+        </is>
+      </c>
+      <c r="D600" s="3" t="n">
+        <v>45589</v>
+      </c>
+      <c r="E600" s="3" t="n">
+        <v>45628</v>
+      </c>
+      <c r="F600" s="3" t="n">
+        <v>46722</v>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYSTRA ENGENHARIA E  CONSULTORIA LTDA </t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>52635422000307</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>ASSESSORIA DE GESTÃO ESTRATÉGICA</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>Consultoria</t>
+        </is>
+      </c>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+        </is>
+      </c>
+      <c r="R600" t="n">
+        <v>1095</v>
+      </c>
+      <c r="S600" t="n">
+        <v>0</v>
+      </c>
+      <c r="T600" t="n">
+        <v>0</v>
+      </c>
+      <c r="U600" t="n">
+        <v>1095</v>
+      </c>
+      <c r="V600" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="W600" t="n">
+        <v>0</v>
+      </c>
+      <c r="X600" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="Y600" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z600" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA600" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB600" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="AC600" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
           <t>DP-001/2023</t>
         </is>
       </c>
-      <c r="B596" t="inlineStr">
+      <c r="B601" t="inlineStr">
         <is>
           <t>2301601000022020</t>
         </is>
       </c>
-      <c r="C596" t="inlineStr">
+      <c r="C601" t="inlineStr">
         <is>
           <t>ELABORAÇÃO DE PROJETO DE ENGENHARIA RODOVIÁRIA DE MELHORAMENTOS, PAVIMENTAÇÃO E OAE - LOTE 2</t>
         </is>
       </c>
-      <c r="D596" s="3" t="n">
+      <c r="D601" s="3" t="n">
         <v>45166</v>
       </c>
-      <c r="G596" t="inlineStr">
+      <c r="G601" t="inlineStr">
         <is>
           <t>A Iniciar</t>
         </is>
       </c>
-      <c r="H596" t="inlineStr">
+      <c r="H601" t="inlineStr">
         <is>
           <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
-      <c r="I596" t="inlineStr">
+      <c r="I601" t="inlineStr">
         <is>
           <t>38743357000132</t>
         </is>
       </c>
-      <c r="J596" t="inlineStr">
+      <c r="J601" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr">
+      <c r="K601" t="inlineStr">
         <is>
           <t>DIRETORIA DE PROJETOS</t>
         </is>
       </c>
-      <c r="L596" t="inlineStr">
+      <c r="L601" t="inlineStr">
         <is>
           <t>RDC</t>
         </is>
       </c>
-      <c r="M596" t="inlineStr">
+      <c r="M601" t="inlineStr">
         <is>
           <t>EMPREITADA POR PREÇO UNITÁRIO</t>
         </is>
       </c>
-      <c r="N596" t="inlineStr">
+      <c r="N601" t="inlineStr">
         <is>
           <t>Consultoria para Projetos</t>
         </is>
       </c>
-      <c r="O596" t="inlineStr">
+      <c r="O601" t="inlineStr">
         <is>
           <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
         </is>
       </c>
-      <c r="R596" t="n">
-        <v>0</v>
-      </c>
-      <c r="S596" t="n">
-        <v>0</v>
-      </c>
-      <c r="T596" t="n">
-        <v>0</v>
-      </c>
-      <c r="U596" t="n">
-        <v>0</v>
-      </c>
-      <c r="V596" t="n">
+      <c r="R601" t="n">
+        <v>0</v>
+      </c>
+      <c r="S601" t="n">
+        <v>0</v>
+      </c>
+      <c r="T601" t="n">
+        <v>0</v>
+      </c>
+      <c r="U601" t="n">
+        <v>0</v>
+      </c>
+      <c r="V601" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="W596" t="n">
-        <v>0</v>
-      </c>
-      <c r="X596" t="n">
+      <c r="W601" t="n">
+        <v>0</v>
+      </c>
+      <c r="X601" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="Y596" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z596" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA596" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB596" t="n">
+      <c r="Y601" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z601" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA601" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB601" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="AC596" t="n">
+      <c r="AC601" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC596"/>
+  <autoFilter ref="A1:AC601"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/contratos.xlsx
+++ b/upload/contratos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AC$601</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AC$604</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC601"/>
+  <dimension ref="A1:AC604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2273,7 +2273,7 @@
         <v>44524</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1271</v>
+        <v>1278</v>
       </c>
       <c r="U16" t="n">
-        <v>1631</v>
+        <v>1638</v>
       </c>
       <c r="V16" t="n">
         <v>1452371.99</v>
@@ -12200,7 +12200,7 @@
         <v>44850</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -12264,10 +12264,10 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="U101" t="n">
-        <v>1263</v>
+        <v>1270</v>
       </c>
       <c r="V101" t="n">
         <v>1365885.84</v>
@@ -20156,11 +20156,11 @@
         <v>45103</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Paralisado</t>
+          <t>Rescindido</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -20220,10 +20220,10 @@
         <v>240</v>
       </c>
       <c r="T169" t="n">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="U169" t="n">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="V169" t="n">
         <v>20645773.23</v>
@@ -24017,7 +24017,7 @@
         <v>44767</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>46210</v>
+        <v>46217</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -24081,10 +24081,10 @@
         <v>0</v>
       </c>
       <c r="T202" t="n">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="U202" t="n">
-        <v>1444</v>
+        <v>1451</v>
       </c>
       <c r="V202" t="n">
         <v>2519553.4</v>
@@ -26819,7 +26819,7 @@
         <v>44810</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>46131</v>
+        <v>46138</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -26883,10 +26883,10 @@
         <v>0</v>
       </c>
       <c r="T226" t="n">
-        <v>1141</v>
+        <v>1148</v>
       </c>
       <c r="U226" t="n">
-        <v>1322</v>
+        <v>1329</v>
       </c>
       <c r="V226" t="n">
         <v>1559477.28</v>
@@ -28457,7 +28457,7 @@
         <v>44579</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>46327</v>
+        <v>46334</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -28521,10 +28521,10 @@
         <v>180</v>
       </c>
       <c r="T240" t="n">
-        <v>1209</v>
+        <v>1216</v>
       </c>
       <c r="U240" t="n">
-        <v>1749</v>
+        <v>1756</v>
       </c>
       <c r="V240" t="n">
         <v>1175120.88</v>
@@ -37097,7 +37097,7 @@
         <v>45384</v>
       </c>
       <c r="F314" s="3" t="n">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -37161,10 +37161,10 @@
         <v>330</v>
       </c>
       <c r="T314" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="U314" t="n">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="V314" t="n">
         <v>2816620.4</v>
@@ -38735,7 +38735,7 @@
         <v>45082</v>
       </c>
       <c r="F328" s="3" t="n">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
@@ -38799,10 +38799,10 @@
         <v>0</v>
       </c>
       <c r="T328" t="n">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="U328" t="n">
-        <v>1114</v>
+        <v>1121</v>
       </c>
       <c r="V328" t="n">
         <v>3606475.63</v>
@@ -42479,7 +42479,7 @@
         <v>45236</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>46124</v>
+        <v>46131</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -42543,10 +42543,10 @@
         <v>480</v>
       </c>
       <c r="T360" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="U360" t="n">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="V360" t="n">
         <v>5042730.21</v>
@@ -45170,7 +45170,7 @@
         <v>45237</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>46117</v>
+        <v>46124</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -45234,10 +45234,10 @@
         <v>510</v>
       </c>
       <c r="T383" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="U383" t="n">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="V383" t="n">
         <v>4065559.6</v>
@@ -48791,7 +48791,7 @@
         <v>45386</v>
       </c>
       <c r="F414" s="3" t="n">
-        <v>46116</v>
+        <v>46123</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
@@ -48855,10 +48855,10 @@
         <v>0</v>
       </c>
       <c r="T414" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="U414" t="n">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="V414" t="n">
         <v>65748419.13</v>
@@ -51008,7 +51008,7 @@
         <v>45355</v>
       </c>
       <c r="F433" s="3" t="n">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         <v>330</v>
       </c>
       <c r="T433" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="U433" t="n">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="V433" t="n">
         <v>5820891.54</v>
@@ -52257,19 +52257,19 @@
         <v>34071020.86</v>
       </c>
       <c r="Y443" t="n">
-        <v>14926675.21</v>
+        <v>15858861.26</v>
       </c>
       <c r="Z443" t="n">
-        <v>2396358.14</v>
+        <v>2594810.81</v>
       </c>
       <c r="AA443" t="n">
-        <v>17323033.35</v>
+        <v>18453672.07</v>
       </c>
       <c r="AB443" t="n">
-        <v>19144345.65</v>
+        <v>18212159.6</v>
       </c>
       <c r="AC443" t="n">
-        <v>0.4381047245791272</v>
+        <v>0.4654648102610448</v>
       </c>
     </row>
     <row r="444">
@@ -52763,7 +52763,7 @@
         <v>45722</v>
       </c>
       <c r="F448" s="3" t="n">
-        <v>46120</v>
+        <v>46127</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
@@ -52827,10 +52827,10 @@
         <v>0</v>
       </c>
       <c r="T448" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="U448" t="n">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="V448" t="n">
         <v>1922644.28</v>
@@ -56150,7 +56150,7 @@
         <v>45573</v>
       </c>
       <c r="F477" s="3" t="n">
-        <v>46183</v>
+        <v>46190</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
@@ -56214,10 +56214,10 @@
         <v>0</v>
       </c>
       <c r="T477" t="n">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="U477" t="n">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="V477" t="n">
         <v>3876550</v>
@@ -57510,10 +57510,10 @@
         <v>158500000</v>
       </c>
       <c r="W488" t="n">
-        <v>0</v>
+        <v>4658631.5</v>
       </c>
       <c r="X488" t="n">
-        <v>158500000</v>
+        <v>163158631.5</v>
       </c>
       <c r="Y488" t="n">
         <v>61056495.82</v>
@@ -57525,10 +57525,10 @@
         <v>63382144.31</v>
       </c>
       <c r="AB488" t="n">
-        <v>97443504.18000001</v>
+        <v>102102135.68</v>
       </c>
       <c r="AC488" t="n">
-        <v>0.3852144846687697</v>
+        <v>0.374215542620557</v>
       </c>
     </row>
     <row r="489">
@@ -58256,7 +58256,7 @@
         <v>45653</v>
       </c>
       <c r="F495" s="3" t="n">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
@@ -58320,10 +58320,10 @@
         <v>0</v>
       </c>
       <c r="T495" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="U495" t="n">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="V495" t="n">
         <v>21305007.22</v>
@@ -61235,7 +61235,7 @@
       </c>
       <c r="Q520" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Guapé, Pimenta</t>
+          <t xml:space="preserve"> Obra 1 - Formiga, Guapé, Pains, Pimenta</t>
         </is>
       </c>
       <c r="R520" t="n">
@@ -61371,10 +61371,10 @@
         <v>35900000</v>
       </c>
       <c r="W521" t="n">
-        <v>6894139.74</v>
+        <v>7889355.88</v>
       </c>
       <c r="X521" t="n">
-        <v>42794139.74</v>
+        <v>43789355.88</v>
       </c>
       <c r="Y521" t="n">
         <v>34319619.39</v>
@@ -61386,10 +61386,10 @@
         <v>34772263.1</v>
       </c>
       <c r="AB521" t="n">
-        <v>8474520.35</v>
+        <v>9469736.49</v>
       </c>
       <c r="AC521" t="n">
-        <v>0.8019700734379104</v>
+        <v>0.7837434166432868</v>
       </c>
     </row>
     <row r="522">
@@ -61605,10 +61605,10 @@
         <v>78647423.75</v>
       </c>
       <c r="W523" t="n">
-        <v>8753988.41</v>
+        <v>17014249.18</v>
       </c>
       <c r="X523" t="n">
-        <v>87401412.16</v>
+        <v>95661672.93000001</v>
       </c>
       <c r="Y523" t="n">
         <v>12480224.9</v>
@@ -61620,10 +61620,10 @@
         <v>13020980.01</v>
       </c>
       <c r="AB523" t="n">
-        <v>74921187.26000001</v>
+        <v>83181448.03</v>
       </c>
       <c r="AC523" t="n">
-        <v>0.1427920280870666</v>
+        <v>0.130462122579984</v>
       </c>
     </row>
     <row r="524">
@@ -65220,10 +65220,10 @@
         <v>7710000</v>
       </c>
       <c r="W554" t="n">
-        <v>0</v>
+        <v>1924126.24</v>
       </c>
       <c r="X554" t="n">
-        <v>7710000</v>
+        <v>9634126.24</v>
       </c>
       <c r="Y554" t="n">
         <v>3808666.66</v>
@@ -65235,10 +65235,10 @@
         <v>3876682.7</v>
       </c>
       <c r="AB554" t="n">
-        <v>3901333.34</v>
+        <v>5825459.58</v>
       </c>
       <c r="AC554" t="n">
-        <v>0.4939904876783398</v>
+        <v>0.3953307819640943</v>
       </c>
     </row>
     <row r="555">
@@ -67215,19 +67215,19 @@
         <v>22167830.47</v>
       </c>
       <c r="Y571" t="n">
-        <v>1466960.34</v>
+        <v>2304211.64</v>
       </c>
       <c r="Z571" t="n">
-        <v>313064.99</v>
+        <v>491722.4</v>
       </c>
       <c r="AA571" t="n">
-        <v>1780025.33</v>
+        <v>2795934.04</v>
       </c>
       <c r="AB571" t="n">
-        <v>20700870.13</v>
+        <v>19863618.83</v>
       </c>
       <c r="AC571" t="n">
-        <v>0.06617518759831981</v>
+        <v>0.1039439399862931</v>
       </c>
     </row>
     <row r="572">
@@ -68730,19 +68730,19 @@
         <v>6677404.33</v>
       </c>
       <c r="Y584" t="n">
-        <v>0</v>
+        <v>119550.83</v>
       </c>
       <c r="Z584" t="n">
-        <v>0</v>
+        <v>3813.67</v>
       </c>
       <c r="AA584" t="n">
-        <v>0</v>
+        <v>123364.5</v>
       </c>
       <c r="AB584" t="n">
-        <v>6677404.33</v>
+        <v>6557853.5</v>
       </c>
       <c r="AC584" t="n">
-        <v>0</v>
+        <v>0.01790378777317503</v>
       </c>
     </row>
     <row r="585">
@@ -70455,27 +70455,27 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>PO</t>
+          <t>DO-009482014/2025</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>2301901 1/2025</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>SERVIÇOS ESPECIAIS DE APOIO À COORDENAÇÃO E APOIO TÉCNICO NO PLANEJAMENTO, MONITORAMENTO E AVALIAÇÃO DO PORTIFÓLIO DE EMPREENDIMENTOS DO DER-MG</t>
+          <t>PROGRAMA DE CONTROLE DE VELOCIDADE-LOTE 01</t>
         </is>
       </c>
       <c r="D600" s="3" t="n">
-        <v>45589</v>
+        <v>45974</v>
       </c>
       <c r="E600" s="3" t="n">
-        <v>45628</v>
+        <v>46099</v>
       </c>
       <c r="F600" s="3" t="n">
-        <v>46722</v>
+        <v>47013</v>
       </c>
       <c r="G600" t="inlineStr">
         <is>
@@ -70484,12 +70484,12 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYSTRA ENGENHARIA E  CONSULTORIA LTDA </t>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>52635422000307</t>
+          <t>16502551000193</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
@@ -70499,7 +70499,7 @@
       </c>
       <c r="K600" t="inlineStr">
         <is>
-          <t>ASSESSORIA DE GESTÃO ESTRATÉGICA</t>
+          <t>DIRETORIA DE OPERACAO VIARIA  DO DER-MG - CAMG</t>
         </is>
       </c>
       <c r="L600" t="inlineStr">
@@ -70514,16 +70514,26 @@
       </c>
       <c r="N600" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Operação-Radar</t>
         </is>
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+          <t>Obra Rodoviária</t>
+        </is>
+      </c>
+      <c r="P600" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 01</t>
+        </is>
+      </c>
+      <c r="Q600" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Belo Horizonte</t>
         </is>
       </c>
       <c r="R600" t="n">
-        <v>1095</v>
+        <v>915</v>
       </c>
       <c r="S600" t="n">
         <v>0</v>
@@ -70532,16 +70542,16 @@
         <v>0</v>
       </c>
       <c r="U600" t="n">
-        <v>1095</v>
+        <v>915</v>
       </c>
       <c r="V600" t="n">
-        <v>5774752.44</v>
+        <v>77898894.3</v>
       </c>
       <c r="W600" t="n">
         <v>0</v>
       </c>
       <c r="X600" t="n">
-        <v>5774752.44</v>
+        <v>77898894.3</v>
       </c>
       <c r="Y600" t="n">
         <v>0</v>
@@ -70553,7 +70563,7 @@
         <v>0</v>
       </c>
       <c r="AB600" t="n">
-        <v>5774752.44</v>
+        <v>77898894.3</v>
       </c>
       <c r="AC600" t="n">
         <v>0</v>
@@ -70562,106 +70572,431 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
+          <t>DO-009482046/2025</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Não Disponível</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>PROGRAMA DE CONTROLE DE VELOCIDADE- LOTE 2</t>
+        </is>
+      </c>
+      <c r="D601" s="3" t="n">
+        <v>45968</v>
+      </c>
+      <c r="E601" s="3" t="n">
+        <v>46099</v>
+      </c>
+      <c r="F601" s="3" t="n">
+        <v>47013</v>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>ELISEU KOPP &amp; CIA LTDA</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>93315190000117</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE OPERACAO VIARIA  DO DER-MG - CAMG</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>Operação-Radar</t>
+        </is>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária</t>
+        </is>
+      </c>
+      <c r="P601" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 02</t>
+        </is>
+      </c>
+      <c r="Q601" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="R601" t="n">
+        <v>915</v>
+      </c>
+      <c r="S601" t="n">
+        <v>0</v>
+      </c>
+      <c r="T601" t="n">
+        <v>0</v>
+      </c>
+      <c r="U601" t="n">
+        <v>915</v>
+      </c>
+      <c r="V601" t="n">
+        <v>45188997.86</v>
+      </c>
+      <c r="W601" t="n">
+        <v>0</v>
+      </c>
+      <c r="X601" t="n">
+        <v>45188997.86</v>
+      </c>
+      <c r="Y601" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z601" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA601" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB601" t="n">
+        <v>45188997.86</v>
+      </c>
+      <c r="AC601" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Não Disponível</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>SERVIÇOS ESPECIAIS DE APOIO À COORDENAÇÃO E APOIO TÉCNICO NO PLANEJAMENTO, MONITORAMENTO E AVALIAÇÃO DO PORTIFÓLIO DE EMPREENDIMENTOS DO DER-MG</t>
+        </is>
+      </c>
+      <c r="D602" s="3" t="n">
+        <v>45589</v>
+      </c>
+      <c r="E602" s="3" t="n">
+        <v>45628</v>
+      </c>
+      <c r="F602" s="3" t="n">
+        <v>46722</v>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYSTRA ENGENHARIA E  CONSULTORIA LTDA </t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>52635422000307</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>ASSESSORIA DE GESTÃO ESTRATÉGICA</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>Consultoria</t>
+        </is>
+      </c>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+        </is>
+      </c>
+      <c r="R602" t="n">
+        <v>1095</v>
+      </c>
+      <c r="S602" t="n">
+        <v>0</v>
+      </c>
+      <c r="T602" t="n">
+        <v>0</v>
+      </c>
+      <c r="U602" t="n">
+        <v>1095</v>
+      </c>
+      <c r="V602" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="W602" t="n">
+        <v>0</v>
+      </c>
+      <c r="X602" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="Y602" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z602" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA602" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB602" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="AC602" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>009482014/2025</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>2301901 1/2025</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇO DE ENGENHARIA DE TRANSITO - LOTE 01 </t>
+        </is>
+      </c>
+      <c r="D603" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>A Iniciar</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>16502551000193</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>GERÊNCIA DE TRÂFEGO E SEGURANÇA VIÁRIA</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>Operação-Radar</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="R603" t="n">
+        <v>0</v>
+      </c>
+      <c r="S603" t="n">
+        <v>0</v>
+      </c>
+      <c r="T603" t="n">
+        <v>0</v>
+      </c>
+      <c r="U603" t="n">
+        <v>0</v>
+      </c>
+      <c r="V603" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="W603" t="n">
+        <v>0</v>
+      </c>
+      <c r="X603" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="Y603" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z603" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA603" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB603" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="AC603" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
           <t>DP-001/2023</t>
         </is>
       </c>
-      <c r="B601" t="inlineStr">
+      <c r="B604" t="inlineStr">
         <is>
           <t>2301601000022020</t>
         </is>
       </c>
-      <c r="C601" t="inlineStr">
+      <c r="C604" t="inlineStr">
         <is>
           <t>ELABORAÇÃO DE PROJETO DE ENGENHARIA RODOVIÁRIA DE MELHORAMENTOS, PAVIMENTAÇÃO E OAE - LOTE 2</t>
         </is>
       </c>
-      <c r="D601" s="3" t="n">
+      <c r="D604" s="3" t="n">
         <v>45166</v>
       </c>
-      <c r="G601" t="inlineStr">
+      <c r="G604" t="inlineStr">
         <is>
           <t>A Iniciar</t>
         </is>
       </c>
-      <c r="H601" t="inlineStr">
+      <c r="H604" t="inlineStr">
         <is>
           <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
-      <c r="I601" t="inlineStr">
+      <c r="I604" t="inlineStr">
         <is>
           <t>38743357000132</t>
         </is>
       </c>
-      <c r="J601" t="inlineStr">
+      <c r="J604" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr">
+      <c r="K604" t="inlineStr">
         <is>
           <t>DIRETORIA DE PROJETOS</t>
         </is>
       </c>
-      <c r="L601" t="inlineStr">
+      <c r="L604" t="inlineStr">
         <is>
           <t>RDC</t>
         </is>
       </c>
-      <c r="M601" t="inlineStr">
+      <c r="M604" t="inlineStr">
         <is>
           <t>EMPREITADA POR PREÇO UNITÁRIO</t>
         </is>
       </c>
-      <c r="N601" t="inlineStr">
+      <c r="N604" t="inlineStr">
         <is>
           <t>Consultoria para Projetos</t>
         </is>
       </c>
-      <c r="O601" t="inlineStr">
+      <c r="O604" t="inlineStr">
         <is>
           <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
         </is>
       </c>
-      <c r="R601" t="n">
-        <v>0</v>
-      </c>
-      <c r="S601" t="n">
-        <v>0</v>
-      </c>
-      <c r="T601" t="n">
-        <v>0</v>
-      </c>
-      <c r="U601" t="n">
-        <v>0</v>
-      </c>
-      <c r="V601" t="n">
+      <c r="R604" t="n">
+        <v>0</v>
+      </c>
+      <c r="S604" t="n">
+        <v>0</v>
+      </c>
+      <c r="T604" t="n">
+        <v>0</v>
+      </c>
+      <c r="U604" t="n">
+        <v>0</v>
+      </c>
+      <c r="V604" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="W601" t="n">
-        <v>0</v>
-      </c>
-      <c r="X601" t="n">
+      <c r="W604" t="n">
+        <v>0</v>
+      </c>
+      <c r="X604" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="Y601" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z601" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA601" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB601" t="n">
+      <c r="Y604" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z604" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA604" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB604" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="AC601" t="n">
+      <c r="AC604" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC601"/>
+  <autoFilter ref="A1:AC604"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/contratos.xlsx
+++ b/upload/contratos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AC$604</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AC$609</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC604"/>
+  <dimension ref="A1:AC609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2273,7 +2273,7 @@
         <v>44524</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1278</v>
+        <v>1285</v>
       </c>
       <c r="U16" t="n">
-        <v>1638</v>
+        <v>1645</v>
       </c>
       <c r="V16" t="n">
         <v>1452371.99</v>
@@ -12200,7 +12200,7 @@
         <v>44850</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>46119</v>
+        <v>46126</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -12264,10 +12264,10 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="U101" t="n">
-        <v>1270</v>
+        <v>1277</v>
       </c>
       <c r="V101" t="n">
         <v>1365885.84</v>
@@ -24017,7 +24017,7 @@
         <v>44767</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>46217</v>
+        <v>46224</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -24081,10 +24081,10 @@
         <v>0</v>
       </c>
       <c r="T202" t="n">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="U202" t="n">
-        <v>1451</v>
+        <v>1458</v>
       </c>
       <c r="V202" t="n">
         <v>2519553.4</v>
@@ -26819,7 +26819,7 @@
         <v>44810</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>46138</v>
+        <v>46145</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -26883,10 +26883,10 @@
         <v>0</v>
       </c>
       <c r="T226" t="n">
-        <v>1148</v>
+        <v>1155</v>
       </c>
       <c r="U226" t="n">
-        <v>1329</v>
+        <v>1336</v>
       </c>
       <c r="V226" t="n">
         <v>1559477.28</v>
@@ -28457,7 +28457,7 @@
         <v>44579</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>46334</v>
+        <v>46341</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -28521,10 +28521,10 @@
         <v>180</v>
       </c>
       <c r="T240" t="n">
-        <v>1216</v>
+        <v>1223</v>
       </c>
       <c r="U240" t="n">
-        <v>1756</v>
+        <v>1763</v>
       </c>
       <c r="V240" t="n">
         <v>1175120.88</v>
@@ -37097,7 +37097,7 @@
         <v>45384</v>
       </c>
       <c r="F314" s="3" t="n">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -37161,10 +37161,10 @@
         <v>330</v>
       </c>
       <c r="T314" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="U314" t="n">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="V314" t="n">
         <v>2816620.4</v>
@@ -38735,7 +38735,7 @@
         <v>45082</v>
       </c>
       <c r="F328" s="3" t="n">
-        <v>46202</v>
+        <v>46209</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
@@ -38799,10 +38799,10 @@
         <v>0</v>
       </c>
       <c r="T328" t="n">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="U328" t="n">
-        <v>1121</v>
+        <v>1128</v>
       </c>
       <c r="V328" t="n">
         <v>3606475.63</v>
@@ -42479,7 +42479,7 @@
         <v>45236</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>46131</v>
+        <v>46138</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -42543,10 +42543,10 @@
         <v>480</v>
       </c>
       <c r="T360" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="U360" t="n">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="V360" t="n">
         <v>5042730.21</v>
@@ -45170,7 +45170,7 @@
         <v>45237</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>46124</v>
+        <v>46131</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -45234,10 +45234,10 @@
         <v>510</v>
       </c>
       <c r="T383" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="U383" t="n">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="V383" t="n">
         <v>4065559.6</v>
@@ -48791,7 +48791,7 @@
         <v>45386</v>
       </c>
       <c r="F414" s="3" t="n">
-        <v>46123</v>
+        <v>46130</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
@@ -48855,10 +48855,10 @@
         <v>0</v>
       </c>
       <c r="T414" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="U414" t="n">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="V414" t="n">
         <v>65748419.13</v>
@@ -51008,7 +51008,7 @@
         <v>45355</v>
       </c>
       <c r="F433" s="3" t="n">
-        <v>46120</v>
+        <v>46127</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         <v>330</v>
       </c>
       <c r="T433" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="U433" t="n">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="V433" t="n">
         <v>5820891.54</v>
@@ -52763,7 +52763,7 @@
         <v>45722</v>
       </c>
       <c r="F448" s="3" t="n">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
@@ -52827,10 +52827,10 @@
         <v>0</v>
       </c>
       <c r="T448" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="U448" t="n">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="V448" t="n">
         <v>1922644.28</v>
@@ -52959,19 +52959,19 @@
         <v>37153801.63</v>
       </c>
       <c r="Y449" t="n">
-        <v>29264265.66</v>
+        <v>30132401.34</v>
       </c>
       <c r="Z449" t="n">
-        <v>1337201.47</v>
+        <v>1413980.61</v>
       </c>
       <c r="AA449" t="n">
-        <v>30601467.13</v>
+        <v>31546381.95</v>
       </c>
       <c r="AB449" t="n">
-        <v>7889535.97</v>
+        <v>7021400.29</v>
       </c>
       <c r="AC449" t="n">
-        <v>0.7876519865027873</v>
+        <v>0.811017985186998</v>
       </c>
     </row>
     <row r="450">
@@ -53193,19 +53193,19 @@
         <v>33479427.94</v>
       </c>
       <c r="Y451" t="n">
-        <v>18674361.7</v>
+        <v>19221395.57</v>
       </c>
       <c r="Z451" t="n">
-        <v>960635.3100000001</v>
+        <v>1019396.32</v>
       </c>
       <c r="AA451" t="n">
-        <v>19634997.01</v>
+        <v>20240791.89</v>
       </c>
       <c r="AB451" t="n">
-        <v>14805066.24</v>
+        <v>14258032.37</v>
       </c>
       <c r="AC451" t="n">
-        <v>0.5577861644908381</v>
+        <v>0.574125567630592</v>
       </c>
     </row>
     <row r="452">
@@ -56150,7 +56150,7 @@
         <v>45573</v>
       </c>
       <c r="F477" s="3" t="n">
-        <v>46190</v>
+        <v>46197</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
@@ -56214,10 +56214,10 @@
         <v>0</v>
       </c>
       <c r="T477" t="n">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="U477" t="n">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="V477" t="n">
         <v>3876550</v>
@@ -57516,19 +57516,19 @@
         <v>163158631.5</v>
       </c>
       <c r="Y488" t="n">
-        <v>61056495.82</v>
+        <v>63921067.03</v>
       </c>
       <c r="Z488" t="n">
-        <v>2325648.49</v>
+        <v>2481341.16</v>
       </c>
       <c r="AA488" t="n">
-        <v>63382144.31</v>
+        <v>66402408.19</v>
       </c>
       <c r="AB488" t="n">
-        <v>102102135.68</v>
+        <v>99237564.47</v>
       </c>
       <c r="AC488" t="n">
-        <v>0.374215542620557</v>
+        <v>0.391772512691123</v>
       </c>
     </row>
     <row r="489">
@@ -58256,7 +58256,7 @@
         <v>45653</v>
       </c>
       <c r="F495" s="3" t="n">
-        <v>46125</v>
+        <v>46132</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
@@ -58320,10 +58320,10 @@
         <v>0</v>
       </c>
       <c r="T495" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="U495" t="n">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="V495" t="n">
         <v>21305007.22</v>
@@ -61026,19 +61026,19 @@
         <v>44482154.94</v>
       </c>
       <c r="Y518" t="n">
-        <v>6069911.22</v>
+        <v>17027419.71</v>
       </c>
       <c r="Z518" t="n">
-        <v>231447.84</v>
+        <v>515574.38</v>
       </c>
       <c r="AA518" t="n">
-        <v>6301359.06</v>
+        <v>17542994.09</v>
       </c>
       <c r="AB518" t="n">
-        <v>38412243.72</v>
+        <v>27454735.23</v>
       </c>
       <c r="AC518" t="n">
-        <v>0.1364572203884329</v>
+        <v>0.3827921496377037</v>
       </c>
     </row>
     <row r="519">
@@ -64179,19 +64179,19 @@
         <v>53573999.99</v>
       </c>
       <c r="Y545" t="n">
-        <v>5441922.82</v>
+        <v>6093202.3</v>
       </c>
       <c r="Z545" t="n">
-        <v>52013.78</v>
+        <v>63545.71</v>
       </c>
       <c r="AA545" t="n">
-        <v>5493936.6</v>
+        <v>6156748.01</v>
       </c>
       <c r="AB545" t="n">
-        <v>48132077.17</v>
+        <v>47480797.69</v>
       </c>
       <c r="AC545" t="n">
-        <v>0.1015776835968152</v>
+        <v>0.1137343170406791</v>
       </c>
     </row>
     <row r="546">
@@ -66254,7 +66254,7 @@
       </c>
       <c r="Q563" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Ponte Nova, Sericita</t>
+          <t xml:space="preserve"> Obra 1 - Abre Campo, Ponte Nova, Sericita</t>
         </is>
       </c>
       <c r="R563" t="n">
@@ -69734,7 +69734,7 @@
       </c>
       <c r="Q593" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Santa Rita do Itueto</t>
+          <t xml:space="preserve"> Obra 1 - Itueta, Santa Rita do Itueto</t>
         </is>
       </c>
       <c r="R593" t="n">
@@ -70529,7 +70529,7 @@
       </c>
       <c r="Q600" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Belo Horizonte</t>
+          <t xml:space="preserve"> Obra 1 - Abaeté, Bambuí, Belo Horizonte, Bom Sucesso, Brumadinho, Campo Belo, Cláudio, Confins, Contagem, Desterro de Entre Rios, Divinópolis, Ilicínea, Inhaúma, Itabirito, Itapecerica, Itaúna, Jaboticatubas, Lagoa da Prata, Lavras, Luz, Ouro Preto, Pequi, Perdigão, Sarzedo, São Sebastião do Oeste, Vespasiano</t>
         </is>
       </c>
       <c r="R600" t="n">
@@ -70646,7 +70646,7 @@
       </c>
       <c r="Q601" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Belo Horizonte</t>
+          <t xml:space="preserve"> Obra 1 - Aiuruoca, Antônio Carlos, Barbacena, Boa Esperança, Bocaina de Minas, Brazópolis, Cambuí, Campo do Meio, Careaçu, Conceição do Rio Verde, Delfim Moreira, Entre Rios de Minas, Espírito Santo do Dourado, Itajubá, Jesuânia, Lagoa Dourada, Pouso Alegre, Rio Espera, São João Del Rei, São João da Mata, São Tomé das Letras, Três Corações</t>
         </is>
       </c>
       <c r="R601" t="n">
@@ -70689,27 +70689,27 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>PO</t>
+          <t>DO-9493205/2026</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>230190100125</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>SERVIÇOS ESPECIAIS DE APOIO À COORDENAÇÃO E APOIO TÉCNICO NO PLANEJAMENTO, MONITORAMENTO E AVALIAÇÃO DO PORTIFÓLIO DE EMPREENDIMENTOS DO DER-MG</t>
+          <t>PROGRAMA DE CONTROLE DE VELOCIDADE- LOTE 04</t>
         </is>
       </c>
       <c r="D602" s="3" t="n">
-        <v>45589</v>
+        <v>46051</v>
       </c>
       <c r="E602" s="3" t="n">
-        <v>45628</v>
+        <v>46099</v>
       </c>
       <c r="F602" s="3" t="n">
-        <v>46722</v>
+        <v>47013</v>
       </c>
       <c r="G602" t="inlineStr">
         <is>
@@ -70718,12 +70718,12 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYSTRA ENGENHARIA E  CONSULTORIA LTDA </t>
+          <t>FOCALLE - ENGENHARIA VIARIA LTDA.</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>52635422000307</t>
+          <t>09072082000154</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
@@ -70733,7 +70733,7 @@
       </c>
       <c r="K602" t="inlineStr">
         <is>
-          <t>ASSESSORIA DE GESTÃO ESTRATÉGICA</t>
+          <t>DIRETORIA DE OPERACAO VIARIA  DO DER-MG - CAMG</t>
         </is>
       </c>
       <c r="L602" t="inlineStr">
@@ -70748,16 +70748,26 @@
       </c>
       <c r="N602" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Operação-Radar</t>
         </is>
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+          <t>Obra Rodoviária</t>
+        </is>
+      </c>
+      <c r="P602" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 04</t>
+        </is>
+      </c>
+      <c r="Q602" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Bocaiúva, Bonfinópolis de Minas, Buritis, Curvelo, Felixlândia, Francisco Sá, Grão Mogol, Icaraí de Minas, Januária, Japonvar, João Pinheiro, Lagoa dos Patos, Lassance, Mirabela, Monte Azul, Montes Claros, Pedras de Maria da Cruz, Ponto Chique, Porteirinha, Riacho dos Machados, Unaí, Várzea da Palma</t>
         </is>
       </c>
       <c r="R602" t="n">
-        <v>1095</v>
+        <v>915</v>
       </c>
       <c r="S602" t="n">
         <v>0</v>
@@ -70766,16 +70776,16 @@
         <v>0</v>
       </c>
       <c r="U602" t="n">
-        <v>1095</v>
+        <v>915</v>
       </c>
       <c r="V602" t="n">
-        <v>5774752.44</v>
+        <v>31699998.96</v>
       </c>
       <c r="W602" t="n">
         <v>0</v>
       </c>
       <c r="X602" t="n">
-        <v>5774752.44</v>
+        <v>31699998.96</v>
       </c>
       <c r="Y602" t="n">
         <v>0</v>
@@ -70787,7 +70797,7 @@
         <v>0</v>
       </c>
       <c r="AB602" t="n">
-        <v>5774752.44</v>
+        <v>31699998.96</v>
       </c>
       <c r="AC602" t="n">
         <v>0</v>
@@ -70796,35 +70806,41 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>009482014/2025</t>
+          <t>D0-009482032/2025</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>2301901 1/2025</t>
+          <t>Não Disponível</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇO DE ENGENHARIA DE TRANSITO - LOTE 01 </t>
+          <t>PROGRAMA DE CONTROLE DE VELOCIDADE- LOTE 06</t>
         </is>
       </c>
       <c r="D603" s="3" t="n">
-        <v>45974</v>
+        <v>45986</v>
+      </c>
+      <c r="E603" s="3" t="n">
+        <v>46099</v>
+      </c>
+      <c r="F603" s="3" t="n">
+        <v>47013</v>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+          <t>TALENTECH TECNOLOGIA LTDA.</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>16502551000193</t>
+          <t>15773416000110</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
@@ -70834,7 +70850,7 @@
       </c>
       <c r="K603" t="inlineStr">
         <is>
-          <t>GERÊNCIA DE TRÂFEGO E SEGURANÇA VIÁRIA</t>
+          <t>DIRETORIA DE OPERACAO VIARIA  DO DER-MG - CAMG</t>
         </is>
       </c>
       <c r="L603" t="inlineStr">
@@ -70854,11 +70870,21 @@
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t>Natureza continuada e/ou conserva</t>
+          <t>Obra Rodoviária</t>
+        </is>
+      </c>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 06</t>
+        </is>
+      </c>
+      <c r="Q603" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Açucena, Caputira, Cataguases, Dionísio, Dom Silvério, Faria Lemos, Guiricema, Inhapim, Itabira, Muriaé, Mutum, Nova Era, Ouro Preto, Paula Cândido, Piraúba, Raul Soares, Reduto, Rio Piracicaba, Santa Maria de Itabira, São Domingos das Dores, São Geraldo, São Pedro dos Ferros, Tabuleiro, Teixeiras, Viçosa</t>
         </is>
       </c>
       <c r="R603" t="n">
-        <v>0</v>
+        <v>915</v>
       </c>
       <c r="S603" t="n">
         <v>0</v>
@@ -70867,16 +70893,16 @@
         <v>0</v>
       </c>
       <c r="U603" t="n">
-        <v>0</v>
+        <v>915</v>
       </c>
       <c r="V603" t="n">
-        <v>77898894.3</v>
+        <v>35989998.13</v>
       </c>
       <c r="W603" t="n">
         <v>0</v>
       </c>
       <c r="X603" t="n">
-        <v>77898894.3</v>
+        <v>35989998.13</v>
       </c>
       <c r="Y603" t="n">
         <v>0</v>
@@ -70888,7 +70914,7 @@
         <v>0</v>
       </c>
       <c r="AB603" t="n">
-        <v>77898894.3</v>
+        <v>35989998.13</v>
       </c>
       <c r="AC603" t="n">
         <v>0</v>
@@ -70897,106 +70923,665 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
+          <t>DO-9481987/2025</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Não Disponível</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>PROGRAMA DE CONTROLE DE VELOCIDADE</t>
+        </is>
+      </c>
+      <c r="D604" s="3" t="n">
+        <v>45965</v>
+      </c>
+      <c r="E604" s="3" t="n">
+        <v>46098</v>
+      </c>
+      <c r="F604" s="3" t="n">
+        <v>47012</v>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>RAUTAKI TECNOLOGIA LTDA</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>44578594000198</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE OPERACAO VIARIA  DO DER-MG - CAMG</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>Operação-Radar</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária</t>
+        </is>
+      </c>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 07</t>
+        </is>
+      </c>
+      <c r="Q604" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="R604" t="n">
+        <v>915</v>
+      </c>
+      <c r="S604" t="n">
+        <v>0</v>
+      </c>
+      <c r="T604" t="n">
+        <v>0</v>
+      </c>
+      <c r="U604" t="n">
+        <v>915</v>
+      </c>
+      <c r="V604" t="n">
+        <v>23434999.8</v>
+      </c>
+      <c r="W604" t="n">
+        <v>0</v>
+      </c>
+      <c r="X604" t="n">
+        <v>23434999.8</v>
+      </c>
+      <c r="Y604" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z604" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA604" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB604" t="n">
+        <v>23434999.8</v>
+      </c>
+      <c r="AC604" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>DO-009482055/2025</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Não Disponível</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>PROGRAMA DE CONTROLE DE VELOCIDADE- LOTE 05</t>
+        </is>
+      </c>
+      <c r="D605" s="3" t="n">
+        <v>45975</v>
+      </c>
+      <c r="E605" s="3" t="n">
+        <v>46099</v>
+      </c>
+      <c r="F605" s="3" t="n">
+        <v>47013</v>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>DATA TRAFFIC S/A</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>01175068000174</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE OPERACAO VIARIA  DO DER-MG - CAMG</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>Operação-Radar</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária</t>
+        </is>
+      </c>
+      <c r="P605" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 05</t>
+        </is>
+      </c>
+      <c r="Q605" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Araçuaí, Capelinha, Carbonita, Carlos Chagas, Coluna, Conceição do Mato Dentro, Diamantina, Dom Joaquim, Fronteira dos Vales, Fruta de Leite, Gouvea, Governador Valadares, Jacinto, José Gonçalves de Minas, José Raydan, Malacacheta, Mata Verde, Montezuma, Nanuque, Ponto dos Volantes, Rio Pardo de Minas, Salinas, Senhora do Porto, São João do Manteninha, Umburatiba, Virginópolis, Água Boa</t>
+        </is>
+      </c>
+      <c r="R605" t="n">
+        <v>915</v>
+      </c>
+      <c r="S605" t="n">
+        <v>0</v>
+      </c>
+      <c r="T605" t="n">
+        <v>0</v>
+      </c>
+      <c r="U605" t="n">
+        <v>915</v>
+      </c>
+      <c r="V605" t="n">
+        <v>32097999.96</v>
+      </c>
+      <c r="W605" t="n">
+        <v>0</v>
+      </c>
+      <c r="X605" t="n">
+        <v>32097999.96</v>
+      </c>
+      <c r="Y605" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z605" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA605" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB605" t="n">
+        <v>32097999.96</v>
+      </c>
+      <c r="AC605" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>DO-009482017/2025</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Não Disponível</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>PROGRAMA DE CONTROLE DE VELOCIDADE- LOTE 3</t>
+        </is>
+      </c>
+      <c r="D606" s="3" t="n">
+        <v>45968</v>
+      </c>
+      <c r="E606" s="3" t="n">
+        <v>46099</v>
+      </c>
+      <c r="F606" s="3" t="n">
+        <v>47013</v>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>GCT GERENCIAMENTO E CONTROLE DE TRANSITO LTDA</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>01466431000100</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE OPERACAO VIARIA  DO DER-MG - CAMG</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>Operação-Radar</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária</t>
+        </is>
+      </c>
+      <c r="P606" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Serviços de Eng. de Trânsito,de forma contínua,de acordo com as qntds.,especific.técnicas e demais condições expressas no Edital e seus Anexos-Lote 03</t>
+        </is>
+      </c>
+      <c r="Q606" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Abadia dos Dourados, Alpinópolis, Alterosa, Arceburgo, Campina Verde, Capetinga, Conceição da Aparecida, Coromandel, Cássia, Delta, Ibiá, Ituiutaba, Monte Carmelo, Paracatu, Presidente Olegário, Sacramento, Serra do Salitre, Tapira, Uberaba, Uberlândia, Unaí</t>
+        </is>
+      </c>
+      <c r="R606" t="n">
+        <v>915</v>
+      </c>
+      <c r="S606" t="n">
+        <v>0</v>
+      </c>
+      <c r="T606" t="n">
+        <v>0</v>
+      </c>
+      <c r="U606" t="n">
+        <v>915</v>
+      </c>
+      <c r="V606" t="n">
+        <v>47349998.43</v>
+      </c>
+      <c r="W606" t="n">
+        <v>0</v>
+      </c>
+      <c r="X606" t="n">
+        <v>47349998.43</v>
+      </c>
+      <c r="Y606" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z606" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA606" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB606" t="n">
+        <v>47349998.43</v>
+      </c>
+      <c r="AC606" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Não Disponível</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>SERVIÇOS ESPECIAIS DE APOIO À COORDENAÇÃO E APOIO TÉCNICO NO PLANEJAMENTO, MONITORAMENTO E AVALIAÇÃO DO PORTIFÓLIO DE EMPREENDIMENTOS DO DER-MG</t>
+        </is>
+      </c>
+      <c r="D607" s="3" t="n">
+        <v>45589</v>
+      </c>
+      <c r="E607" s="3" t="n">
+        <v>45628</v>
+      </c>
+      <c r="F607" s="3" t="n">
+        <v>46722</v>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYSTRA ENGENHARIA E  CONSULTORIA LTDA </t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>52635422000307</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>ASSESSORIA DE GESTÃO ESTRATÉGICA</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>Consultoria</t>
+        </is>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+        </is>
+      </c>
+      <c r="R607" t="n">
+        <v>1095</v>
+      </c>
+      <c r="S607" t="n">
+        <v>0</v>
+      </c>
+      <c r="T607" t="n">
+        <v>0</v>
+      </c>
+      <c r="U607" t="n">
+        <v>1095</v>
+      </c>
+      <c r="V607" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="W607" t="n">
+        <v>0</v>
+      </c>
+      <c r="X607" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="Y607" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z607" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA607" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB607" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="AC607" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>DO009482014/2025</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>230190100125</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇO DE ENGENHARIA DE TRANSITO - LOTE 01 </t>
+        </is>
+      </c>
+      <c r="D608" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>A Iniciar</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>16502551000193</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>GERÊNCIA DE TRÂFEGO E SEGURANÇA VIÁRIA</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>Operação-Radar</t>
+        </is>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="R608" t="n">
+        <v>0</v>
+      </c>
+      <c r="S608" t="n">
+        <v>0</v>
+      </c>
+      <c r="T608" t="n">
+        <v>0</v>
+      </c>
+      <c r="U608" t="n">
+        <v>0</v>
+      </c>
+      <c r="V608" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="W608" t="n">
+        <v>0</v>
+      </c>
+      <c r="X608" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="Y608" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z608" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA608" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB608" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="AC608" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
           <t>DP-001/2023</t>
         </is>
       </c>
-      <c r="B604" t="inlineStr">
+      <c r="B609" t="inlineStr">
         <is>
           <t>2301601000022020</t>
         </is>
       </c>
-      <c r="C604" t="inlineStr">
+      <c r="C609" t="inlineStr">
         <is>
           <t>ELABORAÇÃO DE PROJETO DE ENGENHARIA RODOVIÁRIA DE MELHORAMENTOS, PAVIMENTAÇÃO E OAE - LOTE 2</t>
         </is>
       </c>
-      <c r="D604" s="3" t="n">
+      <c r="D609" s="3" t="n">
         <v>45166</v>
       </c>
-      <c r="G604" t="inlineStr">
+      <c r="G609" t="inlineStr">
         <is>
           <t>A Iniciar</t>
         </is>
       </c>
-      <c r="H604" t="inlineStr">
+      <c r="H609" t="inlineStr">
         <is>
           <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
-      <c r="I604" t="inlineStr">
+      <c r="I609" t="inlineStr">
         <is>
           <t>38743357000132</t>
         </is>
       </c>
-      <c r="J604" t="inlineStr">
+      <c r="J609" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr">
+      <c r="K609" t="inlineStr">
         <is>
           <t>DIRETORIA DE PROJETOS</t>
         </is>
       </c>
-      <c r="L604" t="inlineStr">
+      <c r="L609" t="inlineStr">
         <is>
           <t>RDC</t>
         </is>
       </c>
-      <c r="M604" t="inlineStr">
+      <c r="M609" t="inlineStr">
         <is>
           <t>EMPREITADA POR PREÇO UNITÁRIO</t>
         </is>
       </c>
-      <c r="N604" t="inlineStr">
+      <c r="N609" t="inlineStr">
         <is>
           <t>Consultoria para Projetos</t>
         </is>
       </c>
-      <c r="O604" t="inlineStr">
+      <c r="O609" t="inlineStr">
         <is>
           <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
         </is>
       </c>
-      <c r="R604" t="n">
-        <v>0</v>
-      </c>
-      <c r="S604" t="n">
-        <v>0</v>
-      </c>
-      <c r="T604" t="n">
-        <v>0</v>
-      </c>
-      <c r="U604" t="n">
-        <v>0</v>
-      </c>
-      <c r="V604" t="n">
+      <c r="R609" t="n">
+        <v>0</v>
+      </c>
+      <c r="S609" t="n">
+        <v>0</v>
+      </c>
+      <c r="T609" t="n">
+        <v>0</v>
+      </c>
+      <c r="U609" t="n">
+        <v>0</v>
+      </c>
+      <c r="V609" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="W604" t="n">
-        <v>0</v>
-      </c>
-      <c r="X604" t="n">
+      <c r="W609" t="n">
+        <v>0</v>
+      </c>
+      <c r="X609" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="Y604" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z604" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA604" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB604" t="n">
+      <c r="Y609" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z609" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA609" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB609" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="AC604" t="n">
+      <c r="AC609" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC604"/>
+  <autoFilter ref="A1:AC609"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/contratos.xlsx
+++ b/upload/contratos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AC$609</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AC$619</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC609"/>
+  <dimension ref="A1:AC619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>EMCONBRAS EMPR CON BRASILEIRA LT</t>
+          <t>EMCONBRÁS EMPRESA DE CONSERVAÇÃO BRASILEIRA LTDA</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2273,7 +2273,7 @@
         <v>44524</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46168</v>
+        <v>46182</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1285</v>
+        <v>1299</v>
       </c>
       <c r="U16" t="n">
-        <v>1645</v>
+        <v>1659</v>
       </c>
       <c r="V16" t="n">
         <v>1452371.99</v>
@@ -9185,7 +9185,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>EMCONBRAS EMPR CON BRASILEIRA LT</t>
+          <t>EMCONBRÁS EMPRESA DE CONSERVAÇÃO BRASILEIRA LTDA</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>EMCONBRAS EMPR CON BRASILEIRA LT</t>
+          <t>EMCONBRÁS EMPRESA DE CONSERVAÇÃO BRASILEIRA LTDA</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -12200,7 +12200,7 @@
         <v>44850</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>46126</v>
+        <v>46140</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -12264,10 +12264,10 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>912</v>
+        <v>926</v>
       </c>
       <c r="U101" t="n">
-        <v>1277</v>
+        <v>1291</v>
       </c>
       <c r="V101" t="n">
         <v>1365885.84</v>
@@ -15906,19 +15906,19 @@
         <v>24865514.03</v>
       </c>
       <c r="Y132" t="n">
-        <v>19863600.32</v>
+        <v>20353151.07</v>
       </c>
       <c r="Z132" t="n">
-        <v>1987435.56</v>
+        <v>2062875.33</v>
       </c>
       <c r="AA132" t="n">
-        <v>21851035.88</v>
+        <v>22416026.4</v>
       </c>
       <c r="AB132" t="n">
-        <v>5001913.71</v>
+        <v>4512362.96</v>
       </c>
       <c r="AC132" t="n">
-        <v>0.7988413308502194</v>
+        <v>0.8185292709189169</v>
       </c>
     </row>
     <row r="133">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>EMCONBRAS EMPR CON BRASILEIRA LT</t>
+          <t>EMCONBRÁS EMPRESA DE CONSERVAÇÃO BRASILEIRA LTDA</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -24017,7 +24017,7 @@
         <v>44767</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>46224</v>
+        <v>46238</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -24081,10 +24081,10 @@
         <v>0</v>
       </c>
       <c r="T202" t="n">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="U202" t="n">
-        <v>1458</v>
+        <v>1472</v>
       </c>
       <c r="V202" t="n">
         <v>2519553.4</v>
@@ -26819,7 +26819,7 @@
         <v>44810</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>46145</v>
+        <v>46159</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -26883,10 +26883,10 @@
         <v>0</v>
       </c>
       <c r="T226" t="n">
-        <v>1155</v>
+        <v>1169</v>
       </c>
       <c r="U226" t="n">
-        <v>1336</v>
+        <v>1350</v>
       </c>
       <c r="V226" t="n">
         <v>1559477.28</v>
@@ -28457,7 +28457,7 @@
         <v>44579</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>46341</v>
+        <v>46355</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -28521,10 +28521,10 @@
         <v>180</v>
       </c>
       <c r="T240" t="n">
-        <v>1223</v>
+        <v>1237</v>
       </c>
       <c r="U240" t="n">
-        <v>1763</v>
+        <v>1777</v>
       </c>
       <c r="V240" t="n">
         <v>1175120.88</v>
@@ -28583,7 +28583,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>EMCONBRAS EMPR CON BRASILEIRA LT</t>
+          <t>EMCONBRÁS EMPRESA DE CONSERVAÇÃO BRASILEIRA LTDA</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -33368,7 +33368,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>EMCONBRAS EMPR CON BRASILEIRA LT</t>
+          <t>EMCONBRÁS EMPRESA DE CONSERVAÇÃO BRASILEIRA LTDA</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -37097,7 +37097,7 @@
         <v>45384</v>
       </c>
       <c r="F314" s="3" t="n">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -37161,10 +37161,10 @@
         <v>330</v>
       </c>
       <c r="T314" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="U314" t="n">
-        <v>756</v>
+        <v>770</v>
       </c>
       <c r="V314" t="n">
         <v>2816620.4</v>
@@ -37176,19 +37176,19 @@
         <v>2923843.86</v>
       </c>
       <c r="Y314" t="n">
-        <v>957623.3199999999</v>
+        <v>1056691.25</v>
       </c>
       <c r="Z314" t="n">
-        <v>363466.8</v>
+        <v>405055.51</v>
       </c>
       <c r="AA314" t="n">
-        <v>1321090.12</v>
+        <v>1461746.76</v>
       </c>
       <c r="AB314" t="n">
-        <v>1966220.54</v>
+        <v>1867152.61</v>
       </c>
       <c r="AC314" t="n">
-        <v>0.3275220449015359</v>
+        <v>0.3614048152352431</v>
       </c>
     </row>
     <row r="315">
@@ -38580,19 +38580,19 @@
         <v>70591515.05</v>
       </c>
       <c r="Y326" t="n">
-        <v>31067942.92</v>
+        <v>31711324.65</v>
       </c>
       <c r="Z326" t="n">
-        <v>1590984.64</v>
+        <v>1632147.35</v>
       </c>
       <c r="AA326" t="n">
-        <v>32658927.56</v>
+        <v>33343472</v>
       </c>
       <c r="AB326" t="n">
-        <v>39523572.13</v>
+        <v>38880190.4</v>
       </c>
       <c r="AC326" t="n">
-        <v>0.4401087425024744</v>
+        <v>0.4492228935381095</v>
       </c>
     </row>
     <row r="327">
@@ -38735,11 +38735,11 @@
         <v>45082</v>
       </c>
       <c r="F328" s="3" t="n">
-        <v>46209</v>
+        <v>46195</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Paralisado</t>
+          <t>Rescindido</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -38799,10 +38799,10 @@
         <v>0</v>
       </c>
       <c r="T328" t="n">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="U328" t="n">
-        <v>1128</v>
+        <v>1114</v>
       </c>
       <c r="V328" t="n">
         <v>3606475.63</v>
@@ -40373,11 +40373,11 @@
         <v>45110</v>
       </c>
       <c r="F342" s="3" t="n">
-        <v>46129</v>
+        <v>46158</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Paralisado</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -40437,10 +40437,10 @@
         <v>398</v>
       </c>
       <c r="T342" t="n">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="U342" t="n">
-        <v>1020</v>
+        <v>1049</v>
       </c>
       <c r="V342" t="n">
         <v>3655796.23</v>
@@ -40452,19 +40452,19 @@
         <v>3655796.23</v>
       </c>
       <c r="Y342" t="n">
-        <v>2018694.35</v>
+        <v>2122647.3</v>
       </c>
       <c r="Z342" t="n">
-        <v>288245.56</v>
+        <v>304264.7</v>
       </c>
       <c r="AA342" t="n">
-        <v>2306939.91</v>
+        <v>2426912</v>
       </c>
       <c r="AB342" t="n">
-        <v>1637101.88</v>
+        <v>1533148.93</v>
       </c>
       <c r="AC342" t="n">
-        <v>0.5521900628471298</v>
+        <v>0.5806251679405009</v>
       </c>
     </row>
     <row r="343">
@@ -41973,19 +41973,19 @@
         <v>3270756.85</v>
       </c>
       <c r="Y355" t="n">
-        <v>725981.9399999999</v>
+        <v>743694.8199999999</v>
       </c>
       <c r="Z355" t="n">
-        <v>75168.59</v>
+        <v>77898.14</v>
       </c>
       <c r="AA355" t="n">
-        <v>801150.53</v>
+        <v>821592.96</v>
       </c>
       <c r="AB355" t="n">
-        <v>2544774.91</v>
+        <v>2527062.03</v>
       </c>
       <c r="AC355" t="n">
-        <v>0.2219614521330132</v>
+        <v>0.2273769815692658</v>
       </c>
     </row>
     <row r="356">
@@ -42479,7 +42479,7 @@
         <v>45236</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>46138</v>
+        <v>46152</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -42543,10 +42543,10 @@
         <v>480</v>
       </c>
       <c r="T360" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="U360" t="n">
-        <v>903</v>
+        <v>917</v>
       </c>
       <c r="V360" t="n">
         <v>5042730.21</v>
@@ -42909,19 +42909,19 @@
         <v>7053152.91</v>
       </c>
       <c r="Y363" t="n">
-        <v>2399454.03</v>
+        <v>2439684.98</v>
       </c>
       <c r="Z363" t="n">
-        <v>277638.16</v>
+        <v>283837.74</v>
       </c>
       <c r="AA363" t="n">
-        <v>2677092.19</v>
+        <v>2723522.72</v>
       </c>
       <c r="AB363" t="n">
-        <v>4653698.88</v>
+        <v>4613467.93</v>
       </c>
       <c r="AC363" t="n">
-        <v>0.3401959464962174</v>
+        <v>0.345899913291402</v>
       </c>
     </row>
     <row r="364">
@@ -43143,19 +43143,19 @@
         <v>6173972.84</v>
       </c>
       <c r="Y365" t="n">
-        <v>2560383.73</v>
+        <v>2784645.93</v>
       </c>
       <c r="Z365" t="n">
-        <v>324015.91</v>
+        <v>358574.71</v>
       </c>
       <c r="AA365" t="n">
-        <v>2884399.64</v>
+        <v>3143220.64</v>
       </c>
       <c r="AB365" t="n">
-        <v>3613589.11</v>
+        <v>3389326.91</v>
       </c>
       <c r="AC365" t="n">
-        <v>0.4147060242007802</v>
+        <v>0.4510298315468456</v>
       </c>
     </row>
     <row r="366">
@@ -43260,19 +43260,19 @@
         <v>4004374.41</v>
       </c>
       <c r="Y366" t="n">
-        <v>178536.39</v>
+        <v>226431.45</v>
       </c>
       <c r="Z366" t="n">
-        <v>27512.43</v>
+        <v>34893.05</v>
       </c>
       <c r="AA366" t="n">
-        <v>206048.82</v>
+        <v>261324.5</v>
       </c>
       <c r="AB366" t="n">
-        <v>3825838.02</v>
+        <v>3777942.96</v>
       </c>
       <c r="AC366" t="n">
-        <v>0.04458533886195722</v>
+        <v>0.05654602362719624</v>
       </c>
     </row>
     <row r="367">
@@ -43611,19 +43611,19 @@
         <v>6324008.13</v>
       </c>
       <c r="Y369" t="n">
-        <v>1518978.78</v>
+        <v>1593439.12</v>
       </c>
       <c r="Z369" t="n">
-        <v>157690.12</v>
+        <v>169164.45</v>
       </c>
       <c r="AA369" t="n">
-        <v>1676668.9</v>
+        <v>1762603.57</v>
       </c>
       <c r="AB369" t="n">
-        <v>4805029.35</v>
+        <v>4730569.01</v>
       </c>
       <c r="AC369" t="n">
-        <v>0.2401924141738888</v>
+        <v>0.2519666463490141</v>
       </c>
     </row>
     <row r="370">
@@ -43728,19 +43728,19 @@
         <v>8240827.41</v>
       </c>
       <c r="Y370" t="n">
-        <v>1507542.69</v>
+        <v>1603853.4</v>
       </c>
       <c r="Z370" t="n">
-        <v>175162.04</v>
+        <v>190003.52</v>
       </c>
       <c r="AA370" t="n">
-        <v>1682704.73</v>
+        <v>1793856.92</v>
       </c>
       <c r="AB370" t="n">
-        <v>6733284.72</v>
+        <v>6636974.01</v>
       </c>
       <c r="AC370" t="n">
-        <v>0.1829358406621454</v>
+        <v>0.194622860084871</v>
       </c>
     </row>
     <row r="371">
@@ -44430,19 +44430,19 @@
         <v>9807936.460000001</v>
       </c>
       <c r="Y376" t="n">
-        <v>5043747.34</v>
+        <v>8514031.869999999</v>
       </c>
       <c r="Z376" t="n">
-        <v>203448.59</v>
+        <v>552492.78</v>
       </c>
       <c r="AA376" t="n">
-        <v>5247195.93</v>
+        <v>9066524.65</v>
       </c>
       <c r="AB376" t="n">
-        <v>4764189.12</v>
+        <v>1293904.59</v>
       </c>
       <c r="AC376" t="n">
-        <v>0.5142516329066839</v>
+        <v>0.868075757293395</v>
       </c>
     </row>
     <row r="377">
@@ -45015,19 +45015,19 @@
         <v>7576922.1</v>
       </c>
       <c r="Y381" t="n">
-        <v>4097169.68</v>
+        <v>4239229.08</v>
       </c>
       <c r="Z381" t="n">
-        <v>403537.68</v>
+        <v>423752.72</v>
       </c>
       <c r="AA381" t="n">
-        <v>4500707.36</v>
+        <v>4662981.8</v>
       </c>
       <c r="AB381" t="n">
-        <v>3479752.42</v>
+        <v>3337693.02</v>
       </c>
       <c r="AC381" t="n">
-        <v>0.5407432762176609</v>
+        <v>0.5594922349802171</v>
       </c>
     </row>
     <row r="382">
@@ -45170,7 +45170,7 @@
         <v>45237</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>46131</v>
+        <v>46145</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -45234,10 +45234,10 @@
         <v>510</v>
       </c>
       <c r="T383" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="U383" t="n">
-        <v>895</v>
+        <v>909</v>
       </c>
       <c r="V383" t="n">
         <v>4065559.6</v>
@@ -45249,19 +45249,19 @@
         <v>4065559.6</v>
       </c>
       <c r="Y383" t="n">
-        <v>1266033.65</v>
+        <v>1318964.23</v>
       </c>
       <c r="Z383" t="n">
-        <v>143681.45</v>
+        <v>151838.04</v>
       </c>
       <c r="AA383" t="n">
-        <v>1409715.1</v>
+        <v>1470802.27</v>
       </c>
       <c r="AB383" t="n">
-        <v>2799525.95</v>
+        <v>2746595.37</v>
       </c>
       <c r="AC383" t="n">
-        <v>0.3114045235002827</v>
+        <v>0.3244237841206411</v>
       </c>
     </row>
     <row r="384">
@@ -47396,7 +47396,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>EMCONBRAS EMPR CON BRASILEIRA LT</t>
+          <t>EMCONBRÁS EMPRESA DE CONSERVAÇÃO BRASILEIRA LTDA</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -48210,7 +48210,7 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -48285,19 +48285,19 @@
         <v>33128884.09</v>
       </c>
       <c r="Y409" t="n">
-        <v>29938521.01</v>
+        <v>30703508.45</v>
       </c>
       <c r="Z409" t="n">
-        <v>1905593.01</v>
+        <v>1985017.74</v>
       </c>
       <c r="AA409" t="n">
-        <v>31844114.02</v>
+        <v>32688526.19</v>
       </c>
       <c r="AB409" t="n">
-        <v>3190363.08</v>
+        <v>2425375.64</v>
       </c>
       <c r="AC409" t="n">
-        <v>0.9036984441935062</v>
+        <v>0.9267896970688456</v>
       </c>
     </row>
     <row r="410">
@@ -48791,11 +48791,11 @@
         <v>45386</v>
       </c>
       <c r="F414" s="3" t="n">
-        <v>46130</v>
+        <v>46311</v>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Paralisado</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -48852,13 +48852,13 @@
         <v>720</v>
       </c>
       <c r="S414" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="T414" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U414" t="n">
-        <v>745</v>
+        <v>926</v>
       </c>
       <c r="V414" t="n">
         <v>65748419.13</v>
@@ -48870,19 +48870,19 @@
         <v>75282924.23</v>
       </c>
       <c r="Y414" t="n">
-        <v>49530165.98</v>
+        <v>50964371.23</v>
       </c>
       <c r="Z414" t="n">
-        <v>2871590.78</v>
+        <v>2994474.72</v>
       </c>
       <c r="AA414" t="n">
-        <v>52401756.76</v>
+        <v>53958845.95</v>
       </c>
       <c r="AB414" t="n">
-        <v>25752758.25</v>
+        <v>24318553</v>
       </c>
       <c r="AC414" t="n">
-        <v>0.6579203250484575</v>
+        <v>0.6769711956764143</v>
       </c>
     </row>
     <row r="415">
@@ -48987,19 +48987,19 @@
         <v>33826877.05</v>
       </c>
       <c r="Y415" t="n">
-        <v>28979164.65</v>
+        <v>29210734.29</v>
       </c>
       <c r="Z415" t="n">
-        <v>1329854.23</v>
+        <v>1346526.87</v>
       </c>
       <c r="AA415" t="n">
-        <v>30309018.88</v>
+        <v>30557261.16</v>
       </c>
       <c r="AB415" t="n">
-        <v>4847712.4</v>
+        <v>4616142.76</v>
       </c>
       <c r="AC415" t="n">
-        <v>0.8566905129068071</v>
+        <v>0.8635362421078123</v>
       </c>
     </row>
     <row r="416">
@@ -50502,19 +50502,19 @@
         <v>38819029.96</v>
       </c>
       <c r="Y428" t="n">
-        <v>33638673.8</v>
+        <v>34740432.66</v>
       </c>
       <c r="Z428" t="n">
-        <v>2021305.47</v>
+        <v>2122047.18</v>
       </c>
       <c r="AA428" t="n">
-        <v>35659979.27</v>
+        <v>36862479.84</v>
       </c>
       <c r="AB428" t="n">
-        <v>5180356.16</v>
+        <v>4078597.3</v>
       </c>
       <c r="AC428" t="n">
-        <v>0.8665511177034059</v>
+        <v>0.8949330443289624</v>
       </c>
     </row>
     <row r="429">
@@ -50544,7 +50544,7 @@
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -50661,7 +50661,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -50778,7 +50778,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -50970,19 +50970,19 @@
         <v>1425000</v>
       </c>
       <c r="Y432" t="n">
-        <v>1004477.76</v>
+        <v>1051152.96</v>
       </c>
       <c r="Z432" t="n">
-        <v>56210.2</v>
+        <v>60859.04</v>
       </c>
       <c r="AA432" t="n">
-        <v>1060687.96</v>
+        <v>1112012</v>
       </c>
       <c r="AB432" t="n">
-        <v>420522.24</v>
+        <v>373847.04</v>
       </c>
       <c r="AC432" t="n">
-        <v>0.7048966736842105</v>
+        <v>0.7376512</v>
       </c>
     </row>
     <row r="433">
@@ -51008,7 +51008,7 @@
         <v>45355</v>
       </c>
       <c r="F433" s="3" t="n">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
@@ -51072,10 +51072,10 @@
         <v>330</v>
       </c>
       <c r="T433" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="U433" t="n">
-        <v>773</v>
+        <v>787</v>
       </c>
       <c r="V433" t="n">
         <v>5820891.54</v>
@@ -51129,7 +51129,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -51204,19 +51204,19 @@
         <v>797999.85</v>
       </c>
       <c r="Y434" t="n">
-        <v>391292.63</v>
+        <v>400277.37</v>
       </c>
       <c r="Z434" t="n">
-        <v>26931.97</v>
+        <v>27793.59</v>
       </c>
       <c r="AA434" t="n">
-        <v>418224.6</v>
+        <v>428070.96</v>
       </c>
       <c r="AB434" t="n">
-        <v>406707.22</v>
+        <v>397722.48</v>
       </c>
       <c r="AC434" t="n">
-        <v>0.4903417337735089</v>
+        <v>0.5016008085715805</v>
       </c>
     </row>
     <row r="435">
@@ -51246,7 +51246,7 @@
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -51438,19 +51438,19 @@
         <v>28096598.89</v>
       </c>
       <c r="Y436" t="n">
-        <v>26154150.05</v>
+        <v>26999282.29</v>
       </c>
       <c r="Z436" t="n">
-        <v>1298454.05</v>
+        <v>1385505.74</v>
       </c>
       <c r="AA436" t="n">
-        <v>27452604.1</v>
+        <v>28384788.03</v>
       </c>
       <c r="AB436" t="n">
-        <v>1942448.84</v>
+        <v>1097316.6</v>
       </c>
       <c r="AC436" t="n">
-        <v>0.9308653389826714</v>
+        <v>0.9609448601129245</v>
       </c>
     </row>
     <row r="437">
@@ -51480,7 +51480,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -51672,19 +51672,19 @@
         <v>31994041.87</v>
       </c>
       <c r="Y438" t="n">
-        <v>28815897.11</v>
+        <v>29342447.39</v>
       </c>
       <c r="Z438" t="n">
-        <v>1776195.35</v>
+        <v>1839385.71</v>
       </c>
       <c r="AA438" t="n">
-        <v>30592092.46</v>
+        <v>31181833.1</v>
       </c>
       <c r="AB438" t="n">
-        <v>3178144.76</v>
+        <v>2651594.48</v>
       </c>
       <c r="AC438" t="n">
-        <v>0.9006644808144711</v>
+        <v>0.9171222413606225</v>
       </c>
     </row>
     <row r="439">
@@ -51906,19 +51906,19 @@
         <v>41801980.63</v>
       </c>
       <c r="Y440" t="n">
-        <v>36859439.52</v>
+        <v>37778568.04</v>
       </c>
       <c r="Z440" t="n">
-        <v>2588739.03</v>
+        <v>2690060.18</v>
       </c>
       <c r="AA440" t="n">
-        <v>39448178.55</v>
+        <v>40468628.22</v>
       </c>
       <c r="AB440" t="n">
-        <v>4942541.11</v>
+        <v>4023412.59</v>
       </c>
       <c r="AC440" t="n">
-        <v>0.8817629921953294</v>
+        <v>0.9037506709164752</v>
       </c>
     </row>
     <row r="441">
@@ -52023,19 +52023,19 @@
         <v>29715772.52</v>
       </c>
       <c r="Y441" t="n">
-        <v>23090287.3</v>
+        <v>23439872.67</v>
       </c>
       <c r="Z441" t="n">
-        <v>1177613.07</v>
+        <v>1224383.25</v>
       </c>
       <c r="AA441" t="n">
-        <v>24267900.37</v>
+        <v>24664255.92</v>
       </c>
       <c r="AB441" t="n">
-        <v>6625485.22</v>
+        <v>6275899.85</v>
       </c>
       <c r="AC441" t="n">
-        <v>0.7770380959963009</v>
+        <v>0.7888023996086237</v>
       </c>
     </row>
     <row r="442">
@@ -52140,19 +52140,19 @@
         <v>30648355.12</v>
       </c>
       <c r="Y442" t="n">
-        <v>16551136.84</v>
+        <v>17173368.49</v>
       </c>
       <c r="Z442" t="n">
-        <v>1112171.11</v>
+        <v>1180122.02</v>
       </c>
       <c r="AA442" t="n">
-        <v>17663307.95</v>
+        <v>18353490.51</v>
       </c>
       <c r="AB442" t="n">
-        <v>14097218.28</v>
+        <v>13474986.63</v>
       </c>
       <c r="AC442" t="n">
-        <v>0.5400334463365485</v>
+        <v>0.5603357316488834</v>
       </c>
     </row>
     <row r="443">
@@ -52763,7 +52763,7 @@
         <v>45722</v>
       </c>
       <c r="F448" s="3" t="n">
-        <v>46134</v>
+        <v>46148</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
@@ -52827,10 +52827,10 @@
         <v>0</v>
       </c>
       <c r="T448" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="U448" t="n">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="V448" t="n">
         <v>1922644.28</v>
@@ -53076,19 +53076,19 @@
         <v>37310856.76</v>
       </c>
       <c r="Y450" t="n">
-        <v>29934224.39</v>
+        <v>30828416.26</v>
       </c>
       <c r="Z450" t="n">
-        <v>1561880.22</v>
+        <v>1645889.91</v>
       </c>
       <c r="AA450" t="n">
-        <v>31496104.61</v>
+        <v>32474306.17</v>
       </c>
       <c r="AB450" t="n">
-        <v>7376632.37</v>
+        <v>6482440.5</v>
       </c>
       <c r="AC450" t="n">
-        <v>0.8022926029962331</v>
+        <v>0.8262585996966531</v>
       </c>
     </row>
     <row r="451">
@@ -53544,19 +53544,19 @@
         <v>32023158.45</v>
       </c>
       <c r="Y454" t="n">
-        <v>26705330.6</v>
+        <v>27938707.57</v>
       </c>
       <c r="Z454" t="n">
-        <v>1191342.54</v>
+        <v>1300896.83</v>
       </c>
       <c r="AA454" t="n">
-        <v>27896673.14</v>
+        <v>29239604.4</v>
       </c>
       <c r="AB454" t="n">
-        <v>5317827.85</v>
+        <v>4084450.88</v>
       </c>
       <c r="AC454" t="n">
-        <v>0.8339380589736926</v>
+        <v>0.8724532158070123</v>
       </c>
     </row>
     <row r="455">
@@ -53661,19 +53661,19 @@
         <v>33721624.27</v>
       </c>
       <c r="Y455" t="n">
-        <v>17120516.56</v>
+        <v>17654827.84</v>
       </c>
       <c r="Z455" t="n">
-        <v>972473.9</v>
+        <v>1026710.9</v>
       </c>
       <c r="AA455" t="n">
-        <v>18092990.46</v>
+        <v>18681538.74</v>
       </c>
       <c r="AB455" t="n">
-        <v>16601107.71</v>
+        <v>16066796.43</v>
       </c>
       <c r="AC455" t="n">
-        <v>0.5077014209908934</v>
+        <v>0.5235461880081022</v>
       </c>
     </row>
     <row r="456">
@@ -54012,19 +54012,19 @@
         <v>42788655.89</v>
       </c>
       <c r="Y458" t="n">
-        <v>26817950.04</v>
+        <v>27461062.39</v>
       </c>
       <c r="Z458" t="n">
-        <v>1413131.04</v>
+        <v>1481599.91</v>
       </c>
       <c r="AA458" t="n">
-        <v>28231081.08</v>
+        <v>28942662.3</v>
       </c>
       <c r="AB458" t="n">
-        <v>15970705.85</v>
+        <v>15327593.5</v>
       </c>
       <c r="AC458" t="n">
-        <v>0.6267537383960579</v>
+        <v>0.6417837115658928</v>
       </c>
     </row>
     <row r="459">
@@ -54129,19 +54129,19 @@
         <v>34984519.25</v>
       </c>
       <c r="Y459" t="n">
-        <v>29104302.64</v>
+        <v>30596587.45</v>
       </c>
       <c r="Z459" t="n">
-        <v>1506627.07</v>
+        <v>1638048.83</v>
       </c>
       <c r="AA459" t="n">
-        <v>30610929.71</v>
+        <v>32234636.28</v>
       </c>
       <c r="AB459" t="n">
-        <v>5880216.61</v>
+        <v>4387931.8</v>
       </c>
       <c r="AC459" t="n">
-        <v>0.8319194679229442</v>
+        <v>0.874575043645912</v>
       </c>
     </row>
     <row r="460">
@@ -54480,19 +54480,19 @@
         <v>50256753.54</v>
       </c>
       <c r="Y462" t="n">
-        <v>40609650.97</v>
+        <v>41981889.57</v>
       </c>
       <c r="Z462" t="n">
-        <v>1467687.93</v>
+        <v>1522076.2</v>
       </c>
       <c r="AA462" t="n">
-        <v>42077338.9</v>
+        <v>43503965.77</v>
       </c>
       <c r="AB462" t="n">
-        <v>9647102.57</v>
+        <v>8274863.97</v>
       </c>
       <c r="AC462" t="n">
-        <v>0.8080436580066449</v>
+        <v>0.8353482191520005</v>
       </c>
     </row>
     <row r="463">
@@ -54948,19 +54948,19 @@
         <v>47634588.04</v>
       </c>
       <c r="Y466" t="n">
-        <v>25655505.35</v>
+        <v>26881215.87</v>
       </c>
       <c r="Z466" t="n">
-        <v>1123267.81</v>
+        <v>1223574.14</v>
       </c>
       <c r="AA466" t="n">
-        <v>26778773.16</v>
+        <v>28104790.01</v>
       </c>
       <c r="AB466" t="n">
-        <v>21979082.69</v>
+        <v>20753372.17</v>
       </c>
       <c r="AC466" t="n">
-        <v>0.5385898441791164</v>
+        <v>0.5643213676462814</v>
       </c>
     </row>
     <row r="467">
@@ -55065,19 +55065,19 @@
         <v>52604103.19</v>
       </c>
       <c r="Y467" t="n">
-        <v>31955189.39</v>
+        <v>33806452.17</v>
       </c>
       <c r="Z467" t="n">
-        <v>1394191.19</v>
+        <v>1522593.9</v>
       </c>
       <c r="AA467" t="n">
-        <v>33349380.58</v>
+        <v>35329046.07</v>
       </c>
       <c r="AB467" t="n">
-        <v>20648913.8</v>
+        <v>18797651.02</v>
       </c>
       <c r="AC467" t="n">
-        <v>0.6074657194436243</v>
+        <v>0.6426580840641835</v>
       </c>
     </row>
     <row r="468">
@@ -55182,19 +55182,19 @@
         <v>45768946.45</v>
       </c>
       <c r="Y468" t="n">
-        <v>18109441.46</v>
+        <v>20394072.15</v>
       </c>
       <c r="Z468" t="n">
-        <v>822203.95</v>
+        <v>967683.63</v>
       </c>
       <c r="AA468" t="n">
-        <v>18931645.41</v>
+        <v>21361755.78</v>
       </c>
       <c r="AB468" t="n">
-        <v>27659504.99</v>
+        <v>25374874.3</v>
       </c>
       <c r="AC468" t="n">
-        <v>0.3956709267883967</v>
+        <v>0.4455875376611383</v>
       </c>
     </row>
     <row r="469">
@@ -55299,19 +55299,19 @@
         <v>46337191.41</v>
       </c>
       <c r="Y469" t="n">
-        <v>29530146.27</v>
+        <v>29856106.57</v>
       </c>
       <c r="Z469" t="n">
-        <v>1334902.9</v>
+        <v>1357169.26</v>
       </c>
       <c r="AA469" t="n">
-        <v>30865049.17</v>
+        <v>31213275.83</v>
       </c>
       <c r="AB469" t="n">
-        <v>16807045.14</v>
+        <v>16481084.84</v>
       </c>
       <c r="AC469" t="n">
-        <v>0.6372882207881748</v>
+        <v>0.6443227494266468</v>
       </c>
     </row>
     <row r="470">
@@ -55416,19 +55416,19 @@
         <v>49131721.25</v>
       </c>
       <c r="Y470" t="n">
-        <v>24194469.19</v>
+        <v>25075761.49</v>
       </c>
       <c r="Z470" t="n">
-        <v>919247.1</v>
+        <v>984837.09</v>
       </c>
       <c r="AA470" t="n">
-        <v>25113716.29</v>
+        <v>26060598.58</v>
       </c>
       <c r="AB470" t="n">
-        <v>24937252.06</v>
+        <v>24055959.76</v>
       </c>
       <c r="AC470" t="n">
-        <v>0.4924409032382516</v>
+        <v>0.5103782414299194</v>
       </c>
     </row>
     <row r="471">
@@ -55533,19 +55533,19 @@
         <v>51333755.33</v>
       </c>
       <c r="Y471" t="n">
-        <v>21600091.6</v>
+        <v>23304932.85</v>
       </c>
       <c r="Z471" t="n">
-        <v>1130458.87</v>
+        <v>1252057.26</v>
       </c>
       <c r="AA471" t="n">
-        <v>22730550.47</v>
+        <v>24556990.11</v>
       </c>
       <c r="AB471" t="n">
-        <v>29733663.73</v>
+        <v>28028822.48</v>
       </c>
       <c r="AC471" t="n">
-        <v>0.4207775461028209</v>
+        <v>0.4539884662671532</v>
       </c>
     </row>
     <row r="472">
@@ -55650,19 +55650,19 @@
         <v>47758833.23</v>
       </c>
       <c r="Y472" t="n">
-        <v>27758013.78</v>
+        <v>29365376.04</v>
       </c>
       <c r="Z472" t="n">
-        <v>1159437.88</v>
+        <v>1263434.93</v>
       </c>
       <c r="AA472" t="n">
-        <v>28917451.66</v>
+        <v>30628810.97</v>
       </c>
       <c r="AB472" t="n">
-        <v>20000819.45</v>
+        <v>18393457.19</v>
       </c>
       <c r="AC472" t="n">
-        <v>0.5812121423972233</v>
+        <v>0.6148679532973591</v>
       </c>
     </row>
     <row r="473">
@@ -55884,19 +55884,19 @@
         <v>47005570.55</v>
       </c>
       <c r="Y474" t="n">
-        <v>23005707.02</v>
+        <v>23528643.71</v>
       </c>
       <c r="Z474" t="n">
-        <v>1065585.4</v>
+        <v>1104146.56</v>
       </c>
       <c r="AA474" t="n">
-        <v>24071292.42</v>
+        <v>24632790.27</v>
       </c>
       <c r="AB474" t="n">
-        <v>23999863.53</v>
+        <v>23476926.84</v>
       </c>
       <c r="AC474" t="n">
-        <v>0.4894251202743884</v>
+        <v>0.5005501142672546</v>
       </c>
     </row>
     <row r="475">
@@ -56001,19 +56001,19 @@
         <v>50062054.28</v>
       </c>
       <c r="Y475" t="n">
-        <v>24152609.14</v>
+        <v>26145936.44</v>
       </c>
       <c r="Z475" t="n">
-        <v>1146491.71</v>
+        <v>1281115.95</v>
       </c>
       <c r="AA475" t="n">
-        <v>25299100.85</v>
+        <v>27427052.39</v>
       </c>
       <c r="AB475" t="n">
-        <v>25909445.14</v>
+        <v>23916117.84</v>
       </c>
       <c r="AC475" t="n">
-        <v>0.4824534168117242</v>
+        <v>0.5222705463456263</v>
       </c>
     </row>
     <row r="476">
@@ -56150,7 +56150,7 @@
         <v>45573</v>
       </c>
       <c r="F477" s="3" t="n">
-        <v>46197</v>
+        <v>46211</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
@@ -56214,10 +56214,10 @@
         <v>0</v>
       </c>
       <c r="T477" t="n">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="U477" t="n">
-        <v>625</v>
+        <v>639</v>
       </c>
       <c r="V477" t="n">
         <v>3876550</v>
@@ -56346,19 +56346,19 @@
         <v>859769.01</v>
       </c>
       <c r="Y478" t="n">
-        <v>584820.63</v>
+        <v>688450.6899999999</v>
       </c>
       <c r="Z478" t="n">
-        <v>18452.61</v>
+        <v>26141.96</v>
       </c>
       <c r="AA478" t="n">
-        <v>603273.24</v>
+        <v>714592.65</v>
       </c>
       <c r="AB478" t="n">
-        <v>274948.38</v>
+        <v>171318.32</v>
       </c>
       <c r="AC478" t="n">
-        <v>0.6802066871426314</v>
+        <v>0.8007391310835918</v>
       </c>
     </row>
     <row r="479">
@@ -56622,7 +56622,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -56697,19 +56697,19 @@
         <v>13735008.46</v>
       </c>
       <c r="Y481" t="n">
-        <v>12277111.63</v>
+        <v>12437651.25</v>
       </c>
       <c r="Z481" t="n">
-        <v>827898.05</v>
+        <v>845771.1899999999</v>
       </c>
       <c r="AA481" t="n">
-        <v>13105009.68</v>
+        <v>13283422.44</v>
       </c>
       <c r="AB481" t="n">
-        <v>1457896.83</v>
+        <v>1297357.21</v>
       </c>
       <c r="AC481" t="n">
-        <v>0.8938554108469766</v>
+        <v>0.9055437633126875</v>
       </c>
     </row>
     <row r="482">
@@ -56814,19 +56814,19 @@
         <v>1484780.82</v>
       </c>
       <c r="Y482" t="n">
-        <v>759251.79</v>
+        <v>923251.2</v>
       </c>
       <c r="Z482" t="n">
-        <v>26700.76</v>
+        <v>38869.51</v>
       </c>
       <c r="AA482" t="n">
-        <v>785952.55</v>
+        <v>962120.71</v>
       </c>
       <c r="AB482" t="n">
-        <v>725529.03</v>
+        <v>561529.62</v>
       </c>
       <c r="AC482" t="n">
-        <v>0.5113561407669585</v>
+        <v>0.6218097564056626</v>
       </c>
     </row>
     <row r="483">
@@ -56931,19 +56931,19 @@
         <v>7278955.82</v>
       </c>
       <c r="Y483" t="n">
-        <v>4675593.17</v>
+        <v>4953180.67</v>
       </c>
       <c r="Z483" t="n">
         <v>0</v>
       </c>
       <c r="AA483" t="n">
-        <v>4675593.17</v>
+        <v>4953180.67</v>
       </c>
       <c r="AB483" t="n">
-        <v>2603362.65</v>
+        <v>2325775.15</v>
       </c>
       <c r="AC483" t="n">
-        <v>0.6423439413044824</v>
+        <v>0.6804795622457838</v>
       </c>
     </row>
     <row r="484">
@@ -57399,19 +57399,19 @@
         <v>24308955.5</v>
       </c>
       <c r="Y487" t="n">
-        <v>13284295.25</v>
+        <v>15133680.75</v>
       </c>
       <c r="Z487" t="n">
-        <v>74469.48</v>
+        <v>170125.57</v>
       </c>
       <c r="AA487" t="n">
-        <v>13358764.73</v>
+        <v>15303806.32</v>
       </c>
       <c r="AB487" t="n">
-        <v>11024660.25</v>
+        <v>9175274.75</v>
       </c>
       <c r="AC487" t="n">
-        <v>0.546477418579338</v>
+        <v>0.622555779905887</v>
       </c>
     </row>
     <row r="488">
@@ -58256,11 +58256,11 @@
         <v>45653</v>
       </c>
       <c r="F495" s="3" t="n">
-        <v>46132</v>
+        <v>46138</v>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>Paralisado</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -58320,10 +58320,10 @@
         <v>0</v>
       </c>
       <c r="T495" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="U495" t="n">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="V495" t="n">
         <v>21305007.22</v>
@@ -58865,7 +58865,7 @@
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>DIRETORIA DE MANUTENCAO</t>
+          <t>DIRETORIA DE OPERAÇÕES</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
@@ -58920,19 +58920,19 @@
         <v>4917800.43</v>
       </c>
       <c r="Y500" t="n">
-        <v>0</v>
+        <v>208430.57</v>
       </c>
       <c r="Z500" t="n">
-        <v>0</v>
+        <v>10175.13</v>
       </c>
       <c r="AA500" t="n">
-        <v>0</v>
+        <v>218605.7</v>
       </c>
       <c r="AB500" t="n">
-        <v>4917800.43</v>
+        <v>4709369.86</v>
       </c>
       <c r="AC500" t="n">
-        <v>0</v>
+        <v>0.04238288498421234</v>
       </c>
     </row>
     <row r="501">
@@ -59154,19 +59154,19 @@
         <v>5774752.44</v>
       </c>
       <c r="Y502" t="n">
-        <v>1744569.6</v>
+        <v>1912436.46</v>
       </c>
       <c r="Z502" t="n">
-        <v>66890.25999999999</v>
+        <v>77533.00999999999</v>
       </c>
       <c r="AA502" t="n">
-        <v>1811459.86</v>
+        <v>1989969.47</v>
       </c>
       <c r="AB502" t="n">
-        <v>4030182.84</v>
+        <v>3862315.98</v>
       </c>
       <c r="AC502" t="n">
-        <v>0.3021029244328957</v>
+        <v>0.3311720250989668</v>
       </c>
     </row>
     <row r="503">
@@ -59435,7 +59435,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>EMCONBRAS EMPR CON BRASILEIRA LT</t>
+          <t>EMCONBRÁS EMPRESA DE CONSERVAÇÃO BRASILEIRA LTDA</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -59622,19 +59622,19 @@
         <v>2540551.02</v>
       </c>
       <c r="Y506" t="n">
-        <v>117040.09</v>
+        <v>129788.89</v>
       </c>
       <c r="Z506" t="n">
-        <v>5015.29</v>
+        <v>5961.25</v>
       </c>
       <c r="AA506" t="n">
-        <v>122055.38</v>
+        <v>135750.14</v>
       </c>
       <c r="AB506" t="n">
-        <v>2423510.93</v>
+        <v>2410762.13</v>
       </c>
       <c r="AC506" t="n">
-        <v>0.04606878156692165</v>
+        <v>0.05108690554854513</v>
       </c>
     </row>
     <row r="507">
@@ -60090,19 +60090,19 @@
         <v>39334571.99</v>
       </c>
       <c r="Y510" t="n">
-        <v>8620630.609999999</v>
+        <v>10734557.59</v>
       </c>
       <c r="Z510" t="n">
-        <v>251344.61</v>
+        <v>315285.64</v>
       </c>
       <c r="AA510" t="n">
-        <v>8871975.220000001</v>
+        <v>11049843.23</v>
       </c>
       <c r="AB510" t="n">
-        <v>30713941.38</v>
+        <v>28600014.4</v>
       </c>
       <c r="AC510" t="n">
-        <v>0.2191616731508256</v>
+        <v>0.2729038870113812</v>
       </c>
     </row>
     <row r="511">
@@ -60207,19 +60207,19 @@
         <v>924684.42</v>
       </c>
       <c r="Y511" t="n">
-        <v>647541.22</v>
+        <v>664376.46</v>
       </c>
       <c r="Z511" t="n">
-        <v>28643.38</v>
+        <v>29892.55</v>
       </c>
       <c r="AA511" t="n">
-        <v>676184.6</v>
+        <v>694269.01</v>
       </c>
       <c r="AB511" t="n">
-        <v>277143.2</v>
+        <v>260307.96</v>
       </c>
       <c r="AC511" t="n">
-        <v>0.7002834761723357</v>
+        <v>0.7184899470891918</v>
       </c>
     </row>
     <row r="512">
@@ -60324,19 +60324,19 @@
         <v>31648004.35</v>
       </c>
       <c r="Y512" t="n">
-        <v>27179395.08</v>
+        <v>27221408.52</v>
       </c>
       <c r="Z512" t="n">
-        <v>334304.68</v>
+        <v>335837.84</v>
       </c>
       <c r="AA512" t="n">
-        <v>27513699.76</v>
+        <v>27557246.36</v>
       </c>
       <c r="AB512" t="n">
-        <v>4468609.27</v>
+        <v>4426595.83</v>
       </c>
       <c r="AC512" t="n">
-        <v>0.8588028104211254</v>
+        <v>0.8601303329889108</v>
       </c>
     </row>
     <row r="513">
@@ -60441,19 +60441,19 @@
         <v>7109673.15</v>
       </c>
       <c r="Y513" t="n">
-        <v>0</v>
+        <v>134831.17</v>
       </c>
       <c r="Z513" t="n">
-        <v>0</v>
+        <v>4696.72</v>
       </c>
       <c r="AA513" t="n">
-        <v>0</v>
+        <v>139527.89</v>
       </c>
       <c r="AB513" t="n">
-        <v>7109673.15</v>
+        <v>6974841.98</v>
       </c>
       <c r="AC513" t="n">
-        <v>0</v>
+        <v>0.01896446814858149</v>
       </c>
     </row>
     <row r="514">
@@ -60558,19 +60558,19 @@
         <v>9659997.08</v>
       </c>
       <c r="Y514" t="n">
-        <v>153335</v>
+        <v>206968.35</v>
       </c>
       <c r="Z514" t="n">
-        <v>14183.47</v>
+        <v>19144.55</v>
       </c>
       <c r="AA514" t="n">
-        <v>167518.47</v>
+        <v>226112.9</v>
       </c>
       <c r="AB514" t="n">
-        <v>9506662.08</v>
+        <v>9453028.73</v>
       </c>
       <c r="AC514" t="n">
-        <v>0.01587319320390519</v>
+        <v>0.02142530150744103</v>
       </c>
     </row>
     <row r="515">
@@ -60792,19 +60792,19 @@
         <v>8415499.810000001</v>
       </c>
       <c r="Y516" t="n">
-        <v>2407110.85</v>
+        <v>2984135.57</v>
       </c>
       <c r="Z516" t="n">
-        <v>82826.58</v>
+        <v>105011.73</v>
       </c>
       <c r="AA516" t="n">
-        <v>2489937.43</v>
+        <v>3089147.3</v>
       </c>
       <c r="AB516" t="n">
-        <v>6008388.96</v>
+        <v>5431364.24</v>
       </c>
       <c r="AC516" t="n">
-        <v>0.2860330229156051</v>
+        <v>0.3545999212612423</v>
       </c>
     </row>
     <row r="517">
@@ -61064,7 +61064,7 @@
         <v>45756</v>
       </c>
       <c r="F519" s="3" t="n">
-        <v>46151</v>
+        <v>46305</v>
       </c>
       <c r="G519" t="inlineStr">
         <is>
@@ -61125,13 +61125,13 @@
         <v>365</v>
       </c>
       <c r="S519" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="T519" t="n">
         <v>31</v>
       </c>
       <c r="U519" t="n">
-        <v>396</v>
+        <v>550</v>
       </c>
       <c r="V519" t="n">
         <v>803371.39</v>
@@ -61143,19 +61143,19 @@
         <v>803371.39</v>
       </c>
       <c r="Y519" t="n">
-        <v>263096.11</v>
+        <v>307553.14</v>
       </c>
       <c r="Z519" t="n">
-        <v>10984.67</v>
+        <v>13149.72</v>
       </c>
       <c r="AA519" t="n">
-        <v>274080.78</v>
+        <v>320702.86</v>
       </c>
       <c r="AB519" t="n">
-        <v>540275.28</v>
+        <v>495818.25</v>
       </c>
       <c r="AC519" t="n">
-        <v>0.3274900167903664</v>
+        <v>0.3828280964797613</v>
       </c>
     </row>
     <row r="520">
@@ -61260,19 +61260,19 @@
         <v>29576179.41</v>
       </c>
       <c r="Y520" t="n">
-        <v>1039591.93</v>
+        <v>1373835.81</v>
       </c>
       <c r="Z520" t="n">
-        <v>60971.02</v>
+        <v>73245.00999999999</v>
       </c>
       <c r="AA520" t="n">
-        <v>1100562.95</v>
+        <v>1447080.82</v>
       </c>
       <c r="AB520" t="n">
-        <v>28536587.48</v>
+        <v>28202343.6</v>
       </c>
       <c r="AC520" t="n">
-        <v>0.03514963564389603</v>
+        <v>0.04645075318739419</v>
       </c>
     </row>
     <row r="521">
@@ -61494,19 +61494,19 @@
         <v>11569905.95</v>
       </c>
       <c r="Y522" t="n">
-        <v>6145327.29</v>
+        <v>6271540.57</v>
       </c>
       <c r="Z522" t="n">
-        <v>186278.45</v>
+        <v>190178.79</v>
       </c>
       <c r="AA522" t="n">
-        <v>6331605.74</v>
+        <v>6461719.36</v>
       </c>
       <c r="AB522" t="n">
-        <v>5424578.66</v>
+        <v>5298365.38</v>
       </c>
       <c r="AC522" t="n">
-        <v>0.5311475578589298</v>
+        <v>0.5420563137766906</v>
       </c>
     </row>
     <row r="523">
@@ -61728,19 +61728,19 @@
         <v>28955069.4</v>
       </c>
       <c r="Y524" t="n">
-        <v>14314001.61</v>
+        <v>14841369.03</v>
       </c>
       <c r="Z524" t="n">
-        <v>337730.55</v>
+        <v>351155.7</v>
       </c>
       <c r="AA524" t="n">
-        <v>14651732.16</v>
+        <v>15192524.73</v>
       </c>
       <c r="AB524" t="n">
-        <v>14641067.79</v>
+        <v>14113700.37</v>
       </c>
       <c r="AC524" t="n">
-        <v>0.4943521775844889</v>
+        <v>0.5125654794666111</v>
       </c>
     </row>
     <row r="525">
@@ -62313,19 +62313,19 @@
         <v>3900717.4</v>
       </c>
       <c r="Y529" t="n">
-        <v>1587630.07</v>
+        <v>1798925.05</v>
       </c>
       <c r="Z529" t="n">
-        <v>810167.5699999999</v>
+        <v>917991.39</v>
       </c>
       <c r="AA529" t="n">
-        <v>2397797.64</v>
+        <v>2716916.44</v>
       </c>
       <c r="AB529" t="n">
-        <v>2313087.33</v>
+        <v>2101792.35</v>
       </c>
       <c r="AC529" t="n">
-        <v>0.4070097644089777</v>
+        <v>0.4611780002314446</v>
       </c>
     </row>
     <row r="530">
@@ -62664,19 +62664,19 @@
         <v>9147934.25</v>
       </c>
       <c r="Y532" t="n">
-        <v>1566140.15</v>
+        <v>1867887.53</v>
       </c>
       <c r="Z532" t="n">
-        <v>34789.89</v>
+        <v>45682.96</v>
       </c>
       <c r="AA532" t="n">
-        <v>1600930.04</v>
+        <v>1913570.49</v>
       </c>
       <c r="AB532" t="n">
-        <v>7581794.1</v>
+        <v>7280046.72</v>
       </c>
       <c r="AC532" t="n">
-        <v>0.1712015092369078</v>
+        <v>0.2041868119023702</v>
       </c>
     </row>
     <row r="533">
@@ -63009,19 +63009,19 @@
         <v>49093539.45</v>
       </c>
       <c r="Y535" t="n">
-        <v>4634384.99</v>
+        <v>5181810.35</v>
       </c>
       <c r="Z535" t="n">
-        <v>33669.31</v>
+        <v>41982.04</v>
       </c>
       <c r="AA535" t="n">
-        <v>4668054.3</v>
+        <v>5223792.39</v>
       </c>
       <c r="AB535" t="n">
-        <v>44459154.46</v>
+        <v>43911729.1</v>
       </c>
       <c r="AC535" t="n">
-        <v>0.09439908065133405</v>
+        <v>0.1055497405168248</v>
       </c>
     </row>
     <row r="536">
@@ -63126,19 +63126,19 @@
         <v>9522992.289999999</v>
       </c>
       <c r="Y536" t="n">
-        <v>2703721.53</v>
+        <v>2955353.01</v>
       </c>
       <c r="Z536" t="n">
-        <v>43602.39</v>
+        <v>51034.6</v>
       </c>
       <c r="AA536" t="n">
-        <v>2747323.92</v>
+        <v>3006387.61</v>
       </c>
       <c r="AB536" t="n">
-        <v>6819270.76</v>
+        <v>6567639.28</v>
       </c>
       <c r="AC536" t="n">
-        <v>0.2839151232789668</v>
+        <v>0.3103386960738577</v>
       </c>
     </row>
     <row r="537">
@@ -63243,19 +63243,19 @@
         <v>44573000</v>
       </c>
       <c r="Y537" t="n">
-        <v>4087799.31</v>
+        <v>4670098.83</v>
       </c>
       <c r="Z537" t="n">
-        <v>50292.73</v>
+        <v>66649.77</v>
       </c>
       <c r="AA537" t="n">
-        <v>4138092.04</v>
+        <v>4736748.6</v>
       </c>
       <c r="AB537" t="n">
-        <v>40485200.69</v>
+        <v>39902901.17</v>
       </c>
       <c r="AC537" t="n">
-        <v>0.09171021268480919</v>
+        <v>0.1047741644044601</v>
       </c>
     </row>
     <row r="538">
@@ -63360,19 +63360,19 @@
         <v>51814575.44</v>
       </c>
       <c r="Y538" t="n">
-        <v>5982264.67</v>
+        <v>6832001.61</v>
       </c>
       <c r="Z538" t="n">
-        <v>74117.67999999999</v>
+        <v>97809.87</v>
       </c>
       <c r="AA538" t="n">
-        <v>6056382.35</v>
+        <v>6929811.48</v>
       </c>
       <c r="AB538" t="n">
-        <v>45832310.77</v>
+        <v>44982573.83</v>
       </c>
       <c r="AC538" t="n">
-        <v>0.1154552482424046</v>
+        <v>0.1318548217752221</v>
       </c>
     </row>
     <row r="539">
@@ -63477,19 +63477,19 @@
         <v>50960749.38</v>
       </c>
       <c r="Y539" t="n">
-        <v>5226168.65</v>
+        <v>5881370.48</v>
       </c>
       <c r="Z539" t="n">
-        <v>39243.01</v>
+        <v>49202.31</v>
       </c>
       <c r="AA539" t="n">
-        <v>5265411.66</v>
+        <v>5930572.79</v>
       </c>
       <c r="AB539" t="n">
-        <v>45734580.73</v>
+        <v>45079378.9</v>
       </c>
       <c r="AC539" t="n">
-        <v>0.1025528218007535</v>
+        <v>0.1154098115030505</v>
       </c>
     </row>
     <row r="540">
@@ -63594,19 +63594,19 @@
         <v>22458906.7</v>
       </c>
       <c r="Y540" t="n">
-        <v>1152827.26</v>
+        <v>1487538.65</v>
       </c>
       <c r="Z540" t="n">
-        <v>23447.85</v>
+        <v>35530.91</v>
       </c>
       <c r="AA540" t="n">
-        <v>1176275.11</v>
+        <v>1523069.56</v>
       </c>
       <c r="AB540" t="n">
-        <v>21306079.44</v>
+        <v>20971368.05</v>
       </c>
       <c r="AC540" t="n">
-        <v>0.05133051556779476</v>
+        <v>0.06623379623372316</v>
       </c>
     </row>
     <row r="541">
@@ -63711,19 +63711,19 @@
         <v>30872072.3</v>
       </c>
       <c r="Y541" t="n">
-        <v>3148412.06</v>
+        <v>3733445.15</v>
       </c>
       <c r="Z541" t="n">
-        <v>69280.47</v>
+        <v>90400.14999999999</v>
       </c>
       <c r="AA541" t="n">
-        <v>3217692.53</v>
+        <v>3823845.3</v>
       </c>
       <c r="AB541" t="n">
-        <v>27723660.24</v>
+        <v>27138627.15</v>
       </c>
       <c r="AC541" t="n">
-        <v>0.1019825306641304</v>
+        <v>0.1209327677688809</v>
       </c>
     </row>
     <row r="542">
@@ -63828,19 +63828,19 @@
         <v>53356791.72</v>
       </c>
       <c r="Y542" t="n">
-        <v>8108338.48</v>
+        <v>9603132.49</v>
       </c>
       <c r="Z542" t="n">
-        <v>107589.5</v>
+        <v>146432.54</v>
       </c>
       <c r="AA542" t="n">
-        <v>8215927.98</v>
+        <v>9749565.029999999</v>
       </c>
       <c r="AB542" t="n">
-        <v>45248453.24</v>
+        <v>43753659.23</v>
       </c>
       <c r="AC542" t="n">
-        <v>0.1519645057099771</v>
+        <v>0.1799795711180365</v>
       </c>
     </row>
     <row r="543">
@@ -63945,19 +63945,19 @@
         <v>53241874.38</v>
       </c>
       <c r="Y543" t="n">
-        <v>10278516.91</v>
+        <v>11593843.28</v>
       </c>
       <c r="Z543" t="n">
-        <v>103589.31</v>
+        <v>129819.98</v>
       </c>
       <c r="AA543" t="n">
-        <v>10382106.22</v>
+        <v>11723663.26</v>
       </c>
       <c r="AB543" t="n">
-        <v>42963357.47</v>
+        <v>41648031.1</v>
       </c>
       <c r="AC543" t="n">
-        <v>0.1930532504667241</v>
+        <v>0.2177579849509423</v>
       </c>
     </row>
     <row r="544">
@@ -64062,19 +64062,19 @@
         <v>59299394.97</v>
       </c>
       <c r="Y544" t="n">
-        <v>22747695.41</v>
+        <v>24082394.71</v>
       </c>
       <c r="Z544" t="n">
-        <v>197398.65</v>
+        <v>225294.14</v>
       </c>
       <c r="AA544" t="n">
-        <v>22945094.06</v>
+        <v>24307688.85</v>
       </c>
       <c r="AB544" t="n">
-        <v>36551699.56</v>
+        <v>35217000.26</v>
       </c>
       <c r="AC544" t="n">
-        <v>0.3836075464430662</v>
+        <v>0.4061153528157153</v>
       </c>
     </row>
     <row r="545">
@@ -64407,19 +64407,19 @@
         <v>1655673.22</v>
       </c>
       <c r="Y547" t="n">
-        <v>261385</v>
+        <v>375709.28</v>
       </c>
       <c r="Z547" t="n">
-        <v>4014.01</v>
+        <v>8141.11</v>
       </c>
       <c r="AA547" t="n">
-        <v>265399.01</v>
+        <v>383850.39</v>
       </c>
       <c r="AB547" t="n">
-        <v>1394288.22</v>
+        <v>1279963.94</v>
       </c>
       <c r="AC547" t="n">
-        <v>0.1578723366679809</v>
+        <v>0.2269223633393068</v>
       </c>
     </row>
     <row r="548">
@@ -64524,19 +64524,19 @@
         <v>5978999.99</v>
       </c>
       <c r="Y548" t="n">
-        <v>2550950.75</v>
+        <v>3278560.72</v>
       </c>
       <c r="Z548" t="n">
-        <v>2027.55</v>
+        <v>1944.54</v>
       </c>
       <c r="AA548" t="n">
-        <v>2552978.3</v>
+        <v>3280505.26</v>
       </c>
       <c r="AB548" t="n">
-        <v>3428049.24</v>
+        <v>2700439.27</v>
       </c>
       <c r="AC548" t="n">
-        <v>0.4266517401348917</v>
+        <v>0.5483459985755912</v>
       </c>
     </row>
     <row r="549">
@@ -64641,19 +64641,19 @@
         <v>9284408.859999999</v>
       </c>
       <c r="Y549" t="n">
-        <v>1295218.13</v>
+        <v>1544810.85</v>
       </c>
       <c r="Z549" t="n">
-        <v>32866.19</v>
+        <v>41876.47</v>
       </c>
       <c r="AA549" t="n">
-        <v>1328084.32</v>
+        <v>1586687.32</v>
       </c>
       <c r="AB549" t="n">
-        <v>7989190.73</v>
+        <v>7739598.01</v>
       </c>
       <c r="AC549" t="n">
-        <v>0.1395046415480673</v>
+        <v>0.1663876368753541</v>
       </c>
     </row>
     <row r="550">
@@ -64992,19 +64992,19 @@
         <v>9218472.49</v>
       </c>
       <c r="Y552" t="n">
-        <v>829896.92</v>
+        <v>1041486.75</v>
       </c>
       <c r="Z552" t="n">
-        <v>25417.53</v>
+        <v>33055.91</v>
       </c>
       <c r="AA552" t="n">
-        <v>855314.45</v>
+        <v>1074542.66</v>
       </c>
       <c r="AB552" t="n">
-        <v>8388575.57</v>
+        <v>8176985.74</v>
       </c>
       <c r="AC552" t="n">
-        <v>0.09002542676134839</v>
+        <v>0.1129782348572155</v>
       </c>
     </row>
     <row r="553">
@@ -65109,19 +65109,19 @@
         <v>21429526.4</v>
       </c>
       <c r="Y553" t="n">
-        <v>2490585.68</v>
+        <v>2750527.43</v>
       </c>
       <c r="Z553" t="n">
         <v>0</v>
       </c>
       <c r="AA553" t="n">
-        <v>2490585.68</v>
+        <v>2750527.43</v>
       </c>
       <c r="AB553" t="n">
-        <v>18938940.72</v>
+        <v>18678998.97</v>
       </c>
       <c r="AC553" t="n">
-        <v>0.1162221522543774</v>
+        <v>0.1283522266735675</v>
       </c>
     </row>
     <row r="554">
@@ -65226,19 +65226,19 @@
         <v>9634126.24</v>
       </c>
       <c r="Y554" t="n">
-        <v>3808666.66</v>
+        <v>4736694.87</v>
       </c>
       <c r="Z554" t="n">
-        <v>68016.03999999999</v>
+        <v>90981.28999999999</v>
       </c>
       <c r="AA554" t="n">
-        <v>3876682.7</v>
+        <v>4827676.16</v>
       </c>
       <c r="AB554" t="n">
-        <v>5825459.58</v>
+        <v>4897431.37</v>
       </c>
       <c r="AC554" t="n">
-        <v>0.3953307819640943</v>
+        <v>0.4916579617084195</v>
       </c>
     </row>
     <row r="555">
@@ -65343,19 +65343,19 @@
         <v>7056321.74</v>
       </c>
       <c r="Y555" t="n">
-        <v>457787.93</v>
+        <v>474633.67</v>
       </c>
       <c r="Z555" t="n">
-        <v>12448.02</v>
+        <v>13056.15</v>
       </c>
       <c r="AA555" t="n">
-        <v>470235.95</v>
+        <v>487689.82</v>
       </c>
       <c r="AB555" t="n">
-        <v>6598533.81</v>
+        <v>6581688.07</v>
       </c>
       <c r="AC555" t="n">
-        <v>0.06487628354656062</v>
+        <v>0.06726360949635497</v>
       </c>
     </row>
     <row r="556">
@@ -65460,19 +65460,19 @@
         <v>2401689.3</v>
       </c>
       <c r="Y556" t="n">
-        <v>764724.91</v>
+        <v>1355674.86</v>
       </c>
       <c r="Z556" t="n">
         <v>0</v>
       </c>
       <c r="AA556" t="n">
-        <v>764724.91</v>
+        <v>1355674.86</v>
       </c>
       <c r="AB556" t="n">
-        <v>1636964.39</v>
+        <v>1046014.44</v>
       </c>
       <c r="AC556" t="n">
-        <v>0.3184112574428341</v>
+        <v>0.5644672106421093</v>
       </c>
     </row>
     <row r="557">
@@ -65577,19 +65577,19 @@
         <v>14619000</v>
       </c>
       <c r="Y557" t="n">
-        <v>2398334.49</v>
+        <v>4429527.64</v>
       </c>
       <c r="Z557" t="n">
-        <v>8420.889999999999</v>
+        <v>20772.43</v>
       </c>
       <c r="AA557" t="n">
-        <v>2406755.38</v>
+        <v>4450300.07</v>
       </c>
       <c r="AB557" t="n">
-        <v>12220665.51</v>
+        <v>10189472.36</v>
       </c>
       <c r="AC557" t="n">
-        <v>0.1640559880976811</v>
+        <v>0.3029979916546959</v>
       </c>
     </row>
     <row r="558">
@@ -65694,19 +65694,19 @@
         <v>9410345.890000001</v>
       </c>
       <c r="Y558" t="n">
-        <v>816218.0699999999</v>
+        <v>1006178.54</v>
       </c>
       <c r="Z558" t="n">
-        <v>22458.58</v>
+        <v>29316.14</v>
       </c>
       <c r="AA558" t="n">
-        <v>838676.65</v>
+        <v>1035494.68</v>
       </c>
       <c r="AB558" t="n">
-        <v>8594127.82</v>
+        <v>8404167.35</v>
       </c>
       <c r="AC558" t="n">
-        <v>0.08673624535601422</v>
+        <v>0.1069225883683219</v>
       </c>
     </row>
     <row r="559">
@@ -65811,19 +65811,19 @@
         <v>9200787.869999999</v>
       </c>
       <c r="Y559" t="n">
-        <v>1133906.65</v>
+        <v>1400596.05</v>
       </c>
       <c r="Z559" t="n">
-        <v>31496.39</v>
+        <v>41123.86</v>
       </c>
       <c r="AA559" t="n">
-        <v>1165403.04</v>
+        <v>1441719.91</v>
       </c>
       <c r="AB559" t="n">
-        <v>8066881.22</v>
+        <v>7800191.82</v>
       </c>
       <c r="AC559" t="n">
-        <v>0.1232401687791548</v>
+        <v>0.1522256647788577</v>
       </c>
     </row>
     <row r="560">
@@ -65928,19 +65928,19 @@
         <v>2086583.52</v>
       </c>
       <c r="Y560" t="n">
-        <v>120945.94</v>
+        <v>152799.08</v>
       </c>
       <c r="Z560" t="n">
-        <v>7631.67</v>
+        <v>9641.6</v>
       </c>
       <c r="AA560" t="n">
-        <v>128577.61</v>
+        <v>162440.68</v>
       </c>
       <c r="AB560" t="n">
-        <v>1965637.58</v>
+        <v>1933784.44</v>
       </c>
       <c r="AC560" t="n">
-        <v>0.05796362275496166</v>
+        <v>0.07322931410864397</v>
       </c>
     </row>
     <row r="561">
@@ -66162,19 +66162,19 @@
         <v>21860486.4</v>
       </c>
       <c r="Y562" t="n">
-        <v>2841863.22</v>
+        <v>3570546.1</v>
       </c>
       <c r="Z562" t="n">
-        <v>23244.98</v>
+        <v>46489.96</v>
       </c>
       <c r="AA562" t="n">
-        <v>2865108.2</v>
+        <v>3617036.06</v>
       </c>
       <c r="AB562" t="n">
-        <v>19018623.18</v>
+        <v>18289940.3</v>
       </c>
       <c r="AC562" t="n">
-        <v>0.1299999994510644</v>
+        <v>0.1633333327843977</v>
       </c>
     </row>
     <row r="563">
@@ -66279,19 +66279,19 @@
         <v>6199729.76</v>
       </c>
       <c r="Y563" t="n">
-        <v>0</v>
+        <v>289152.96</v>
       </c>
       <c r="Z563" t="n">
         <v>0</v>
       </c>
       <c r="AA563" t="n">
-        <v>0</v>
+        <v>289152.96</v>
       </c>
       <c r="AB563" t="n">
-        <v>6199729.76</v>
+        <v>5910576.8</v>
       </c>
       <c r="AC563" t="n">
-        <v>0</v>
+        <v>0.04663960707861563</v>
       </c>
     </row>
     <row r="564">
@@ -66371,7 +66371,7 @@
       </c>
       <c r="Q564" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Ponte Nova, Santa Cruz do Escalvado</t>
+          <t xml:space="preserve"> Obra 1 - Ponte Nova, Santa Cruz do Escalvado, Urucânia</t>
         </is>
       </c>
       <c r="R564" t="n">
@@ -66396,19 +66396,19 @@
         <v>10929975.56</v>
       </c>
       <c r="Y564" t="n">
-        <v>0</v>
+        <v>405673.71</v>
       </c>
       <c r="Z564" t="n">
         <v>0</v>
       </c>
       <c r="AA564" t="n">
-        <v>0</v>
+        <v>405673.71</v>
       </c>
       <c r="AB564" t="n">
-        <v>10929975.56</v>
+        <v>10524301.85</v>
       </c>
       <c r="AC564" t="n">
-        <v>0</v>
+        <v>0.03711570147371857</v>
       </c>
     </row>
     <row r="565">
@@ -66630,19 +66630,19 @@
         <v>41984578.11</v>
       </c>
       <c r="Y566" t="n">
-        <v>0</v>
+        <v>3794113.75</v>
       </c>
       <c r="Z566" t="n">
         <v>0</v>
       </c>
       <c r="AA566" t="n">
-        <v>0</v>
+        <v>3794113.75</v>
       </c>
       <c r="AB566" t="n">
-        <v>41984578.11</v>
+        <v>38190464.36</v>
       </c>
       <c r="AC566" t="n">
-        <v>0</v>
+        <v>0.09036922414843339</v>
       </c>
     </row>
     <row r="567">
@@ -66747,19 +66747,19 @@
         <v>27994383.03</v>
       </c>
       <c r="Y567" t="n">
-        <v>1555732.35</v>
+        <v>2365248.99</v>
       </c>
       <c r="Z567" t="n">
-        <v>331506.92</v>
+        <v>504016.44</v>
       </c>
       <c r="AA567" t="n">
-        <v>1887239.27</v>
+        <v>2869265.43</v>
       </c>
       <c r="AB567" t="n">
-        <v>26438650.68</v>
+        <v>25629134.04</v>
       </c>
       <c r="AC567" t="n">
-        <v>0.05557301792766104</v>
+        <v>0.08449012744682732</v>
       </c>
     </row>
     <row r="568">
@@ -66864,19 +66864,19 @@
         <v>12159273.83</v>
       </c>
       <c r="Y568" t="n">
-        <v>2524796.62</v>
+        <v>3823205.97</v>
       </c>
       <c r="Z568" t="n">
-        <v>189478.08</v>
+        <v>313522.25</v>
       </c>
       <c r="AA568" t="n">
-        <v>2714274.7</v>
+        <v>4136728.22</v>
       </c>
       <c r="AB568" t="n">
-        <v>9634477.210000001</v>
+        <v>8336067.86</v>
       </c>
       <c r="AC568" t="n">
-        <v>0.2076437010383539</v>
+        <v>0.3144271626293328</v>
       </c>
     </row>
     <row r="569">
@@ -66981,19 +66981,19 @@
         <v>2624909.09</v>
       </c>
       <c r="Y569" t="n">
-        <v>155585.6</v>
+        <v>258309.25</v>
       </c>
       <c r="Z569" t="n">
-        <v>3067.68</v>
+        <v>6344.56</v>
       </c>
       <c r="AA569" t="n">
-        <v>158653.28</v>
+        <v>264653.81</v>
       </c>
       <c r="AB569" t="n">
-        <v>2469323.49</v>
+        <v>2366599.84</v>
       </c>
       <c r="AC569" t="n">
-        <v>0.05927275751862324</v>
+        <v>0.09840693187587689</v>
       </c>
     </row>
     <row r="570">
@@ -67098,19 +67098,19 @@
         <v>12585961.98</v>
       </c>
       <c r="Y570" t="n">
-        <v>792234.27</v>
+        <v>1511276.19</v>
       </c>
       <c r="Z570" t="n">
-        <v>71680.64</v>
+        <v>138325.23</v>
       </c>
       <c r="AA570" t="n">
-        <v>863914.91</v>
+        <v>1649601.42</v>
       </c>
       <c r="AB570" t="n">
-        <v>11793727.71</v>
+        <v>11074685.79</v>
       </c>
       <c r="AC570" t="n">
-        <v>0.06294586550149422</v>
+        <v>0.1200763352377456</v>
       </c>
     </row>
     <row r="571">
@@ -67332,19 +67332,19 @@
         <v>12403029.87</v>
       </c>
       <c r="Y572" t="n">
-        <v>896838.3100000001</v>
+        <v>1614142.18</v>
       </c>
       <c r="Z572" t="n">
-        <v>69963.45</v>
+        <v>134082.77</v>
       </c>
       <c r="AA572" t="n">
-        <v>966801.76</v>
+        <v>1748224.95</v>
       </c>
       <c r="AB572" t="n">
-        <v>11506191.56</v>
+        <v>10788887.69</v>
       </c>
       <c r="AC572" t="n">
-        <v>0.07230800210916528</v>
+        <v>0.1301409572433772</v>
       </c>
     </row>
     <row r="573">
@@ -67449,19 +67449,19 @@
         <v>14704896.91</v>
       </c>
       <c r="Y573" t="n">
-        <v>805855.4399999999</v>
+        <v>1937021.67</v>
       </c>
       <c r="Z573" t="n">
-        <v>73274.23</v>
+        <v>213905.91</v>
       </c>
       <c r="AA573" t="n">
-        <v>879129.67</v>
+        <v>2150927.58</v>
       </c>
       <c r="AB573" t="n">
-        <v>13899041.47</v>
+        <v>12767875.24</v>
       </c>
       <c r="AC573" t="n">
-        <v>0.05480184219802191</v>
+        <v>0.1317263005552074</v>
       </c>
     </row>
     <row r="574">
@@ -67566,19 +67566,19 @@
         <v>14929346.95</v>
       </c>
       <c r="Y574" t="n">
-        <v>551298.7</v>
+        <v>833120.1899999999</v>
       </c>
       <c r="Z574" t="n">
-        <v>118361.5</v>
+        <v>178892.04</v>
       </c>
       <c r="AA574" t="n">
-        <v>669660.2</v>
+        <v>1012012.23</v>
       </c>
       <c r="AB574" t="n">
-        <v>14378048.25</v>
+        <v>14096226.76</v>
       </c>
       <c r="AC574" t="n">
-        <v>0.0369271811986391</v>
+        <v>0.05580419510580133</v>
       </c>
     </row>
     <row r="575">
@@ -67717,9 +67717,15 @@
       <c r="D576" s="3" t="n">
         <v>45933</v>
       </c>
+      <c r="E576" s="3" t="n">
+        <v>46125</v>
+      </c>
+      <c r="F576" s="3" t="n">
+        <v>46724</v>
+      </c>
       <c r="G576" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H576" t="inlineStr">
@@ -67773,7 +67779,7 @@
         </is>
       </c>
       <c r="R576" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="S576" t="n">
         <v>0</v>
@@ -67782,7 +67788,7 @@
         <v>0</v>
       </c>
       <c r="U576" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="V576" t="n">
         <v>57467603.75</v>
@@ -68145,19 +68151,19 @@
         <v>20125000</v>
       </c>
       <c r="Y579" t="n">
-        <v>0</v>
+        <v>865117.08</v>
       </c>
       <c r="Z579" t="n">
-        <v>0</v>
+        <v>36023.22</v>
       </c>
       <c r="AA579" t="n">
-        <v>0</v>
+        <v>901140.3</v>
       </c>
       <c r="AB579" t="n">
-        <v>20125000</v>
+        <v>19259882.92</v>
       </c>
       <c r="AC579" t="n">
-        <v>0</v>
+        <v>0.04298718409937888</v>
       </c>
     </row>
     <row r="580">
@@ -68262,19 +68268,19 @@
         <v>59889999.58</v>
       </c>
       <c r="Y580" t="n">
-        <v>0</v>
+        <v>897085.83</v>
       </c>
       <c r="Z580" t="n">
-        <v>0</v>
+        <v>47341.54</v>
       </c>
       <c r="AA580" t="n">
-        <v>0</v>
+        <v>944427.37</v>
       </c>
       <c r="AB580" t="n">
-        <v>59889999.58</v>
+        <v>58992913.75</v>
       </c>
       <c r="AC580" t="n">
-        <v>0</v>
+        <v>0.01497889190668116</v>
       </c>
     </row>
     <row r="581">
@@ -68379,19 +68385,19 @@
         <v>64984305.34</v>
       </c>
       <c r="Y581" t="n">
-        <v>1000383.75</v>
+        <v>2647093.02</v>
       </c>
       <c r="Z581" t="n">
-        <v>34560.42</v>
+        <v>76958.82000000001</v>
       </c>
       <c r="AA581" t="n">
-        <v>1034944.17</v>
+        <v>2724051.84</v>
       </c>
       <c r="AB581" t="n">
-        <v>63983921.59</v>
+        <v>62337212.32</v>
       </c>
       <c r="AC581" t="n">
-        <v>0.01539423626621782</v>
+        <v>0.04073434356419328</v>
       </c>
     </row>
     <row r="582">
@@ -68426,7 +68432,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>EMCONBRAS EMPR CON BRASILEIRA LT</t>
+          <t>EMCONBRÁS EMPRESA DE CONSERVAÇÃO BRASILEIRA LTDA</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -68496,19 +68502,19 @@
         <v>15304996.19</v>
       </c>
       <c r="Y582" t="n">
-        <v>593834.61</v>
+        <v>1636050.93</v>
       </c>
       <c r="Z582" t="n">
-        <v>72067.83</v>
+        <v>184473.31</v>
       </c>
       <c r="AA582" t="n">
-        <v>665902.4399999999</v>
+        <v>1820524.24</v>
       </c>
       <c r="AB582" t="n">
-        <v>14711161.58</v>
+        <v>13668945.26</v>
       </c>
       <c r="AC582" t="n">
-        <v>0.03880004951507277</v>
+        <v>0.1068965264472895</v>
       </c>
     </row>
     <row r="583">
@@ -69069,19 +69075,19 @@
         <v>13190992.89</v>
       </c>
       <c r="Y587" t="n">
-        <v>592401.33</v>
+        <v>1124617.17</v>
       </c>
       <c r="Z587" t="n">
-        <v>71211.28999999999</v>
+        <v>126675.2</v>
       </c>
       <c r="AA587" t="n">
-        <v>663612.62</v>
+        <v>1251292.37</v>
       </c>
       <c r="AB587" t="n">
-        <v>12598591.56</v>
+        <v>12066375.72</v>
       </c>
       <c r="AC587" t="n">
-        <v>0.04490953296238188</v>
+        <v>0.08525644577161166</v>
       </c>
     </row>
     <row r="588">
@@ -69303,19 +69309,19 @@
         <v>14398046.07</v>
       </c>
       <c r="Y589" t="n">
-        <v>318583.52</v>
+        <v>647838.1</v>
       </c>
       <c r="Z589" t="n">
-        <v>30598.96</v>
+        <v>75894.34</v>
       </c>
       <c r="AA589" t="n">
-        <v>349182.48</v>
+        <v>723732.4399999999</v>
       </c>
       <c r="AB589" t="n">
-        <v>14079462.55</v>
+        <v>13750207.97</v>
       </c>
       <c r="AC589" t="n">
-        <v>0.02212685793968987</v>
+        <v>0.04499486227855917</v>
       </c>
     </row>
     <row r="590">
@@ -69337,9 +69343,15 @@
       <c r="D590" s="3" t="n">
         <v>46063</v>
       </c>
+      <c r="E590" s="3" t="n">
+        <v>46134</v>
+      </c>
+      <c r="F590" s="3" t="n">
+        <v>46493</v>
+      </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -69393,7 +69405,7 @@
         </is>
       </c>
       <c r="R590" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="S590" t="n">
         <v>0</v>
@@ -69402,7 +69414,7 @@
         <v>0</v>
       </c>
       <c r="U590" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="V590" t="n">
         <v>2962697.76</v>
@@ -70209,19 +70221,19 @@
         <v>32998445.8</v>
       </c>
       <c r="Y597" t="n">
-        <v>0</v>
+        <v>604883.63</v>
       </c>
       <c r="Z597" t="n">
-        <v>0</v>
+        <v>62432.08</v>
       </c>
       <c r="AA597" t="n">
-        <v>0</v>
+        <v>667315.71</v>
       </c>
       <c r="AB597" t="n">
-        <v>32998445.8</v>
+        <v>32393562.17</v>
       </c>
       <c r="AC597" t="n">
-        <v>0</v>
+        <v>0.01833067028872008</v>
       </c>
     </row>
     <row r="598">
@@ -71069,12 +71081,12 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>DATA TRAFFIC S/A</t>
+          <t>CONSORCIO DTSV MOBILIDADE</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>01175068000174</t>
+          <t>63619417000157</t>
         </is>
       </c>
       <c r="J605" t="inlineStr">
@@ -71114,7 +71126,7 @@
       </c>
       <c r="Q605" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Araçuaí, Capelinha, Carbonita, Carlos Chagas, Coluna, Conceição do Mato Dentro, Diamantina, Dom Joaquim, Fronteira dos Vales, Fruta de Leite, Gouvea, Governador Valadares, Jacinto, José Gonçalves de Minas, José Raydan, Malacacheta, Mata Verde, Montezuma, Nanuque, Ponto dos Volantes, Rio Pardo de Minas, Salinas, Senhora do Porto, São João do Manteninha, Umburatiba, Virginópolis, Água Boa</t>
+          <t xml:space="preserve"> Obra 1 - Alvorada de Minas, Araçuaí, Capelinha, Carbonita, Carlos Chagas, Coluna, Conceição do Mato Dentro, Diamantina, Dom Joaquim, Fronteira dos Vales, Fruta de Leite, Gouvea, Governador Valadares, Jacinto, José Gonçalves de Minas, José Raydan, Malacacheta, Mata Verde, Montezuma, Nanuque, Ponto dos Volantes, Rio Pardo de Minas, Salinas, Senhora do Porto, São João do Manteninha, Umburatiba, Virginópolis, Água Boa</t>
         </is>
       </c>
       <c r="R605" t="n">
@@ -71274,27 +71286,27 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>PO</t>
+          <t>DM-008/2024-A</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>230176203623</t>
         </is>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>SERVIÇOS ESPECIAIS DE APOIO À COORDENAÇÃO E APOIO TÉCNICO NO PLANEJAMENTO, MONITORAMENTO E AVALIAÇÃO DO PORTIFÓLIO DE EMPREENDIMENTOS DO DER-MG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
         </is>
       </c>
       <c r="D607" s="3" t="n">
-        <v>45589</v>
+        <v>46112</v>
       </c>
       <c r="E607" s="3" t="n">
-        <v>45628</v>
+        <v>46121</v>
       </c>
       <c r="F607" s="3" t="n">
-        <v>46722</v>
+        <v>46851</v>
       </c>
       <c r="G607" t="inlineStr">
         <is>
@@ -71303,12 +71315,12 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYSTRA ENGENHARIA E  CONSULTORIA LTDA </t>
+          <t>HWN ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>52635422000307</t>
+          <t>19256565000162</t>
         </is>
       </c>
       <c r="J607" t="inlineStr">
@@ -71318,7 +71330,7 @@
       </c>
       <c r="K607" t="inlineStr">
         <is>
-          <t>ASSESSORIA DE GESTÃO ESTRATÉGICA</t>
+          <t>DIRETORIA DE OPERAÇÕES</t>
         </is>
       </c>
       <c r="L607" t="inlineStr">
@@ -71333,16 +71345,26 @@
       </c>
       <c r="N607" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Manutenção e Conservação</t>
         </is>
       </c>
       <c r="O607" t="inlineStr">
         <is>
-          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="P607" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - MANUTENÇÃO E CONSERVAÇÃO - 07ª URG</t>
+        </is>
+      </c>
+      <c r="Q607" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Araxá, Ibiá, Patrocínio, Pedrinópolis, Perdizes, Pratinha, Rio Paranaíba, Sacramento, Santa Juliana, Serra do Salitre, Tapira</t>
         </is>
       </c>
       <c r="R607" t="n">
-        <v>1095</v>
+        <v>731</v>
       </c>
       <c r="S607" t="n">
         <v>0</v>
@@ -71351,16 +71373,16 @@
         <v>0</v>
       </c>
       <c r="U607" t="n">
-        <v>1095</v>
+        <v>731</v>
       </c>
       <c r="V607" t="n">
-        <v>5774752.44</v>
+        <v>31172534.58</v>
       </c>
       <c r="W607" t="n">
         <v>0</v>
       </c>
       <c r="X607" t="n">
-        <v>5774752.44</v>
+        <v>31172534.58</v>
       </c>
       <c r="Y607" t="n">
         <v>0</v>
@@ -71372,7 +71394,7 @@
         <v>0</v>
       </c>
       <c r="AB607" t="n">
-        <v>5774752.44</v>
+        <v>31172534.58</v>
       </c>
       <c r="AC607" t="n">
         <v>0</v>
@@ -71381,35 +71403,41 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>DO009482014/2025</t>
+          <t>DM-011/2024-A</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>230190100125</t>
+          <t>230176203623</t>
         </is>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇO DE ENGENHARIA DE TRANSITO - LOTE 01 </t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
         </is>
       </c>
       <c r="D608" s="3" t="n">
-        <v>45974</v>
+        <v>46112</v>
+      </c>
+      <c r="E608" s="3" t="n">
+        <v>46120</v>
+      </c>
+      <c r="F608" s="3" t="n">
+        <v>46850</v>
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+          <t>CONSÓRCIO AGR - CSR</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>16502551000193</t>
+          <t>54308576000140</t>
         </is>
       </c>
       <c r="J608" t="inlineStr">
@@ -71419,7 +71447,7 @@
       </c>
       <c r="K608" t="inlineStr">
         <is>
-          <t>GERÊNCIA DE TRÂFEGO E SEGURANÇA VIÁRIA</t>
+          <t>DIRETORIA DE OPERAÇÕES</t>
         </is>
       </c>
       <c r="L608" t="inlineStr">
@@ -71434,7 +71462,7 @@
       </c>
       <c r="N608" t="inlineStr">
         <is>
-          <t>Operação-Radar</t>
+          <t>Manutenção e Conservação</t>
         </is>
       </c>
       <c r="O608" t="inlineStr">
@@ -71442,8 +71470,18 @@
           <t>Natureza continuada e/ou conserva</t>
         </is>
       </c>
+      <c r="P608" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - MANUTENÇÃO E CONSERVAÇÃO - 33ª URG</t>
+        </is>
+      </c>
+      <c r="Q608" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Buritizeiro, Coração de Jesus, Corinto, Ibiaí, João Pinheiro, Lagoa dos Patos, Lassance, Pirapora, Ponto Chique, Santa Fé de Minas, São Romão, Várzea da Palma</t>
+        </is>
+      </c>
       <c r="R608" t="n">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="S608" t="n">
         <v>0</v>
@@ -71452,16 +71490,16 @@
         <v>0</v>
       </c>
       <c r="U608" t="n">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="V608" t="n">
-        <v>77898894.3</v>
+        <v>24832463.21</v>
       </c>
       <c r="W608" t="n">
         <v>0</v>
       </c>
       <c r="X608" t="n">
-        <v>77898894.3</v>
+        <v>24832463.21</v>
       </c>
       <c r="Y608" t="n">
         <v>0</v>
@@ -71473,7 +71511,7 @@
         <v>0</v>
       </c>
       <c r="AB608" t="n">
-        <v>77898894.3</v>
+        <v>24832463.21</v>
       </c>
       <c r="AC608" t="n">
         <v>0</v>
@@ -71482,106 +71520,1222 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
+          <t>DM-009/2024-A</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>230176203623</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="D609" s="3" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E609" s="3" t="n">
+        <v>46122</v>
+      </c>
+      <c r="F609" s="3" t="n">
+        <v>46852</v>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>ASEL CONSTRUCOES RODOVIARIAS LTDA</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>20966503000123</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>Manutenção e Conservação</t>
+        </is>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="P609" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - MANUTENÇÃO E CONSERVAÇÃO - 14ª URG</t>
+        </is>
+      </c>
+      <c r="Q609" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Arapuá, Carmo do Paranaíba, Cruzeiro da Fortaleza, Lagamar, Lagoa Formosa, Lagoa Grande, Matutina, Patos de Minas, Presidente Olegário, Rio Paranaíba, Santa Rosa da Serra, Serra do Salitre, São Gonçalo do Abaeté, São Gotardo, Tiros, Varjão de Minas, Vazante</t>
+        </is>
+      </c>
+      <c r="R609" t="n">
+        <v>731</v>
+      </c>
+      <c r="S609" t="n">
+        <v>0</v>
+      </c>
+      <c r="T609" t="n">
+        <v>0</v>
+      </c>
+      <c r="U609" t="n">
+        <v>731</v>
+      </c>
+      <c r="V609" t="n">
+        <v>30603197.87</v>
+      </c>
+      <c r="W609" t="n">
+        <v>0</v>
+      </c>
+      <c r="X609" t="n">
+        <v>30603197.87</v>
+      </c>
+      <c r="Y609" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z609" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA609" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB609" t="n">
+        <v>30603197.87</v>
+      </c>
+      <c r="AC609" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>DM-010/2024-A</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>230176203623</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="D610" s="3" t="n">
+        <v>46118</v>
+      </c>
+      <c r="E610" s="3" t="n">
+        <v>46120</v>
+      </c>
+      <c r="F610" s="3" t="n">
+        <v>46850</v>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>CONSÓRCIO IPÊ / ABRIL</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>54414852000154</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>Manutenção e Conservação</t>
+        </is>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="P610" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - MANUTENÇÃO E CONSERVAÇÃO - 23ª URG</t>
+        </is>
+      </c>
+      <c r="Q610" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Alpercata, Alvarenga, Campanário, Capitão Andrade, Central de Minas, Conselheiro Pena, Cuparaque, Divino das Laranjeiras, Dom Cavati, Engenheiro Caldas, Fernandes Tourinho, Frei Inocêncio, Galiléia, Goiabeira, Governador Valadares, Itabirinha de Mantena, Itanhomi, Itueta, Jampruca, Mantena, Marilac, Mathias Lobato, Mendes Pimentel, Nacip Raydan, Nova Belém, Nova Módica, Periquito, Pescador, Resplendor, Santa Maria do Suaçuí, Santa Rita do Itueto, Sobrália, São Félix de Minas, São Geraldo do Baixio, São José da Safira, São José do Divino, São João do Manteninha, Tarumirim, Tumiritinga, Virgolândia</t>
+        </is>
+      </c>
+      <c r="R610" t="n">
+        <v>731</v>
+      </c>
+      <c r="S610" t="n">
+        <v>0</v>
+      </c>
+      <c r="T610" t="n">
+        <v>0</v>
+      </c>
+      <c r="U610" t="n">
+        <v>731</v>
+      </c>
+      <c r="V610" t="n">
+        <v>34422078.35</v>
+      </c>
+      <c r="W610" t="n">
+        <v>0</v>
+      </c>
+      <c r="X610" t="n">
+        <v>34422078.35</v>
+      </c>
+      <c r="Y610" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z610" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA610" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB610" t="n">
+        <v>34422078.35</v>
+      </c>
+      <c r="AC610" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>DM-012/2024-A</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>230176203623</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 35ª URG</t>
+        </is>
+      </c>
+      <c r="D611" s="3" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E611" s="3" t="n">
+        <v>46123</v>
+      </c>
+      <c r="F611" s="3" t="n">
+        <v>46853</v>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>GUAXIMA ENGENHARIA LTDA</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>19230918000155</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>Manutenção e Conservação</t>
+        </is>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="P611" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - MANUTENÇÃO E CONSERVAÇÃO - 35ª URG</t>
+        </is>
+      </c>
+      <c r="Q611" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Abaeté, Biquinhas, Bom Despacho, Cedro do Abaeté, Curvelo, Dores do Indaiá, Estrela do Indaiá, Luz, Martinho Campos, Morada Nova de Minas, Paineiras, Pompéu, Quartel Geral, Serra da Saudade, São Gotardo</t>
+        </is>
+      </c>
+      <c r="R611" t="n">
+        <v>731</v>
+      </c>
+      <c r="S611" t="n">
+        <v>0</v>
+      </c>
+      <c r="T611" t="n">
+        <v>0</v>
+      </c>
+      <c r="U611" t="n">
+        <v>731</v>
+      </c>
+      <c r="V611" t="n">
+        <v>29302939.12</v>
+      </c>
+      <c r="W611" t="n">
+        <v>0</v>
+      </c>
+      <c r="X611" t="n">
+        <v>29302939.12</v>
+      </c>
+      <c r="Y611" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z611" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA611" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB611" t="n">
+        <v>29302939.12</v>
+      </c>
+      <c r="AC611" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>DM-9502116/2026</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>230176202625</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>APOIO À SUPERVISÃO E GESTÃO DOS CONTRATOS DE CONSERVAÇÃO/MANUTENÇÃO E RECUPERAÇÃO FUNCIONAL</t>
+        </is>
+      </c>
+      <c r="D612" s="3" t="n">
+        <v>46125</v>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>A Iniciar</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>PLANEP PLANEJAMENTO, ESTUDOS E PROJETOS LTDA.</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>10417566000177</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>Consultoria</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+        </is>
+      </c>
+      <c r="P612" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Apoio à supervisão e gestão dos contratos de conservação/manutenção e recuperação funcional</t>
+        </is>
+      </c>
+      <c r="Q612" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="R612" t="n">
+        <v>0</v>
+      </c>
+      <c r="S612" t="n">
+        <v>0</v>
+      </c>
+      <c r="T612" t="n">
+        <v>0</v>
+      </c>
+      <c r="U612" t="n">
+        <v>0</v>
+      </c>
+      <c r="V612" t="n">
+        <v>5342582.88</v>
+      </c>
+      <c r="W612" t="n">
+        <v>0</v>
+      </c>
+      <c r="X612" t="n">
+        <v>5342582.88</v>
+      </c>
+      <c r="Y612" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z612" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA612" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB612" t="n">
+        <v>5342582.88</v>
+      </c>
+      <c r="AC612" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>DM-018/2024-A</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>230176205123</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 36ª URG</t>
+        </is>
+      </c>
+      <c r="D613" s="3" t="n">
+        <v>46112</v>
+      </c>
+      <c r="E613" s="3" t="n">
+        <v>46136</v>
+      </c>
+      <c r="F613" s="3" t="n">
+        <v>46866</v>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>CONSTRUTORA SAGENDRA LTDA</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>17311358000138</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>RDC</t>
+        </is>
+      </c>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>Manutenção e Conservação</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - MANUTENÇÃO E CONSERVAÇÃO - 36ª URG</t>
+        </is>
+      </c>
+      <c r="Q613" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Arinos, Buritis, Chapada Gaúcha, Formoso, Pintópolis, Riachinho, Unaí, Uruana de Minas, Urucuia</t>
+        </is>
+      </c>
+      <c r="R613" t="n">
+        <v>731</v>
+      </c>
+      <c r="S613" t="n">
+        <v>0</v>
+      </c>
+      <c r="T613" t="n">
+        <v>0</v>
+      </c>
+      <c r="U613" t="n">
+        <v>731</v>
+      </c>
+      <c r="V613" t="n">
+        <v>36954174.97</v>
+      </c>
+      <c r="W613" t="n">
+        <v>0</v>
+      </c>
+      <c r="X613" t="n">
+        <v>36954174.97</v>
+      </c>
+      <c r="Y613" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z613" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA613" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB613" t="n">
+        <v>36954174.97</v>
+      </c>
+      <c r="AC613" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>DM-016/2024-A</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>230176205123</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 13ª URG</t>
+        </is>
+      </c>
+      <c r="D614" s="3" t="n">
+        <v>46127</v>
+      </c>
+      <c r="E614" s="3" t="n">
+        <v>46138</v>
+      </c>
+      <c r="F614" s="3" t="n">
+        <v>46868</v>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>LCM CONSTRUCAO E COMERCIO S/A</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>19758842000135</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE OPERAÇÕES</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>RDC</t>
+        </is>
+      </c>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>Manutenção e Conservação</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - MANUTENÇÃO E CONSERVAÇÃO - 13ª URG</t>
+        </is>
+      </c>
+      <c r="Q614" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Brasília de Minas, Campo Azul, Chapada Gaúcha, Coração de Jesus, Ibiaí, Ibiracatu, Icaraí de Minas, Japonvar, Lontra, Luislândia, Mirabela, Patis, Pedras de Maria da Cruz, Pintópolis, Ponto Chique, São Francisco, São João da Ponte, São João do Pacuí, Ubaí, Varzelândia</t>
+        </is>
+      </c>
+      <c r="R614" t="n">
+        <v>731</v>
+      </c>
+      <c r="S614" t="n">
+        <v>0</v>
+      </c>
+      <c r="T614" t="n">
+        <v>0</v>
+      </c>
+      <c r="U614" t="n">
+        <v>731</v>
+      </c>
+      <c r="V614" t="n">
+        <v>33205062.4</v>
+      </c>
+      <c r="W614" t="n">
+        <v>0</v>
+      </c>
+      <c r="X614" t="n">
+        <v>33205062.4</v>
+      </c>
+      <c r="Y614" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z614" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA614" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB614" t="n">
+        <v>33205062.4</v>
+      </c>
+      <c r="AC614" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>DC-9501601/2026</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>230152003725</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>IMPLANTAÇÃO DE PONTES : TRECHO PINTÓPOLIS - URUCUIA (RODOVIA MG-202) PTS CÓRREGO GAMELEIRAS ,TABOCAS E RIBEIRÃO DAS PEDRAS</t>
+        </is>
+      </c>
+      <c r="D615" s="3" t="n">
+        <v>46125</v>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>A Iniciar</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t xml:space="preserve">S3 VEREDA CONSORCIO LTDA </t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>65300070000100</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIRETORIA DE CONSTRUÇÃO E OBRAS RODOVIÁRIAS </t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>OAE</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária</t>
+        </is>
+      </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Implantação da Ponte sobre o Ribeirão das Pedras, dimensões  33,0 x 10,0m (Estaca 2.796+15,00),  Obra 2 - Implantação da Ponte sobre o Córrego das Tabocas, dimensões  59,0m x 10,0m (Estaca 3.514+6,00),  Obra 3 - Implantação da Ponte sobre o Córrego  da Gameleiras, dimensões  39,0m x 10,0m (Estaca 3.161+16,00)</t>
+        </is>
+      </c>
+      <c r="Q615" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Pintópolis,  Obra 2 - Pintópolis,  Obra 3 - Pintópolis</t>
+        </is>
+      </c>
+      <c r="R615" t="n">
+        <v>0</v>
+      </c>
+      <c r="S615" t="n">
+        <v>0</v>
+      </c>
+      <c r="T615" t="n">
+        <v>0</v>
+      </c>
+      <c r="U615" t="n">
+        <v>0</v>
+      </c>
+      <c r="V615" t="n">
+        <v>9814000</v>
+      </c>
+      <c r="W615" t="n">
+        <v>0</v>
+      </c>
+      <c r="X615" t="n">
+        <v>9814000</v>
+      </c>
+      <c r="Y615" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z615" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA615" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB615" t="n">
+        <v>9814000</v>
+      </c>
+      <c r="AC615" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Não Disponível</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>SERVIÇOS ESPECIAIS DE APOIO À COORDENAÇÃO E APOIO TÉCNICO NO PLANEJAMENTO, MONITORAMENTO E AVALIAÇÃO DO PORTIFÓLIO DE EMPREENDIMENTOS DO DER-MG</t>
+        </is>
+      </c>
+      <c r="D616" s="3" t="n">
+        <v>45589</v>
+      </c>
+      <c r="E616" s="3" t="n">
+        <v>45628</v>
+      </c>
+      <c r="F616" s="3" t="n">
+        <v>46722</v>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYSTRA ENGENHARIA E  CONSULTORIA LTDA </t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>52635422000307</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>ASSESSORIA DE GESTÃO ESTRATÉGICA</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>Consultoria</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+        </is>
+      </c>
+      <c r="R616" t="n">
+        <v>1095</v>
+      </c>
+      <c r="S616" t="n">
+        <v>0</v>
+      </c>
+      <c r="T616" t="n">
+        <v>0</v>
+      </c>
+      <c r="U616" t="n">
+        <v>1095</v>
+      </c>
+      <c r="V616" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="W616" t="n">
+        <v>0</v>
+      </c>
+      <c r="X616" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="Y616" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z616" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA616" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB616" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="AC616" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>DO009482014/2025</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>230190100125</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇO DE ENGENHARIA DE TRANSITO - LOTE 01 </t>
+        </is>
+      </c>
+      <c r="D617" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>A Iniciar</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>16502551000193</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>GERÊNCIA DE TRÂFEGO E SEGURANÇA VIÁRIA</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>Operação-Radar</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="R617" t="n">
+        <v>0</v>
+      </c>
+      <c r="S617" t="n">
+        <v>0</v>
+      </c>
+      <c r="T617" t="n">
+        <v>0</v>
+      </c>
+      <c r="U617" t="n">
+        <v>0</v>
+      </c>
+      <c r="V617" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="W617" t="n">
+        <v>0</v>
+      </c>
+      <c r="X617" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="Y617" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z617" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA617" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB617" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="AC617" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Não Disponível</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>APOIO À SUPERVISÃO AMBIENTAL E AOS PROCEDIMENTOS DE GESTÃO E REGULARIZAÇÃO AMBIENTAL DOS EMPREENDIMENTOS RODOVIÁRIOS DO DER-MG</t>
+        </is>
+      </c>
+      <c r="D618" s="3" t="n">
+        <v>46108</v>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>A Iniciar</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>STE SERVIÇOS TÉCNICOS DE ENGENHARIA S/A</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>88849773000198</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>DER/DG/ASSESSORIA DE MEIO AMBIENTE</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>Concorrência - Concorrência eletrônica</t>
+        </is>
+      </c>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>Estudos Ambientais</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+        </is>
+      </c>
+      <c r="R618" t="n">
+        <v>0</v>
+      </c>
+      <c r="S618" t="n">
+        <v>0</v>
+      </c>
+      <c r="T618" t="n">
+        <v>0</v>
+      </c>
+      <c r="U618" t="n">
+        <v>0</v>
+      </c>
+      <c r="V618" t="n">
+        <v>0</v>
+      </c>
+      <c r="W618" t="n">
+        <v>0</v>
+      </c>
+      <c r="X618" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y618" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z618" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA618" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB618" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC618" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
           <t>DP-001/2023</t>
         </is>
       </c>
-      <c r="B609" t="inlineStr">
+      <c r="B619" t="inlineStr">
         <is>
           <t>2301601000022020</t>
         </is>
       </c>
-      <c r="C609" t="inlineStr">
+      <c r="C619" t="inlineStr">
         <is>
           <t>ELABORAÇÃO DE PROJETO DE ENGENHARIA RODOVIÁRIA DE MELHORAMENTOS, PAVIMENTAÇÃO E OAE - LOTE 2</t>
         </is>
       </c>
-      <c r="D609" s="3" t="n">
+      <c r="D619" s="3" t="n">
         <v>45166</v>
       </c>
-      <c r="G609" t="inlineStr">
+      <c r="G619" t="inlineStr">
         <is>
           <t>A Iniciar</t>
         </is>
       </c>
-      <c r="H609" t="inlineStr">
+      <c r="H619" t="inlineStr">
         <is>
           <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
-      <c r="I609" t="inlineStr">
+      <c r="I619" t="inlineStr">
         <is>
           <t>38743357000132</t>
         </is>
       </c>
-      <c r="J609" t="inlineStr">
+      <c r="J619" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr">
+      <c r="K619" t="inlineStr">
         <is>
           <t>DIRETORIA DE PROJETOS</t>
         </is>
       </c>
-      <c r="L609" t="inlineStr">
+      <c r="L619" t="inlineStr">
         <is>
           <t>RDC</t>
         </is>
       </c>
-      <c r="M609" t="inlineStr">
+      <c r="M619" t="inlineStr">
         <is>
           <t>EMPREITADA POR PREÇO UNITÁRIO</t>
         </is>
       </c>
-      <c r="N609" t="inlineStr">
+      <c r="N619" t="inlineStr">
         <is>
           <t>Consultoria para Projetos</t>
         </is>
       </c>
-      <c r="O609" t="inlineStr">
+      <c r="O619" t="inlineStr">
         <is>
           <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
         </is>
       </c>
-      <c r="R609" t="n">
-        <v>0</v>
-      </c>
-      <c r="S609" t="n">
-        <v>0</v>
-      </c>
-      <c r="T609" t="n">
-        <v>0</v>
-      </c>
-      <c r="U609" t="n">
-        <v>0</v>
-      </c>
-      <c r="V609" t="n">
+      <c r="R619" t="n">
+        <v>0</v>
+      </c>
+      <c r="S619" t="n">
+        <v>0</v>
+      </c>
+      <c r="T619" t="n">
+        <v>0</v>
+      </c>
+      <c r="U619" t="n">
+        <v>0</v>
+      </c>
+      <c r="V619" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="W609" t="n">
-        <v>0</v>
-      </c>
-      <c r="X609" t="n">
+      <c r="W619" t="n">
+        <v>0</v>
+      </c>
+      <c r="X619" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="Y609" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z609" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA609" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB609" t="n">
+      <c r="Y619" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z619" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA619" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB619" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="AC609" t="n">
+      <c r="AC619" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC609"/>
+  <autoFilter ref="A1:AC619"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/contratos.xlsx
+++ b/upload/contratos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AC$619</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AC$622</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC619"/>
+  <dimension ref="A1:AC622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2273,7 +2273,7 @@
         <v>44524</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46182</v>
+        <v>46189</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1299</v>
+        <v>1306</v>
       </c>
       <c r="U16" t="n">
-        <v>1659</v>
+        <v>1666</v>
       </c>
       <c r="V16" t="n">
         <v>1452371.99</v>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6096,19 +6096,19 @@
         <v>2814906.8</v>
       </c>
       <c r="Y48" t="n">
-        <v>2733037.82</v>
+        <v>2738058.77</v>
       </c>
       <c r="Z48" t="n">
-        <v>290615.2</v>
+        <v>291460.72</v>
       </c>
       <c r="AA48" t="n">
-        <v>3023653.02</v>
+        <v>3029519.49</v>
       </c>
       <c r="AB48" t="n">
-        <v>81868.98</v>
+        <v>76848.03</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.9709159180687617</v>
+        <v>0.9726996183319462</v>
       </c>
     </row>
     <row r="49">
@@ -7383,19 +7383,19 @@
         <v>65069077.71</v>
       </c>
       <c r="Y59" t="n">
-        <v>59045135.03</v>
+        <v>59061564.45</v>
       </c>
       <c r="Z59" t="n">
-        <v>53965887.89</v>
+        <v>53983296.31</v>
       </c>
       <c r="AA59" t="n">
-        <v>113011022.92</v>
+        <v>113044860.76</v>
       </c>
       <c r="AB59" t="n">
-        <v>6023942.68</v>
+        <v>6007513.26</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.9074223441916985</v>
+        <v>0.9076748361675834</v>
       </c>
     </row>
     <row r="60">
@@ -12200,7 +12200,7 @@
         <v>44850</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>46140</v>
+        <v>46147</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -12264,10 +12264,10 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="U101" t="n">
-        <v>1291</v>
+        <v>1298</v>
       </c>
       <c r="V101" t="n">
         <v>1365885.84</v>
@@ -15827,11 +15827,11 @@
         <v>45026</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>46145</v>
+        <v>46150</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Paralisado</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -15891,10 +15891,10 @@
         <v>510</v>
       </c>
       <c r="T132" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U132" t="n">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="V132" t="n">
         <v>19915653.29</v>
@@ -24017,7 +24017,7 @@
         <v>44767</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -24081,10 +24081,10 @@
         <v>0</v>
       </c>
       <c r="T202" t="n">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="U202" t="n">
-        <v>1472</v>
+        <v>1479</v>
       </c>
       <c r="V202" t="n">
         <v>2519553.4</v>
@@ -26819,7 +26819,7 @@
         <v>44810</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>46159</v>
+        <v>46166</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -26883,10 +26883,10 @@
         <v>0</v>
       </c>
       <c r="T226" t="n">
-        <v>1169</v>
+        <v>1176</v>
       </c>
       <c r="U226" t="n">
-        <v>1350</v>
+        <v>1357</v>
       </c>
       <c r="V226" t="n">
         <v>1559477.28</v>
@@ -28457,7 +28457,7 @@
         <v>44579</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>46355</v>
+        <v>46362</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -28521,10 +28521,10 @@
         <v>180</v>
       </c>
       <c r="T240" t="n">
-        <v>1237</v>
+        <v>1244</v>
       </c>
       <c r="U240" t="n">
-        <v>1777</v>
+        <v>1784</v>
       </c>
       <c r="V240" t="n">
         <v>1175120.88</v>
@@ -37097,7 +37097,7 @@
         <v>45384</v>
       </c>
       <c r="F314" s="3" t="n">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -37161,10 +37161,10 @@
         <v>330</v>
       </c>
       <c r="T314" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="U314" t="n">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="V314" t="n">
         <v>2816620.4</v>
@@ -40373,7 +40373,7 @@
         <v>45110</v>
       </c>
       <c r="F342" s="3" t="n">
-        <v>46158</v>
+        <v>46165</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -40437,10 +40437,10 @@
         <v>398</v>
       </c>
       <c r="T342" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="U342" t="n">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="V342" t="n">
         <v>3655796.23</v>
@@ -42479,7 +42479,7 @@
         <v>45236</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -42543,10 +42543,10 @@
         <v>480</v>
       </c>
       <c r="T360" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="U360" t="n">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="V360" t="n">
         <v>5042730.21</v>
@@ -43649,11 +43649,11 @@
         <v>45236</v>
       </c>
       <c r="F370" s="3" t="n">
-        <v>46133</v>
+        <v>46151</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Paralisado</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -43713,10 +43713,10 @@
         <v>510</v>
       </c>
       <c r="T370" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="U370" t="n">
-        <v>898</v>
+        <v>916</v>
       </c>
       <c r="V370" t="n">
         <v>7889881.67</v>
@@ -45170,7 +45170,7 @@
         <v>45237</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>46145</v>
+        <v>46152</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -45234,10 +45234,10 @@
         <v>510</v>
       </c>
       <c r="T383" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="U383" t="n">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="V383" t="n">
         <v>4065559.6</v>
@@ -51008,11 +51008,11 @@
         <v>45355</v>
       </c>
       <c r="F433" s="3" t="n">
-        <v>46141</v>
+        <v>46290</v>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Paralisado</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -51069,13 +51069,13 @@
         <v>360</v>
       </c>
       <c r="S433" t="n">
-        <v>330</v>
+        <v>480</v>
       </c>
       <c r="T433" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U433" t="n">
-        <v>787</v>
+        <v>936</v>
       </c>
       <c r="V433" t="n">
         <v>5820891.54</v>
@@ -51363,7 +51363,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -51438,19 +51438,19 @@
         <v>28096598.89</v>
       </c>
       <c r="Y436" t="n">
-        <v>26999282.29</v>
+        <v>27634042.2</v>
       </c>
       <c r="Z436" t="n">
-        <v>1385505.74</v>
+        <v>1443844.31</v>
       </c>
       <c r="AA436" t="n">
-        <v>28384788.03</v>
+        <v>29077886.51</v>
       </c>
       <c r="AB436" t="n">
-        <v>1097316.6</v>
+        <v>462556.69</v>
       </c>
       <c r="AC436" t="n">
-        <v>0.9609448601129245</v>
+        <v>0.9835369152041875</v>
       </c>
     </row>
     <row r="437">
@@ -52065,7 +52065,7 @@
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -52140,19 +52140,19 @@
         <v>30648355.12</v>
       </c>
       <c r="Y442" t="n">
-        <v>17173368.49</v>
+        <v>18729510.86</v>
       </c>
       <c r="Z442" t="n">
-        <v>1180122.02</v>
+        <v>1331166.75</v>
       </c>
       <c r="AA442" t="n">
-        <v>18353490.51</v>
+        <v>20060677.61</v>
       </c>
       <c r="AB442" t="n">
-        <v>13474986.63</v>
+        <v>11918844.26</v>
       </c>
       <c r="AC442" t="n">
-        <v>0.5603357316488834</v>
+        <v>0.6111098225880907</v>
       </c>
     </row>
     <row r="443">
@@ -52182,7 +52182,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -52257,19 +52257,19 @@
         <v>34071020.86</v>
       </c>
       <c r="Y443" t="n">
-        <v>15858861.26</v>
+        <v>16099407.69</v>
       </c>
       <c r="Z443" t="n">
-        <v>2594810.81</v>
+        <v>2646021.53</v>
       </c>
       <c r="AA443" t="n">
-        <v>18453672.07</v>
+        <v>18745429.22</v>
       </c>
       <c r="AB443" t="n">
-        <v>18212159.6</v>
+        <v>17971613.17</v>
       </c>
       <c r="AC443" t="n">
-        <v>0.4654648102610448</v>
+        <v>0.4725249576804139</v>
       </c>
     </row>
     <row r="444">
@@ -52763,11 +52763,11 @@
         <v>45722</v>
       </c>
       <c r="F448" s="3" t="n">
-        <v>46148</v>
+        <v>46364</v>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Paralisado</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -52824,13 +52824,13 @@
         <v>360</v>
       </c>
       <c r="S448" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="T448" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="U448" t="n">
-        <v>427</v>
+        <v>643</v>
       </c>
       <c r="V448" t="n">
         <v>1922644.28</v>
@@ -52884,7 +52884,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -52959,19 +52959,19 @@
         <v>37153801.63</v>
       </c>
       <c r="Y449" t="n">
-        <v>30132401.34</v>
+        <v>31480840.39</v>
       </c>
       <c r="Z449" t="n">
-        <v>1413980.61</v>
+        <v>1560103.92</v>
       </c>
       <c r="AA449" t="n">
-        <v>31546381.95</v>
+        <v>33040944.31</v>
       </c>
       <c r="AB449" t="n">
-        <v>7021400.29</v>
+        <v>5672961.24</v>
       </c>
       <c r="AC449" t="n">
-        <v>0.811017985186998</v>
+        <v>0.8473114192594671</v>
       </c>
     </row>
     <row r="450">
@@ -54246,19 +54246,19 @@
         <v>3345699.13</v>
       </c>
       <c r="Y460" t="n">
-        <v>2283579.27</v>
+        <v>2386069.14</v>
       </c>
       <c r="Z460" t="n">
-        <v>183253.44</v>
+        <v>196495.13</v>
       </c>
       <c r="AA460" t="n">
-        <v>2466832.71</v>
+        <v>2582564.27</v>
       </c>
       <c r="AB460" t="n">
-        <v>1062119.86</v>
+        <v>959629.99</v>
       </c>
       <c r="AC460" t="n">
-        <v>0.6825417293275861</v>
+        <v>0.7131750487079811</v>
       </c>
     </row>
     <row r="461">
@@ -55293,10 +55293,10 @@
         <v>46337191.41</v>
       </c>
       <c r="W469" t="n">
-        <v>0</v>
+        <v>1821413.8</v>
       </c>
       <c r="X469" t="n">
-        <v>46337191.41</v>
+        <v>48158605.21</v>
       </c>
       <c r="Y469" t="n">
         <v>29856106.57</v>
@@ -55308,10 +55308,10 @@
         <v>31213275.83</v>
       </c>
       <c r="AB469" t="n">
-        <v>16481084.84</v>
+        <v>18302498.64</v>
       </c>
       <c r="AC469" t="n">
-        <v>0.6443227494266468</v>
+        <v>0.6199537224927865</v>
       </c>
     </row>
     <row r="470">
@@ -55767,19 +55767,19 @@
         <v>47556790.26</v>
       </c>
       <c r="Y473" t="n">
-        <v>31001351.31</v>
+        <v>32145995.87</v>
       </c>
       <c r="Z473" t="n">
-        <v>1306191.62</v>
+        <v>1389956.58</v>
       </c>
       <c r="AA473" t="n">
-        <v>32307542.93</v>
+        <v>33535952.45</v>
       </c>
       <c r="AB473" t="n">
-        <v>16555438.95</v>
+        <v>15410794.39</v>
       </c>
       <c r="AC473" t="n">
-        <v>0.6518806492303419</v>
+        <v>0.6759496529150325</v>
       </c>
     </row>
     <row r="474">
@@ -56150,7 +56150,7 @@
         <v>45573</v>
       </c>
       <c r="F477" s="3" t="n">
-        <v>46211</v>
+        <v>46218</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
@@ -56214,10 +56214,10 @@
         <v>0</v>
       </c>
       <c r="T477" t="n">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="U477" t="n">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="V477" t="n">
         <v>3876550</v>
@@ -60675,19 +60675,19 @@
         <v>4776981.58</v>
       </c>
       <c r="Y515" t="n">
-        <v>2916164.28</v>
+        <v>3155692.55</v>
       </c>
       <c r="Z515" t="n">
-        <v>93313.14999999999</v>
+        <v>101679.28</v>
       </c>
       <c r="AA515" t="n">
-        <v>3009477.43</v>
+        <v>3257371.83</v>
       </c>
       <c r="AB515" t="n">
-        <v>1860817.3</v>
+        <v>1621289.03</v>
       </c>
       <c r="AC515" t="n">
-        <v>0.6104616966096821</v>
+        <v>0.6606038765592226</v>
       </c>
     </row>
     <row r="516">
@@ -61020,10 +61020,10 @@
         <v>44482154.94</v>
       </c>
       <c r="W518" t="n">
-        <v>0</v>
+        <v>7757492.99</v>
       </c>
       <c r="X518" t="n">
-        <v>44482154.94</v>
+        <v>52239647.93</v>
       </c>
       <c r="Y518" t="n">
         <v>17027419.71</v>
@@ -61035,10 +61035,10 @@
         <v>17542994.09</v>
       </c>
       <c r="AB518" t="n">
-        <v>27454735.23</v>
+        <v>35212228.22</v>
       </c>
       <c r="AC518" t="n">
-        <v>0.3827921496377037</v>
+        <v>0.325948209544145</v>
       </c>
     </row>
     <row r="519">
@@ -61611,19 +61611,19 @@
         <v>95661672.93000001</v>
       </c>
       <c r="Y523" t="n">
-        <v>12480224.9</v>
+        <v>15151232.48</v>
       </c>
       <c r="Z523" t="n">
-        <v>540755.11</v>
+        <v>646825.62</v>
       </c>
       <c r="AA523" t="n">
-        <v>13020980.01</v>
+        <v>15798058.1</v>
       </c>
       <c r="AB523" t="n">
-        <v>83181448.03</v>
+        <v>80510440.45</v>
       </c>
       <c r="AC523" t="n">
-        <v>0.130462122579984</v>
+        <v>0.1583835199190678</v>
       </c>
     </row>
     <row r="524">
@@ -62781,19 +62781,19 @@
         <v>2876761.94</v>
       </c>
       <c r="Y533" t="n">
-        <v>2383339.88</v>
+        <v>2421023.53</v>
       </c>
       <c r="Z533" t="n">
-        <v>99049.57000000001</v>
+        <v>102143.91</v>
       </c>
       <c r="AA533" t="n">
-        <v>2482389.45</v>
+        <v>2523167.44</v>
       </c>
       <c r="AB533" t="n">
-        <v>493422.06</v>
+        <v>455738.41</v>
       </c>
       <c r="AC533" t="n">
-        <v>0.828480051428934</v>
+        <v>0.8415793800442174</v>
       </c>
     </row>
     <row r="534">
@@ -64758,19 +64758,19 @@
         <v>207490000</v>
       </c>
       <c r="Y550" t="n">
-        <v>22167712.09</v>
+        <v>29767388.25</v>
       </c>
       <c r="Z550" t="n">
-        <v>311814.24</v>
+        <v>444200.11</v>
       </c>
       <c r="AA550" t="n">
-        <v>22479526.33</v>
+        <v>30211588.36</v>
       </c>
       <c r="AB550" t="n">
-        <v>185322287.91</v>
+        <v>177722611.75</v>
       </c>
       <c r="AC550" t="n">
-        <v>0.1068374962166851</v>
+        <v>0.143464206708757</v>
       </c>
     </row>
     <row r="551">
@@ -64875,19 +64875,19 @@
         <v>45918998.95</v>
       </c>
       <c r="Y551" t="n">
-        <v>1575614.78</v>
+        <v>2216386.72</v>
       </c>
       <c r="Z551" t="n">
-        <v>26742.86</v>
+        <v>42264.81</v>
       </c>
       <c r="AA551" t="n">
-        <v>1602357.64</v>
+        <v>2258651.53</v>
       </c>
       <c r="AB551" t="n">
-        <v>44343384.17</v>
+        <v>43702612.23</v>
       </c>
       <c r="AC551" t="n">
-        <v>0.03431291657110482</v>
+        <v>0.04826731354517039</v>
       </c>
     </row>
     <row r="552">
@@ -66513,19 +66513,19 @@
         <v>33799353.36</v>
       </c>
       <c r="Y565" t="n">
-        <v>0</v>
+        <v>673689.27</v>
       </c>
       <c r="Z565" t="n">
-        <v>0</v>
+        <v>143405.59</v>
       </c>
       <c r="AA565" t="n">
-        <v>0</v>
+        <v>817094.86</v>
       </c>
       <c r="AB565" t="n">
-        <v>33799353.36</v>
+        <v>33125664.09</v>
       </c>
       <c r="AC565" t="n">
-        <v>0</v>
+        <v>0.01993201653370329</v>
       </c>
     </row>
     <row r="566">
@@ -67917,19 +67917,19 @@
         <v>3187539.16</v>
       </c>
       <c r="Y577" t="n">
-        <v>82179.63</v>
+        <v>191808.12</v>
       </c>
       <c r="Z577" t="n">
-        <v>2621.53</v>
+        <v>6118.67</v>
       </c>
       <c r="AA577" t="n">
-        <v>84801.16</v>
+        <v>197926.79</v>
       </c>
       <c r="AB577" t="n">
-        <v>3105359.53</v>
+        <v>2995731.04</v>
       </c>
       <c r="AC577" t="n">
-        <v>0.02578152796717327</v>
+        <v>0.06017435719911281</v>
       </c>
     </row>
     <row r="578">
@@ -68034,19 +68034,19 @@
         <v>4324285.68</v>
       </c>
       <c r="Y578" t="n">
-        <v>70934.85000000001</v>
+        <v>170016.64</v>
       </c>
       <c r="Z578" t="n">
-        <v>2262.82</v>
+        <v>5423.52</v>
       </c>
       <c r="AA578" t="n">
-        <v>73197.67</v>
+        <v>175440.16</v>
       </c>
       <c r="AB578" t="n">
-        <v>4253350.83</v>
+        <v>4154269.04</v>
       </c>
       <c r="AC578" t="n">
-        <v>0.01640383065533265</v>
+        <v>0.03931669935368377</v>
       </c>
     </row>
     <row r="579">
@@ -68619,19 +68619,19 @@
         <v>3028048.96</v>
       </c>
       <c r="Y583" t="n">
-        <v>151508.22</v>
+        <v>317502.27</v>
       </c>
       <c r="Z583" t="n">
-        <v>4833.11</v>
+        <v>10128.32</v>
       </c>
       <c r="AA583" t="n">
-        <v>156341.33</v>
+        <v>327630.59</v>
       </c>
       <c r="AB583" t="n">
-        <v>2876540.74</v>
+        <v>2710546.69</v>
       </c>
       <c r="AC583" t="n">
-        <v>0.05003493074299565</v>
+        <v>0.1048537438443532</v>
       </c>
     </row>
     <row r="584">
@@ -68736,19 +68736,19 @@
         <v>6677404.33</v>
       </c>
       <c r="Y584" t="n">
-        <v>119550.83</v>
+        <v>295085.15</v>
       </c>
       <c r="Z584" t="n">
-        <v>3813.67</v>
+        <v>9413.209999999999</v>
       </c>
       <c r="AA584" t="n">
-        <v>123364.5</v>
+        <v>304498.36</v>
       </c>
       <c r="AB584" t="n">
-        <v>6557853.5</v>
+        <v>6382319.18</v>
       </c>
       <c r="AC584" t="n">
-        <v>0.01790378777317503</v>
+        <v>0.04419159532907901</v>
       </c>
     </row>
     <row r="585">
@@ -68881,6 +68881,12 @@
       <c r="D586" s="3" t="n">
         <v>46038</v>
       </c>
+      <c r="E586" s="3" t="n">
+        <v>46153</v>
+      </c>
+      <c r="F586" s="3" t="n">
+        <v>46640</v>
+      </c>
       <c r="G586" t="inlineStr">
         <is>
           <t>A Iniciar</t>
@@ -68937,7 +68943,7 @@
         </is>
       </c>
       <c r="R586" t="n">
-        <v>0</v>
+        <v>488</v>
       </c>
       <c r="S586" t="n">
         <v>0</v>
@@ -68946,7 +68952,7 @@
         <v>0</v>
       </c>
       <c r="U586" t="n">
-        <v>0</v>
+        <v>488</v>
       </c>
       <c r="V586" t="n">
         <v>10619818.83</v>
@@ -69805,9 +69811,15 @@
       <c r="D594" s="3" t="n">
         <v>46099</v>
       </c>
+      <c r="E594" s="3" t="n">
+        <v>46113</v>
+      </c>
+      <c r="F594" s="3" t="n">
+        <v>46832</v>
+      </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -69861,7 +69873,7 @@
         </is>
       </c>
       <c r="R594" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="S594" t="n">
         <v>0</v>
@@ -69870,7 +69882,7 @@
         <v>0</v>
       </c>
       <c r="U594" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="V594" t="n">
         <v>23052682.68</v>
@@ -70467,7 +70479,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>DO-009482014/2025</t>
+          <t>DO-009482014/2025-L1</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -70531,7 +70543,7 @@
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>Obra Rodoviária</t>
+          <t>Natureza continuada e/ou conserva</t>
         </is>
       </c>
       <c r="P600" t="inlineStr">
@@ -70584,7 +70596,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>DO-009482046/2025</t>
+          <t>DO-009482046/2025-L2</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -70648,7 +70660,7 @@
       </c>
       <c r="O601" t="inlineStr">
         <is>
-          <t>Obra Rodoviária</t>
+          <t>Natureza continuada e/ou conserva</t>
         </is>
       </c>
       <c r="P601" t="inlineStr">
@@ -70701,7 +70713,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>DO-9493205/2026</t>
+          <t>DO-9493205/2026-L4</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -70765,7 +70777,7 @@
       </c>
       <c r="O602" t="inlineStr">
         <is>
-          <t>Obra Rodoviária</t>
+          <t>Natureza continuada e/ou conserva</t>
         </is>
       </c>
       <c r="P602" t="inlineStr">
@@ -70818,7 +70830,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>D0-009482032/2025</t>
+          <t>D0-009482032/2025-L6</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -70882,7 +70894,7 @@
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t>Obra Rodoviária</t>
+          <t>Natureza continuada e/ou conserva</t>
         </is>
       </c>
       <c r="P603" t="inlineStr">
@@ -70935,7 +70947,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>DO-9481987/2025</t>
+          <t>DO-9481987/2025-L7</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -70999,7 +71011,7 @@
       </c>
       <c r="O604" t="inlineStr">
         <is>
-          <t>Obra Rodoviária</t>
+          <t>Natureza continuada e/ou conserva</t>
         </is>
       </c>
       <c r="P604" t="inlineStr">
@@ -71052,7 +71064,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>DO-009482055/2025</t>
+          <t>DO-009482055/2025-L5</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -71116,7 +71128,7 @@
       </c>
       <c r="O605" t="inlineStr">
         <is>
-          <t>Obra Rodoviária</t>
+          <t>Natureza continuada e/ou conserva</t>
         </is>
       </c>
       <c r="P605" t="inlineStr">
@@ -71169,7 +71181,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>DO-009482017/2025</t>
+          <t>DO-009482017/2025-L3</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -71233,7 +71245,7 @@
       </c>
       <c r="O606" t="inlineStr">
         <is>
-          <t>Obra Rodoviária</t>
+          <t>Natureza continuada e/ou conserva</t>
         </is>
       </c>
       <c r="P606" t="inlineStr">
@@ -71887,9 +71899,15 @@
       <c r="D612" s="3" t="n">
         <v>46125</v>
       </c>
+      <c r="E612" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="F612" s="3" t="n">
+        <v>46687</v>
+      </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -71943,7 +71961,7 @@
         </is>
       </c>
       <c r="R612" t="n">
-        <v>0</v>
+        <v>548</v>
       </c>
       <c r="S612" t="n">
         <v>0</v>
@@ -71952,7 +71970,7 @@
         <v>0</v>
       </c>
       <c r="U612" t="n">
-        <v>0</v>
+        <v>548</v>
       </c>
       <c r="V612" t="n">
         <v>5342582.88</v>
@@ -72216,21 +72234,21 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>DC-9501601/2026</t>
+          <t>AMA-9499286/2026</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>230152003725</t>
+          <t>Não Disponível</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>IMPLANTAÇÃO DE PONTES : TRECHO PINTÓPOLIS - URUCUIA (RODOVIA MG-202) PTS CÓRREGO GAMELEIRAS ,TABOCAS E RIBEIRÃO DAS PEDRAS</t>
+          <t>APOIO À SUPERVISÃO AMBIENTAL E AOS PROCEDIMENTOS DE GESTÃO E REGULARIZAÇÃO AMBIENTAL DOS EMPREENDIMENTOS RODOVIÁRIOS DO DER-MG</t>
         </is>
       </c>
       <c r="D615" s="3" t="n">
-        <v>46125</v>
+        <v>46108</v>
       </c>
       <c r="G615" t="inlineStr">
         <is>
@@ -72239,12 +72257,12 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t xml:space="preserve">S3 VEREDA CONSORCIO LTDA </t>
+          <t>STE SERVIÇOS TÉCNICOS DE ENGENHARIA S/A</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t>65300070000100</t>
+          <t>88849773000198</t>
         </is>
       </c>
       <c r="J615" t="inlineStr">
@@ -72254,12 +72272,12 @@
       </c>
       <c r="K615" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRETORIA DE CONSTRUÇÃO E OBRAS RODOVIÁRIAS </t>
+          <t>DER/DG/ASSESSORIA DE MEIO AMBIENTE</t>
         </is>
       </c>
       <c r="L615" t="inlineStr">
         <is>
-          <t>CONCORRÊNCIA ELETRÔNICA</t>
+          <t>Concorrência - Concorrência eletrônica</t>
         </is>
       </c>
       <c r="M615" t="inlineStr">
@@ -72269,22 +72287,22 @@
       </c>
       <c r="N615" t="inlineStr">
         <is>
-          <t>OAE</t>
+          <t>Estudos Ambientais</t>
         </is>
       </c>
       <c r="O615" t="inlineStr">
         <is>
-          <t>Obra Rodoviária</t>
+          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
         </is>
       </c>
       <c r="P615" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Implantação da Ponte sobre o Ribeirão das Pedras, dimensões  33,0 x 10,0m (Estaca 2.796+15,00),  Obra 2 - Implantação da Ponte sobre o Córrego das Tabocas, dimensões  59,0m x 10,0m (Estaca 3.514+6,00),  Obra 3 - Implantação da Ponte sobre o Córrego  da Gameleiras, dimensões  39,0m x 10,0m (Estaca 3.161+16,00)</t>
+          <t xml:space="preserve"> Obra 1 - Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários pertencentes ao DER-MG.</t>
         </is>
       </c>
       <c r="Q615" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Pintópolis,  Obra 2 - Pintópolis,  Obra 3 - Pintópolis</t>
+          <t xml:space="preserve"> Obra 1 - Belo Horizonte</t>
         </is>
       </c>
       <c r="R615" t="n">
@@ -72300,13 +72318,13 @@
         <v>0</v>
       </c>
       <c r="V615" t="n">
-        <v>9814000</v>
+        <v>0</v>
       </c>
       <c r="W615" t="n">
         <v>0</v>
       </c>
       <c r="X615" t="n">
-        <v>9814000</v>
+        <v>0</v>
       </c>
       <c r="Y615" t="n">
         <v>0</v>
@@ -72318,7 +72336,7 @@
         <v>0</v>
       </c>
       <c r="AB615" t="n">
-        <v>9814000</v>
+        <v>0</v>
       </c>
       <c r="AC615" t="n">
         <v>0</v>
@@ -72327,41 +72345,35 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>PO</t>
+          <t>DC-9501601/2026</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>230152003725</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>SERVIÇOS ESPECIAIS DE APOIO À COORDENAÇÃO E APOIO TÉCNICO NO PLANEJAMENTO, MONITORAMENTO E AVALIAÇÃO DO PORTIFÓLIO DE EMPREENDIMENTOS DO DER-MG</t>
+          <t>IMPLANTAÇÃO DE PONTES : TRECHO PINTÓPOLIS - URUCUIA (RODOVIA MG-202) PTS CÓRREGO GAMELEIRAS ,TABOCAS E RIBEIRÃO DAS PEDRAS</t>
         </is>
       </c>
       <c r="D616" s="3" t="n">
-        <v>45589</v>
-      </c>
-      <c r="E616" s="3" t="n">
-        <v>45628</v>
-      </c>
-      <c r="F616" s="3" t="n">
-        <v>46722</v>
+        <v>46125</v>
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>A Iniciar</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYSTRA ENGENHARIA E  CONSULTORIA LTDA </t>
+          <t xml:space="preserve">S3 VEREDA CONSORCIO LTDA </t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>52635422000307</t>
+          <t>65300070000100</t>
         </is>
       </c>
       <c r="J616" t="inlineStr">
@@ -72371,7 +72383,7 @@
       </c>
       <c r="K616" t="inlineStr">
         <is>
-          <t>ASSESSORIA DE GESTÃO ESTRATÉGICA</t>
+          <t xml:space="preserve">DIRETORIA DE CONSTRUÇÃO E OBRAS RODOVIÁRIAS </t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
@@ -72386,16 +72398,26 @@
       </c>
       <c r="N616" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>OAE</t>
         </is>
       </c>
       <c r="O616" t="inlineStr">
         <is>
-          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+          <t>Obra Rodoviária</t>
+        </is>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Implantação da Ponte sobre o Ribeirão das Pedras, dimensões  33,0 x 10,0m (Estaca 2.796+15,00),  Obra 2 - Implantação da Ponte sobre o Córrego das Tabocas, dimensões  59,0m x 10,0m (Estaca 3.514+6,00),  Obra 3 - Implantação da Ponte sobre o Córrego  da Gameleiras, dimensões  39,0m x 10,0m (Estaca 3.161+16,00)</t>
+        </is>
+      </c>
+      <c r="Q616" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Pintópolis,  Obra 2 - Pintópolis,  Obra 3 - Pintópolis</t>
         </is>
       </c>
       <c r="R616" t="n">
-        <v>1095</v>
+        <v>0</v>
       </c>
       <c r="S616" t="n">
         <v>0</v>
@@ -72404,16 +72426,16 @@
         <v>0</v>
       </c>
       <c r="U616" t="n">
-        <v>1095</v>
+        <v>0</v>
       </c>
       <c r="V616" t="n">
-        <v>5774752.44</v>
+        <v>9814000</v>
       </c>
       <c r="W616" t="n">
         <v>0</v>
       </c>
       <c r="X616" t="n">
-        <v>5774752.44</v>
+        <v>9814000</v>
       </c>
       <c r="Y616" t="n">
         <v>0</v>
@@ -72425,7 +72447,7 @@
         <v>0</v>
       </c>
       <c r="AB616" t="n">
-        <v>5774752.44</v>
+        <v>9814000</v>
       </c>
       <c r="AC616" t="n">
         <v>0</v>
@@ -72434,35 +72456,41 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>DO009482014/2025</t>
+          <t>DM-017/2024-A</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>230190100125</t>
+          <t>230176205123</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇO DE ENGENHARIA DE TRANSITO - LOTE 01 </t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 21ª URG</t>
         </is>
       </c>
       <c r="D617" s="3" t="n">
-        <v>45974</v>
+        <v>46141</v>
+      </c>
+      <c r="E617" s="3" t="n">
+        <v>46144</v>
+      </c>
+      <c r="F617" s="3" t="n">
+        <v>46874</v>
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+          <t>CONSÓRCIO AGR - CSR II</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
         <is>
-          <t>16502551000193</t>
+          <t>54879586000135</t>
         </is>
       </c>
       <c r="J617" t="inlineStr">
@@ -72472,12 +72500,12 @@
       </c>
       <c r="K617" t="inlineStr">
         <is>
-          <t>GERÊNCIA DE TRÂFEGO E SEGURANÇA VIÁRIA</t>
+          <t>DIRETORIA DE OPERAÇÕES</t>
         </is>
       </c>
       <c r="L617" t="inlineStr">
         <is>
-          <t>CONCORRÊNCIA ELETRÔNICA</t>
+          <t>RDC</t>
         </is>
       </c>
       <c r="M617" t="inlineStr">
@@ -72487,7 +72515,7 @@
       </c>
       <c r="N617" t="inlineStr">
         <is>
-          <t>Operação-Radar</t>
+          <t>Manutenção e Conservação</t>
         </is>
       </c>
       <c r="O617" t="inlineStr">
@@ -72495,8 +72523,18 @@
           <t>Natureza continuada e/ou conserva</t>
         </is>
       </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - MANUTENÇÃO E CONSERVAÇÃO - 21ª URG</t>
+        </is>
+      </c>
+      <c r="Q617" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Almenara, Bertópolis, Felisburgo, Fronteira dos Vales, Jacinto, Jequitinhonha, Joaíma, Machacalis, Palmópolis, Rio do Prado, Rubim, Santa Helena de Minas, Santa Maria do Salto, Santo Antônio do Jacinto, Umburatiba, Águas Formosas</t>
+        </is>
+      </c>
       <c r="R617" t="n">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="S617" t="n">
         <v>0</v>
@@ -72505,16 +72543,16 @@
         <v>0</v>
       </c>
       <c r="U617" t="n">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="V617" t="n">
-        <v>77898894.3</v>
+        <v>31813334.15</v>
       </c>
       <c r="W617" t="n">
         <v>0</v>
       </c>
       <c r="X617" t="n">
-        <v>77898894.3</v>
+        <v>31813334.15</v>
       </c>
       <c r="Y617" t="n">
         <v>0</v>
@@ -72526,7 +72564,7 @@
         <v>0</v>
       </c>
       <c r="AB617" t="n">
-        <v>77898894.3</v>
+        <v>31813334.15</v>
       </c>
       <c r="AC617" t="n">
         <v>0</v>
@@ -72535,35 +72573,41 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>AMA-9499286/2026</t>
+          <t>DM-014/2024-A</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>230176205123</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>APOIO À SUPERVISÃO AMBIENTAL E AOS PROCEDIMENTOS DE GESTÃO E REGULARIZAÇÃO AMBIENTAL DOS EMPREENDIMENTOS RODOVIÁRIOS DO DER-MG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 03ª URG</t>
         </is>
       </c>
       <c r="D618" s="3" t="n">
-        <v>46108</v>
+        <v>46140</v>
+      </c>
+      <c r="E618" s="3" t="n">
+        <v>46143</v>
+      </c>
+      <c r="F618" s="3" t="n">
+        <v>46873</v>
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>STE SERVIÇOS TÉCNICOS DE ENGENHARIA S/A</t>
+          <t>LOMAE MAQUINAS E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t>88849773000198</t>
+          <t>22026959000139</t>
         </is>
       </c>
       <c r="J618" t="inlineStr">
@@ -72573,12 +72617,12 @@
       </c>
       <c r="K618" t="inlineStr">
         <is>
-          <t>DER/DG/ASSESSORIA DE MEIO AMBIENTE</t>
+          <t>DIRETORIA DE OPERAÇÕES</t>
         </is>
       </c>
       <c r="L618" t="inlineStr">
         <is>
-          <t>Concorrência - Concorrência eletrônica</t>
+          <t>RDC</t>
         </is>
       </c>
       <c r="M618" t="inlineStr">
@@ -72588,16 +72632,26 @@
       </c>
       <c r="N618" t="inlineStr">
         <is>
-          <t>Estudos Ambientais</t>
+          <t>Manutenção e Conservação</t>
         </is>
       </c>
       <c r="O618" t="inlineStr">
         <is>
-          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - MANUTENÇÃO E CONSERVAÇÃO - 03ª URG</t>
+        </is>
+      </c>
+      <c r="Q618" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Araújos, Cachoeira da Prata, Carmo do Cajuru, Conceição do Pará, Divinópolis, Esmeraldas, Florestal, Fortuna de Minas, Igaratinga, Inhaúma, Itatiaiuçu, Itaúna, Leandro Ferreira, Maravilhas, Martinho Campos, Mateus Leme, Nova Serrana, Onça de Pitangui, Papagaios, Pará de Minas, Pequi, Perdigão, Pitangui, Pompéu, Ribeirão das Neves, Sete Lagoas, São Gonçalo do Pará, São José da Varginha</t>
         </is>
       </c>
       <c r="R618" t="n">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="S618" t="n">
         <v>0</v>
@@ -72606,16 +72660,16 @@
         <v>0</v>
       </c>
       <c r="U618" t="n">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="V618" t="n">
-        <v>0</v>
+        <v>36950516.6</v>
       </c>
       <c r="W618" t="n">
         <v>0</v>
       </c>
       <c r="X618" t="n">
-        <v>0</v>
+        <v>36950516.6</v>
       </c>
       <c r="Y618" t="n">
         <v>0</v>
@@ -72627,7 +72681,7 @@
         <v>0</v>
       </c>
       <c r="AB618" t="n">
-        <v>0</v>
+        <v>36950516.6</v>
       </c>
       <c r="AC618" t="n">
         <v>0</v>
@@ -72636,106 +72690,426 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
+          <t>PRC-29.008/2017-E</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>2301762000016/17</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>APOIO AO GERENCIAMENTO, OPERAÇÃO E FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="D619" s="3" t="n">
+        <v>46122</v>
+      </c>
+      <c r="E619" s="3" t="n">
+        <v>46125</v>
+      </c>
+      <c r="F619" s="3" t="n">
+        <v>46489</v>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>16502551000193</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>DIRETORIA DE FISCALIZAÇÃO</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>Consultoria / Assessoramento</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - serviços de engenharia de natureza continua, apio ao gerenciamento, operação e fiscalização do transito.</t>
+        </is>
+      </c>
+      <c r="Q619" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Brasília de Minas, Mirabela, Montes Claros</t>
+        </is>
+      </c>
+      <c r="R619" t="n">
+        <v>365</v>
+      </c>
+      <c r="S619" t="n">
+        <v>0</v>
+      </c>
+      <c r="T619" t="n">
+        <v>0</v>
+      </c>
+      <c r="U619" t="n">
+        <v>365</v>
+      </c>
+      <c r="V619" t="n">
+        <v>4506718.06</v>
+      </c>
+      <c r="W619" t="n">
+        <v>0</v>
+      </c>
+      <c r="X619" t="n">
+        <v>4506718.06</v>
+      </c>
+      <c r="Y619" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z619" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA619" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB619" t="n">
+        <v>4506718.06</v>
+      </c>
+      <c r="AC619" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Não Disponível</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>SERVIÇOS ESPECIAIS DE APOIO À COORDENAÇÃO E APOIO TÉCNICO NO PLANEJAMENTO, MONITORAMENTO E AVALIAÇÃO DO PORTIFÓLIO DE EMPREENDIMENTOS DO DER-MG</t>
+        </is>
+      </c>
+      <c r="D620" s="3" t="n">
+        <v>45589</v>
+      </c>
+      <c r="E620" s="3" t="n">
+        <v>45628</v>
+      </c>
+      <c r="F620" s="3" t="n">
+        <v>46722</v>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYSTRA ENGENHARIA E  CONSULTORIA LTDA </t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>52635422000307</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>ASSESSORIA DE GESTÃO ESTRATÉGICA</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>Consultoria</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+        </is>
+      </c>
+      <c r="R620" t="n">
+        <v>1095</v>
+      </c>
+      <c r="S620" t="n">
+        <v>0</v>
+      </c>
+      <c r="T620" t="n">
+        <v>0</v>
+      </c>
+      <c r="U620" t="n">
+        <v>1095</v>
+      </c>
+      <c r="V620" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="W620" t="n">
+        <v>0</v>
+      </c>
+      <c r="X620" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="Y620" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z620" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA620" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB620" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="AC620" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>DO009482014/2025</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>230190100125</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇO DE ENGENHARIA DE TRANSITO - LOTE 01 </t>
+        </is>
+      </c>
+      <c r="D621" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>A Iniciar</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>16502551000193</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>GERÊNCIA DE TRÂFEGO E SEGURANÇA VIÁRIA</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="R621" t="n">
+        <v>0</v>
+      </c>
+      <c r="S621" t="n">
+        <v>0</v>
+      </c>
+      <c r="T621" t="n">
+        <v>0</v>
+      </c>
+      <c r="U621" t="n">
+        <v>0</v>
+      </c>
+      <c r="V621" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="W621" t="n">
+        <v>0</v>
+      </c>
+      <c r="X621" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="Y621" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z621" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA621" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB621" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="AC621" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
           <t>DP-001/2023</t>
         </is>
       </c>
-      <c r="B619" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>2301601000022020</t>
         </is>
       </c>
-      <c r="C619" t="inlineStr">
+      <c r="C622" t="inlineStr">
         <is>
           <t>ELABORAÇÃO DE PROJETO DE ENGENHARIA RODOVIÁRIA DE MELHORAMENTOS, PAVIMENTAÇÃO E OAE - LOTE 2</t>
         </is>
       </c>
-      <c r="D619" s="3" t="n">
+      <c r="D622" s="3" t="n">
         <v>45166</v>
       </c>
-      <c r="G619" t="inlineStr">
+      <c r="G622" t="inlineStr">
         <is>
           <t>A Iniciar</t>
         </is>
       </c>
-      <c r="H619" t="inlineStr">
+      <c r="H622" t="inlineStr">
         <is>
           <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
-      <c r="I619" t="inlineStr">
+      <c r="I622" t="inlineStr">
         <is>
           <t>38743357000132</t>
         </is>
       </c>
-      <c r="J619" t="inlineStr">
+      <c r="J622" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr">
+      <c r="K622" t="inlineStr">
         <is>
           <t>DIRETORIA DE PROJETOS</t>
         </is>
       </c>
-      <c r="L619" t="inlineStr">
+      <c r="L622" t="inlineStr">
         <is>
           <t>RDC</t>
         </is>
       </c>
-      <c r="M619" t="inlineStr">
+      <c r="M622" t="inlineStr">
         <is>
           <t>EMPREITADA POR PREÇO UNITÁRIO</t>
         </is>
       </c>
-      <c r="N619" t="inlineStr">
+      <c r="N622" t="inlineStr">
         <is>
           <t>Consultoria para Projetos</t>
         </is>
       </c>
-      <c r="O619" t="inlineStr">
+      <c r="O622" t="inlineStr">
         <is>
           <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
         </is>
       </c>
-      <c r="R619" t="n">
-        <v>0</v>
-      </c>
-      <c r="S619" t="n">
-        <v>0</v>
-      </c>
-      <c r="T619" t="n">
-        <v>0</v>
-      </c>
-      <c r="U619" t="n">
-        <v>0</v>
-      </c>
-      <c r="V619" t="n">
+      <c r="R622" t="n">
+        <v>0</v>
+      </c>
+      <c r="S622" t="n">
+        <v>0</v>
+      </c>
+      <c r="T622" t="n">
+        <v>0</v>
+      </c>
+      <c r="U622" t="n">
+        <v>0</v>
+      </c>
+      <c r="V622" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="W619" t="n">
-        <v>0</v>
-      </c>
-      <c r="X619" t="n">
+      <c r="W622" t="n">
+        <v>0</v>
+      </c>
+      <c r="X622" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="Y619" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z619" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA619" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB619" t="n">
+      <c r="Y622" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z622" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA622" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB622" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="AC619" t="n">
+      <c r="AC622" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC619"/>
+  <autoFilter ref="A1:AC622"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/contratos.xlsx
+++ b/upload/contratos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AC$622</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AC$625</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC622"/>
+  <dimension ref="A1:AC625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2273,7 +2273,7 @@
         <v>44524</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46189</v>
+        <v>46196</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1306</v>
+        <v>1313</v>
       </c>
       <c r="U16" t="n">
-        <v>1666</v>
+        <v>1673</v>
       </c>
       <c r="V16" t="n">
         <v>1452371.99</v>
@@ -12200,7 +12200,7 @@
         <v>44850</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>46147</v>
+        <v>46154</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -12264,10 +12264,10 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="U101" t="n">
-        <v>1298</v>
+        <v>1305</v>
       </c>
       <c r="V101" t="n">
         <v>1365885.84</v>
@@ -15827,7 +15827,7 @@
         <v>45026</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -15891,10 +15891,10 @@
         <v>510</v>
       </c>
       <c r="T132" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="U132" t="n">
-        <v>1125</v>
+        <v>1132</v>
       </c>
       <c r="V132" t="n">
         <v>19915653.29</v>
@@ -24017,7 +24017,7 @@
         <v>44767</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>46245</v>
+        <v>46252</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -24081,10 +24081,10 @@
         <v>0</v>
       </c>
       <c r="T202" t="n">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="U202" t="n">
-        <v>1479</v>
+        <v>1486</v>
       </c>
       <c r="V202" t="n">
         <v>2519553.4</v>
@@ -26819,7 +26819,7 @@
         <v>44810</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>46166</v>
+        <v>46173</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -26883,10 +26883,10 @@
         <v>0</v>
       </c>
       <c r="T226" t="n">
-        <v>1176</v>
+        <v>1183</v>
       </c>
       <c r="U226" t="n">
-        <v>1357</v>
+        <v>1364</v>
       </c>
       <c r="V226" t="n">
         <v>1559477.28</v>
@@ -28457,7 +28457,7 @@
         <v>44579</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>46362</v>
+        <v>46369</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -28521,10 +28521,10 @@
         <v>180</v>
       </c>
       <c r="T240" t="n">
-        <v>1244</v>
+        <v>1251</v>
       </c>
       <c r="U240" t="n">
-        <v>1784</v>
+        <v>1791</v>
       </c>
       <c r="V240" t="n">
         <v>1175120.88</v>
@@ -37097,7 +37097,7 @@
         <v>45384</v>
       </c>
       <c r="F314" s="3" t="n">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -37161,10 +37161,10 @@
         <v>330</v>
       </c>
       <c r="T314" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="U314" t="n">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="V314" t="n">
         <v>2816620.4</v>
@@ -40373,7 +40373,7 @@
         <v>45110</v>
       </c>
       <c r="F342" s="3" t="n">
-        <v>46165</v>
+        <v>46172</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -40437,10 +40437,10 @@
         <v>398</v>
       </c>
       <c r="T342" t="n">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="U342" t="n">
-        <v>1056</v>
+        <v>1063</v>
       </c>
       <c r="V342" t="n">
         <v>3655796.23</v>
@@ -42479,7 +42479,7 @@
         <v>45236</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>46159</v>
+        <v>46166</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -42543,10 +42543,10 @@
         <v>480</v>
       </c>
       <c r="T360" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="U360" t="n">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="V360" t="n">
         <v>5042730.21</v>
@@ -43649,7 +43649,7 @@
         <v>45236</v>
       </c>
       <c r="F370" s="3" t="n">
-        <v>46151</v>
+        <v>46158</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
@@ -43713,10 +43713,10 @@
         <v>510</v>
       </c>
       <c r="T370" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="U370" t="n">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="V370" t="n">
         <v>7889881.67</v>
@@ -44936,7 +44936,7 @@
         <v>45231</v>
       </c>
       <c r="F381" s="3" t="n">
-        <v>46142</v>
+        <v>46387</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
@@ -44997,13 +44997,13 @@
         <v>912</v>
       </c>
       <c r="S381" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="T381" t="n">
         <v>0</v>
       </c>
       <c r="U381" t="n">
-        <v>912</v>
+        <v>1157</v>
       </c>
       <c r="V381" t="n">
         <v>7576922.1</v>
@@ -45170,7 +45170,7 @@
         <v>45237</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -45234,10 +45234,10 @@
         <v>510</v>
       </c>
       <c r="T383" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="U383" t="n">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="V383" t="n">
         <v>4065559.6</v>
@@ -50427,7 +50427,7 @@
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -50502,19 +50502,19 @@
         <v>38819029.96</v>
       </c>
       <c r="Y428" t="n">
-        <v>34740432.66</v>
+        <v>35394992.2</v>
       </c>
       <c r="Z428" t="n">
-        <v>2122047.18</v>
+        <v>2174619.26</v>
       </c>
       <c r="AA428" t="n">
-        <v>36862479.84</v>
+        <v>37569611.46</v>
       </c>
       <c r="AB428" t="n">
-        <v>4078597.3</v>
+        <v>3424037.76</v>
       </c>
       <c r="AC428" t="n">
-        <v>0.8949330443289624</v>
+        <v>0.9117948654686063</v>
       </c>
     </row>
     <row r="429">
@@ -50891,7 +50891,7 @@
         <v>45383</v>
       </c>
       <c r="F432" s="3" t="n">
-        <v>46112</v>
+        <v>46262</v>
       </c>
       <c r="G432" t="inlineStr">
         <is>
@@ -50952,22 +50952,22 @@
         <v>730</v>
       </c>
       <c r="S432" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="T432" t="n">
         <v>0</v>
       </c>
       <c r="U432" t="n">
-        <v>730</v>
+        <v>880</v>
       </c>
       <c r="V432" t="n">
         <v>1425000</v>
       </c>
       <c r="W432" t="n">
-        <v>0</v>
+        <v>-11585.2</v>
       </c>
       <c r="X432" t="n">
-        <v>1425000</v>
+        <v>1413414.8</v>
       </c>
       <c r="Y432" t="n">
         <v>1051152.96</v>
@@ -50979,10 +50979,10 @@
         <v>1112012</v>
       </c>
       <c r="AB432" t="n">
-        <v>373847.04</v>
+        <v>362261.84</v>
       </c>
       <c r="AC432" t="n">
-        <v>0.7376512</v>
+        <v>0.743697434044132</v>
       </c>
     </row>
     <row r="433">
@@ -51906,19 +51906,19 @@
         <v>41801980.63</v>
       </c>
       <c r="Y440" t="n">
-        <v>37778568.04</v>
+        <v>38850140.53</v>
       </c>
       <c r="Z440" t="n">
-        <v>2690060.18</v>
+        <v>2809692.02</v>
       </c>
       <c r="AA440" t="n">
-        <v>40468628.22</v>
+        <v>41659832.55</v>
       </c>
       <c r="AB440" t="n">
-        <v>4023412.59</v>
+        <v>2951840.1</v>
       </c>
       <c r="AC440" t="n">
-        <v>0.9037506709164752</v>
+        <v>0.9293851617671542</v>
       </c>
     </row>
     <row r="441">
@@ -55065,19 +55065,19 @@
         <v>52604103.19</v>
       </c>
       <c r="Y467" t="n">
-        <v>33806452.17</v>
+        <v>35353156.02</v>
       </c>
       <c r="Z467" t="n">
-        <v>1522593.9</v>
+        <v>1631513.09</v>
       </c>
       <c r="AA467" t="n">
-        <v>35329046.07</v>
+        <v>36984669.11</v>
       </c>
       <c r="AB467" t="n">
-        <v>18797651.02</v>
+        <v>17250947.17</v>
       </c>
       <c r="AC467" t="n">
-        <v>0.6426580840641835</v>
+        <v>0.672060806593517</v>
       </c>
     </row>
     <row r="468">
@@ -56150,7 +56150,7 @@
         <v>45573</v>
       </c>
       <c r="F477" s="3" t="n">
-        <v>46218</v>
+        <v>46225</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
@@ -56214,10 +56214,10 @@
         <v>0</v>
       </c>
       <c r="T477" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="U477" t="n">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="V477" t="n">
         <v>3876550</v>
@@ -56267,7 +56267,7 @@
         <v>45618</v>
       </c>
       <c r="F478" s="3" t="n">
-        <v>46165</v>
+        <v>46288</v>
       </c>
       <c r="G478" t="inlineStr">
         <is>
@@ -56328,13 +56328,13 @@
         <v>365</v>
       </c>
       <c r="S478" t="n">
-        <v>152</v>
+        <v>275</v>
       </c>
       <c r="T478" t="n">
         <v>31</v>
       </c>
       <c r="U478" t="n">
-        <v>548</v>
+        <v>671</v>
       </c>
       <c r="V478" t="n">
         <v>859769.01</v>
@@ -56931,19 +56931,19 @@
         <v>7278955.82</v>
       </c>
       <c r="Y483" t="n">
-        <v>4953180.67</v>
+        <v>4994918.17</v>
       </c>
       <c r="Z483" t="n">
         <v>0</v>
       </c>
       <c r="AA483" t="n">
-        <v>4953180.67</v>
+        <v>4994918.17</v>
       </c>
       <c r="AB483" t="n">
-        <v>2325775.15</v>
+        <v>2284037.65</v>
       </c>
       <c r="AC483" t="n">
-        <v>0.6804795622457838</v>
+        <v>0.6862135577572444</v>
       </c>
     </row>
     <row r="484">
@@ -57516,19 +57516,19 @@
         <v>163158631.5</v>
       </c>
       <c r="Y488" t="n">
-        <v>63921067.03</v>
+        <v>72861330.43000001</v>
       </c>
       <c r="Z488" t="n">
-        <v>2481341.16</v>
+        <v>3038361.41</v>
       </c>
       <c r="AA488" t="n">
-        <v>66402408.19</v>
+        <v>75899691.84</v>
       </c>
       <c r="AB488" t="n">
-        <v>99237564.47</v>
+        <v>90297301.06999999</v>
       </c>
       <c r="AC488" t="n">
-        <v>0.391772512691123</v>
+        <v>0.4465674280309221</v>
       </c>
     </row>
     <row r="489">
@@ -59622,19 +59622,19 @@
         <v>2540551.02</v>
       </c>
       <c r="Y506" t="n">
-        <v>129788.89</v>
+        <v>143989.05</v>
       </c>
       <c r="Z506" t="n">
-        <v>5961.25</v>
+        <v>7014.9</v>
       </c>
       <c r="AA506" t="n">
-        <v>135750.14</v>
+        <v>151003.95</v>
       </c>
       <c r="AB506" t="n">
-        <v>2410762.13</v>
+        <v>2396561.97</v>
       </c>
       <c r="AC506" t="n">
-        <v>0.05108690554854513</v>
+        <v>0.05667630717370911</v>
       </c>
     </row>
     <row r="507">
@@ -62313,19 +62313,19 @@
         <v>3900717.4</v>
       </c>
       <c r="Y529" t="n">
-        <v>1798925.05</v>
+        <v>2016899.4</v>
       </c>
       <c r="Z529" t="n">
-        <v>917991.39</v>
+        <v>1029223.7</v>
       </c>
       <c r="AA529" t="n">
-        <v>2716916.44</v>
+        <v>3046123.1</v>
       </c>
       <c r="AB529" t="n">
-        <v>2101792.35</v>
+        <v>1883818</v>
       </c>
       <c r="AC529" t="n">
-        <v>0.4611780002314446</v>
+        <v>0.5170585800447887</v>
       </c>
     </row>
     <row r="530">
@@ -62430,19 +62430,19 @@
         <v>1346346.46</v>
       </c>
       <c r="Y530" t="n">
-        <v>131945.13</v>
+        <v>172156.59</v>
       </c>
       <c r="Z530" t="n">
-        <v>5409.74</v>
+        <v>8393.43</v>
       </c>
       <c r="AA530" t="n">
-        <v>137354.87</v>
+        <v>180550.02</v>
       </c>
       <c r="AB530" t="n">
-        <v>1214401.33</v>
+        <v>1174189.87</v>
       </c>
       <c r="AC530" t="n">
-        <v>0.09800235966008333</v>
+        <v>0.1278694564250572</v>
       </c>
     </row>
     <row r="531">
@@ -63243,19 +63243,19 @@
         <v>44573000</v>
       </c>
       <c r="Y537" t="n">
-        <v>4670098.83</v>
+        <v>5120476.8</v>
       </c>
       <c r="Z537" t="n">
-        <v>66649.77</v>
+        <v>77902.28999999999</v>
       </c>
       <c r="AA537" t="n">
-        <v>4736748.6</v>
+        <v>5198379.09</v>
       </c>
       <c r="AB537" t="n">
-        <v>39902901.17</v>
+        <v>39452523.2</v>
       </c>
       <c r="AC537" t="n">
-        <v>0.1047741644044601</v>
+        <v>0.1148784421062078</v>
       </c>
     </row>
     <row r="538">
@@ -63594,19 +63594,19 @@
         <v>22458906.7</v>
       </c>
       <c r="Y540" t="n">
-        <v>1487538.65</v>
+        <v>1773004.43</v>
       </c>
       <c r="Z540" t="n">
-        <v>35530.91</v>
+        <v>45836.21</v>
       </c>
       <c r="AA540" t="n">
-        <v>1523069.56</v>
+        <v>1818840.64</v>
       </c>
       <c r="AB540" t="n">
-        <v>20971368.05</v>
+        <v>20685902.27</v>
       </c>
       <c r="AC540" t="n">
-        <v>0.06623379623372316</v>
+        <v>0.07894437844563466</v>
       </c>
     </row>
     <row r="541">
@@ -63711,19 +63711,19 @@
         <v>30872072.3</v>
       </c>
       <c r="Y541" t="n">
-        <v>3733445.15</v>
+        <v>4321961.53</v>
       </c>
       <c r="Z541" t="n">
-        <v>90400.14999999999</v>
+        <v>111645.58</v>
       </c>
       <c r="AA541" t="n">
-        <v>3823845.3</v>
+        <v>4433607.11</v>
       </c>
       <c r="AB541" t="n">
-        <v>27138627.15</v>
+        <v>26550110.77</v>
       </c>
       <c r="AC541" t="n">
-        <v>0.1209327677688809</v>
+        <v>0.1399958346819497</v>
       </c>
     </row>
     <row r="542">
@@ -65226,19 +65226,19 @@
         <v>9634126.24</v>
       </c>
       <c r="Y554" t="n">
-        <v>4736694.87</v>
+        <v>5546633.76</v>
       </c>
       <c r="Z554" t="n">
-        <v>90981.28999999999</v>
+        <v>110994.77</v>
       </c>
       <c r="AA554" t="n">
-        <v>4827676.16</v>
+        <v>5657628.53</v>
       </c>
       <c r="AB554" t="n">
-        <v>4897431.37</v>
+        <v>4087492.48</v>
       </c>
       <c r="AC554" t="n">
-        <v>0.4916579617084195</v>
+        <v>0.5757277434222203</v>
       </c>
     </row>
     <row r="555">
@@ -66864,19 +66864,19 @@
         <v>12159273.83</v>
       </c>
       <c r="Y568" t="n">
-        <v>3823205.97</v>
+        <v>4563869.02</v>
       </c>
       <c r="Z568" t="n">
-        <v>313522.25</v>
+        <v>399359.72</v>
       </c>
       <c r="AA568" t="n">
-        <v>4136728.22</v>
+        <v>4963228.74</v>
       </c>
       <c r="AB568" t="n">
-        <v>8336067.86</v>
+        <v>7595404.81</v>
       </c>
       <c r="AC568" t="n">
-        <v>0.3144271626293328</v>
+        <v>0.3753405905490657</v>
       </c>
     </row>
     <row r="569">
@@ -67683,19 +67683,19 @@
         <v>18749931.77</v>
       </c>
       <c r="Y575" t="n">
-        <v>2160121.29</v>
+        <v>2951267.99</v>
       </c>
       <c r="Z575" t="n">
-        <v>458510.34</v>
+        <v>626313.58</v>
       </c>
       <c r="AA575" t="n">
-        <v>2618631.63</v>
+        <v>3577581.57</v>
       </c>
       <c r="AB575" t="n">
-        <v>16589810.48</v>
+        <v>15798663.78</v>
       </c>
       <c r="AC575" t="n">
-        <v>0.1152068880301851</v>
+        <v>0.1574015322403491</v>
       </c>
     </row>
     <row r="576">
@@ -68502,19 +68502,19 @@
         <v>15304996.19</v>
       </c>
       <c r="Y582" t="n">
-        <v>1636050.93</v>
+        <v>3776564.13</v>
       </c>
       <c r="Z582" t="n">
-        <v>184473.31</v>
+        <v>359723.53</v>
       </c>
       <c r="AA582" t="n">
-        <v>1820524.24</v>
+        <v>4136287.66</v>
       </c>
       <c r="AB582" t="n">
-        <v>13668945.26</v>
+        <v>11528432.06</v>
       </c>
       <c r="AC582" t="n">
-        <v>0.1068965264472895</v>
+        <v>0.2467536798517818</v>
       </c>
     </row>
     <row r="583">
@@ -68889,7 +68889,7 @@
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
@@ -69894,19 +69894,19 @@
         <v>23052682.68</v>
       </c>
       <c r="Y594" t="n">
-        <v>0</v>
+        <v>544858.86</v>
       </c>
       <c r="Z594" t="n">
         <v>0</v>
       </c>
       <c r="AA594" t="n">
-        <v>0</v>
+        <v>544858.86</v>
       </c>
       <c r="AB594" t="n">
-        <v>23052682.68</v>
+        <v>22507823.82</v>
       </c>
       <c r="AC594" t="n">
-        <v>0</v>
+        <v>0.02363537760716706</v>
       </c>
     </row>
     <row r="595">
@@ -70267,9 +70267,15 @@
       <c r="D598" s="3" t="n">
         <v>46101</v>
       </c>
+      <c r="E598" s="3" t="n">
+        <v>46153</v>
+      </c>
+      <c r="F598" s="3" t="n">
+        <v>46609</v>
+      </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -70323,7 +70329,7 @@
         </is>
       </c>
       <c r="R598" t="n">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="S598" t="n">
         <v>0</v>
@@ -70332,7 +70338,7 @@
         <v>0</v>
       </c>
       <c r="U598" t="n">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="V598" t="n">
         <v>14264750.82</v>
@@ -70670,7 +70676,7 @@
       </c>
       <c r="Q601" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Aiuruoca, Antônio Carlos, Barbacena, Boa Esperança, Bocaina de Minas, Brazópolis, Cambuí, Campo do Meio, Careaçu, Conceição do Rio Verde, Delfim Moreira, Entre Rios de Minas, Espírito Santo do Dourado, Itajubá, Jesuânia, Lagoa Dourada, Pouso Alegre, Rio Espera, São João Del Rei, São João da Mata, São Tomé das Letras, Três Corações</t>
+          <t xml:space="preserve"> Obra 1 - Aiuruoca, Antônio Carlos, Barbacena, Boa Esperança, Bocaina de Minas, Brazópolis, Cambuí, Campo do Meio, Careaçu, Conceição do Rio Verde, Delfim Moreira, Entre Rios de Minas, Espírito Santo do Dourado, Itajubá, Jesuânia, Lagoa Dourada, Pouso Alegre, Rio Espera, São João Del Rei, São João da Mata, São Tomé das Letras, Três Corações, Vera Cruz</t>
         </is>
       </c>
       <c r="R601" t="n">
@@ -70787,7 +70793,7 @@
       </c>
       <c r="Q602" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Bocaiúva, Bonfinópolis de Minas, Buritis, Curvelo, Felixlândia, Francisco Sá, Grão Mogol, Icaraí de Minas, Januária, Japonvar, João Pinheiro, Lagoa dos Patos, Lassance, Mirabela, Monte Azul, Montes Claros, Pedras de Maria da Cruz, Ponto Chique, Porteirinha, Riacho dos Machados, Unaí, Várzea da Palma</t>
+          <t xml:space="preserve"> Obra 1 - Belo Horizonte, Bocaiúva, Bonfinópolis de Minas, Buritis, Curvelo, Felixlândia, Francisco Sá, Grão Mogol, Icaraí de Minas, Januária, Japonvar, João Pinheiro, Lagoa dos Patos, Lassance, Mirabela, Monte Azul, Montes Claros, Pedras de Maria da Cruz, Ponto Chique, Porteirinha, Riacho dos Machados, Unaí, Várzea da Palma</t>
         </is>
       </c>
       <c r="R602" t="n">
@@ -70904,7 +70910,7 @@
       </c>
       <c r="Q603" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Açucena, Caputira, Cataguases, Dionísio, Dom Silvério, Faria Lemos, Guiricema, Inhapim, Itabira, Muriaé, Mutum, Nova Era, Ouro Preto, Paula Cândido, Piraúba, Raul Soares, Reduto, Rio Piracicaba, Santa Maria de Itabira, São Domingos das Dores, São Geraldo, São Pedro dos Ferros, Tabuleiro, Teixeiras, Viçosa</t>
+          <t xml:space="preserve"> Obra 1 - Açucena, Belo Horizonte, Caputira, Cataguases, Dionísio, Dom Silvério, Faria Lemos, Guiricema, Inhapim, Itabira, Muriaé, Mutum, Nova Era, Ouro Preto, Paula Cândido, Piraúba, Raul Soares, Reduto, Rio Piracicaba, Santa Maria de Itabira, São Domingos das Dores, São Geraldo, São Pedro dos Ferros, Tabuleiro, Teixeiras, Viçosa</t>
         </is>
       </c>
       <c r="R603" t="n">
@@ -71138,7 +71144,7 @@
       </c>
       <c r="Q605" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Alvorada de Minas, Araçuaí, Capelinha, Carbonita, Carlos Chagas, Coluna, Conceição do Mato Dentro, Diamantina, Dom Joaquim, Fronteira dos Vales, Fruta de Leite, Gouvea, Governador Valadares, Jacinto, José Gonçalves de Minas, José Raydan, Malacacheta, Mata Verde, Montezuma, Nanuque, Ponto dos Volantes, Rio Pardo de Minas, Salinas, Senhora do Porto, São João do Manteninha, Umburatiba, Virginópolis, Água Boa</t>
+          <t xml:space="preserve"> Obra 1 - Alvorada de Minas, Araçuaí, Belo Horizonte, Capelinha, Carbonita, Carlos Chagas, Coluna, Conceição do Mato Dentro, Diamantina, Dom Joaquim, Fronteira dos Vales, Fruta de Leite, Gouvea, Governador Valadares, Jacinto, José Gonçalves de Minas, José Raydan, Malacacheta, Mata Verde, Montezuma, Nanuque, Ponto dos Volantes, Rio Pardo de Minas, Salinas, Senhora do Porto, São João do Manteninha, Umburatiba, Virginópolis, Água Boa</t>
         </is>
       </c>
       <c r="R605" t="n">
@@ -71255,7 +71261,7 @@
       </c>
       <c r="Q606" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Abadia dos Dourados, Alpinópolis, Alterosa, Arceburgo, Campina Verde, Capetinga, Conceição da Aparecida, Coromandel, Cássia, Delta, Ibiá, Ituiutaba, Monte Carmelo, Paracatu, Presidente Olegário, Sacramento, Serra do Salitre, Tapira, Uberaba, Uberlândia, Unaí</t>
+          <t xml:space="preserve"> Obra 1 - Abadia dos Dourados, Alpinópolis, Alterosa, Arceburgo, Belo Horizonte, Campina Verde, Capetinga, Conceição da Aparecida, Coromandel, Cássia, Delta, Ibiá, Ituiutaba, Monte Carmelo, Paracatu, Presidente Olegário, Sacramento, Serra do Salitre, Tapira, Uberaba, Uberlândia, Unaí</t>
         </is>
       </c>
       <c r="R606" t="n">
@@ -71982,19 +71988,19 @@
         <v>5342582.88</v>
       </c>
       <c r="Y612" t="n">
-        <v>0</v>
+        <v>1552.5</v>
       </c>
       <c r="Z612" t="n">
         <v>0</v>
       </c>
       <c r="AA612" t="n">
-        <v>0</v>
+        <v>1552.5</v>
       </c>
       <c r="AB612" t="n">
-        <v>5342582.88</v>
+        <v>5341030.38</v>
       </c>
       <c r="AC612" t="n">
-        <v>0</v>
+        <v>0.0002905897830451626</v>
       </c>
     </row>
     <row r="613">
@@ -72099,19 +72105,19 @@
         <v>36954174.97</v>
       </c>
       <c r="Y613" t="n">
-        <v>0</v>
+        <v>1155443.59</v>
       </c>
       <c r="Z613" t="n">
-        <v>0</v>
+        <v>124341.92</v>
       </c>
       <c r="AA613" t="n">
-        <v>0</v>
+        <v>1279785.51</v>
       </c>
       <c r="AB613" t="n">
-        <v>36954174.97</v>
+        <v>35798731.38</v>
       </c>
       <c r="AC613" t="n">
-        <v>0</v>
+        <v>0.03126692967541578</v>
       </c>
     </row>
     <row r="614">
@@ -72285,11 +72291,6 @@
           <t>EMPREITADA POR PREÇO UNITÁRIO</t>
         </is>
       </c>
-      <c r="N615" t="inlineStr">
-        <is>
-          <t>Estudos Ambientais</t>
-        </is>
-      </c>
       <c r="O615" t="inlineStr">
         <is>
           <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
@@ -72807,41 +72808,35 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>PO</t>
+          <t>DC-9505062/2026</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>230152004425</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>SERVIÇOS ESPECIAIS DE APOIO À COORDENAÇÃO E APOIO TÉCNICO NO PLANEJAMENTO, MONITORAMENTO E AVALIAÇÃO DO PORTIFÓLIO DE EMPREENDIMENTOS DO DER-MG</t>
+          <t>CONSTRUÇÃO DA PONTE SOBRE O RIO CORRENTE, NO TRECHO DE MUNHOZ - TOLEDO, RODOVIA MG-460, COM 34,00M DE EXTENSÃO.</t>
         </is>
       </c>
       <c r="D620" s="3" t="n">
-        <v>45589</v>
-      </c>
-      <c r="E620" s="3" t="n">
-        <v>45628</v>
-      </c>
-      <c r="F620" s="3" t="n">
-        <v>46722</v>
+        <v>46146</v>
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>A Iniciar</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYSTRA ENGENHARIA E  CONSULTORIA LTDA </t>
+          <t>S3 CONSTRUTORA LTDA</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t>52635422000307</t>
+          <t>23785668000197</t>
         </is>
       </c>
       <c r="J620" t="inlineStr">
@@ -72851,7 +72846,7 @@
       </c>
       <c r="K620" t="inlineStr">
         <is>
-          <t>ASSESSORIA DE GESTÃO ESTRATÉGICA</t>
+          <t xml:space="preserve">DIRETORIA DE CONSTRUÇÃO E OBRAS RODOVIÁRIAS </t>
         </is>
       </c>
       <c r="L620" t="inlineStr">
@@ -72866,16 +72861,26 @@
       </c>
       <c r="N620" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>OAE</t>
         </is>
       </c>
       <c r="O620" t="inlineStr">
         <is>
-          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+          <t>Obra Rodoviária</t>
+        </is>
+      </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Construção da Ponte sobre o Rio Corrente, no trecho de Munhoz - Toledo, rodovia MG-460, com 34,00m de extensão</t>
+        </is>
+      </c>
+      <c r="Q620" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Munhoz</t>
         </is>
       </c>
       <c r="R620" t="n">
-        <v>1095</v>
+        <v>0</v>
       </c>
       <c r="S620" t="n">
         <v>0</v>
@@ -72884,16 +72889,16 @@
         <v>0</v>
       </c>
       <c r="U620" t="n">
-        <v>1095</v>
+        <v>0</v>
       </c>
       <c r="V620" t="n">
-        <v>5774752.44</v>
+        <v>2961858.84</v>
       </c>
       <c r="W620" t="n">
         <v>0</v>
       </c>
       <c r="X620" t="n">
-        <v>5774752.44</v>
+        <v>2961858.84</v>
       </c>
       <c r="Y620" t="n">
         <v>0</v>
@@ -72905,7 +72910,7 @@
         <v>0</v>
       </c>
       <c r="AB620" t="n">
-        <v>5774752.44</v>
+        <v>2961858.84</v>
       </c>
       <c r="AC620" t="n">
         <v>0</v>
@@ -72914,35 +72919,41 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>DO009482014/2025</t>
+          <t>DM-9504058/2026</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>230190100125</t>
+          <t>230176203025</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇO DE ENGENHARIA DE TRANSITO - LOTE 01 </t>
+          <t>MANUTENÇÃO LINHA VERDE E COMPLEXO VIÁRIO DA CIDADE ADMINISTRATIVA</t>
         </is>
       </c>
       <c r="D621" s="3" t="n">
-        <v>45974</v>
+        <v>46147</v>
+      </c>
+      <c r="E621" s="3" t="n">
+        <v>46153</v>
+      </c>
+      <c r="F621" s="3" t="n">
+        <v>46517</v>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+          <t xml:space="preserve">CONSORCIO EMCONBRAS-MARINS </t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t>16502551000193</t>
+          <t>66573523000135</t>
         </is>
       </c>
       <c r="J621" t="inlineStr">
@@ -72952,7 +72963,7 @@
       </c>
       <c r="K621" t="inlineStr">
         <is>
-          <t>GERÊNCIA DE TRÂFEGO E SEGURANÇA VIÁRIA</t>
+          <t>DIRETORIA DE OPERAÇÕES</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
@@ -72965,13 +72976,28 @@
           <t>EMPREITADA POR PREÇO UNITÁRIO</t>
         </is>
       </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>Manutenção e Conservação</t>
+        </is>
+      </c>
       <c r="O621" t="inlineStr">
         <is>
           <t>Natureza continuada e/ou conserva</t>
         </is>
       </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Manutenção Linha Verde e complexo viário da Cidade Administrativa</t>
+        </is>
+      </c>
+      <c r="Q621" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Belo Horizonte, Confins, Lagoa Santa, Pedro Leopoldo, Ribeirão das Neves, São José da Lapa, Vespasiano</t>
+        </is>
+      </c>
       <c r="R621" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="S621" t="n">
         <v>0</v>
@@ -72980,16 +73006,16 @@
         <v>0</v>
       </c>
       <c r="U621" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="V621" t="n">
-        <v>77898894.3</v>
+        <v>19798000</v>
       </c>
       <c r="W621" t="n">
         <v>0</v>
       </c>
       <c r="X621" t="n">
-        <v>77898894.3</v>
+        <v>19798000</v>
       </c>
       <c r="Y621" t="n">
         <v>0</v>
@@ -73001,7 +73027,7 @@
         <v>0</v>
       </c>
       <c r="AB621" t="n">
-        <v>77898894.3</v>
+        <v>19798000</v>
       </c>
       <c r="AC621" t="n">
         <v>0</v>
@@ -73010,106 +73036,426 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
+          <t>AMA-9499286/2026</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>230161700325</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>APOIO À SUPERVISÃO AMBIENTAL E PROCEDIMENTOS DE GESTÃO/REGULARIZAÇÃO AMBIENTAL DE EMPREENDIMENTOS RODOVIÁRIOS DO DER-MG</t>
+        </is>
+      </c>
+      <c r="D622" s="3" t="n">
+        <v>46108</v>
+      </c>
+      <c r="E622" s="3" t="n">
+        <v>46118</v>
+      </c>
+      <c r="F622" s="3" t="n">
+        <v>46848</v>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>STE SERVIÇOS TÉCNICOS DE ENGENHARIA S/A</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>88849773000198</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>DER/DG/ASSESSORIA DE MEIO AMBIENTE</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>Estudos Ambientais</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+        </is>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Apoio à Supervisão ambiental e aos procedimentos de gestão e regularização Ambiental dos Empreendimentos rodoviários do DER-MG</t>
+        </is>
+      </c>
+      <c r="Q622" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Belo Horizonte</t>
+        </is>
+      </c>
+      <c r="R622" t="n">
+        <v>731</v>
+      </c>
+      <c r="S622" t="n">
+        <v>0</v>
+      </c>
+      <c r="T622" t="n">
+        <v>0</v>
+      </c>
+      <c r="U622" t="n">
+        <v>731</v>
+      </c>
+      <c r="V622" t="n">
+        <v>36033198.22</v>
+      </c>
+      <c r="W622" t="n">
+        <v>0</v>
+      </c>
+      <c r="X622" t="n">
+        <v>36033198.22</v>
+      </c>
+      <c r="Y622" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z622" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA622" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB622" t="n">
+        <v>36033198.22</v>
+      </c>
+      <c r="AC622" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Não Disponível</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>SERVIÇOS ESPECIAIS DE APOIO À COORDENAÇÃO E APOIO TÉCNICO NO PLANEJAMENTO, MONITORAMENTO E AVALIAÇÃO DO PORTIFÓLIO DE EMPREENDIMENTOS DO DER-MG</t>
+        </is>
+      </c>
+      <c r="D623" s="3" t="n">
+        <v>45589</v>
+      </c>
+      <c r="E623" s="3" t="n">
+        <v>45628</v>
+      </c>
+      <c r="F623" s="3" t="n">
+        <v>46722</v>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYSTRA ENGENHARIA E  CONSULTORIA LTDA </t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>52635422000307</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>ASSESSORIA DE GESTÃO ESTRATÉGICA</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>Consultoria</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+        </is>
+      </c>
+      <c r="R623" t="n">
+        <v>1095</v>
+      </c>
+      <c r="S623" t="n">
+        <v>0</v>
+      </c>
+      <c r="T623" t="n">
+        <v>0</v>
+      </c>
+      <c r="U623" t="n">
+        <v>1095</v>
+      </c>
+      <c r="V623" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="W623" t="n">
+        <v>0</v>
+      </c>
+      <c r="X623" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="Y623" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z623" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA623" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB623" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="AC623" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>DO009482014/2025</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>230190100125</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇO DE ENGENHARIA DE TRANSITO - LOTE 01 </t>
+        </is>
+      </c>
+      <c r="D624" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>A Iniciar</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>16502551000193</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>GERÊNCIA DE TRÂFEGO E SEGURANÇA VIÁRIA</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="R624" t="n">
+        <v>0</v>
+      </c>
+      <c r="S624" t="n">
+        <v>0</v>
+      </c>
+      <c r="T624" t="n">
+        <v>0</v>
+      </c>
+      <c r="U624" t="n">
+        <v>0</v>
+      </c>
+      <c r="V624" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="W624" t="n">
+        <v>0</v>
+      </c>
+      <c r="X624" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="Y624" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z624" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA624" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB624" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="AC624" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
           <t>DP-001/2023</t>
         </is>
       </c>
-      <c r="B622" t="inlineStr">
+      <c r="B625" t="inlineStr">
         <is>
           <t>2301601000022020</t>
         </is>
       </c>
-      <c r="C622" t="inlineStr">
+      <c r="C625" t="inlineStr">
         <is>
           <t>ELABORAÇÃO DE PROJETO DE ENGENHARIA RODOVIÁRIA DE MELHORAMENTOS, PAVIMENTAÇÃO E OAE - LOTE 2</t>
         </is>
       </c>
-      <c r="D622" s="3" t="n">
+      <c r="D625" s="3" t="n">
         <v>45166</v>
       </c>
-      <c r="G622" t="inlineStr">
+      <c r="G625" t="inlineStr">
         <is>
           <t>A Iniciar</t>
         </is>
       </c>
-      <c r="H622" t="inlineStr">
+      <c r="H625" t="inlineStr">
         <is>
           <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
-      <c r="I622" t="inlineStr">
+      <c r="I625" t="inlineStr">
         <is>
           <t>38743357000132</t>
         </is>
       </c>
-      <c r="J622" t="inlineStr">
+      <c r="J625" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr">
+      <c r="K625" t="inlineStr">
         <is>
           <t>DIRETORIA DE PROJETOS</t>
         </is>
       </c>
-      <c r="L622" t="inlineStr">
+      <c r="L625" t="inlineStr">
         <is>
           <t>RDC</t>
         </is>
       </c>
-      <c r="M622" t="inlineStr">
+      <c r="M625" t="inlineStr">
         <is>
           <t>EMPREITADA POR PREÇO UNITÁRIO</t>
         </is>
       </c>
-      <c r="N622" t="inlineStr">
+      <c r="N625" t="inlineStr">
         <is>
           <t>Consultoria para Projetos</t>
         </is>
       </c>
-      <c r="O622" t="inlineStr">
+      <c r="O625" t="inlineStr">
         <is>
           <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
         </is>
       </c>
-      <c r="R622" t="n">
-        <v>0</v>
-      </c>
-      <c r="S622" t="n">
-        <v>0</v>
-      </c>
-      <c r="T622" t="n">
-        <v>0</v>
-      </c>
-      <c r="U622" t="n">
-        <v>0</v>
-      </c>
-      <c r="V622" t="n">
+      <c r="R625" t="n">
+        <v>0</v>
+      </c>
+      <c r="S625" t="n">
+        <v>0</v>
+      </c>
+      <c r="T625" t="n">
+        <v>0</v>
+      </c>
+      <c r="U625" t="n">
+        <v>0</v>
+      </c>
+      <c r="V625" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="W622" t="n">
-        <v>0</v>
-      </c>
-      <c r="X622" t="n">
+      <c r="W625" t="n">
+        <v>0</v>
+      </c>
+      <c r="X625" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="Y622" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z622" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA622" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB622" t="n">
+      <c r="Y625" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z625" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA625" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB625" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="AC622" t="n">
+      <c r="AC625" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC622"/>
+  <autoFilter ref="A1:AC625"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/upload/contratos.xlsx
+++ b/upload/contratos.xlsx
@@ -2273,7 +2273,7 @@
         <v>44524</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46196</v>
+        <v>46203</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1313</v>
+        <v>1320</v>
       </c>
       <c r="U16" t="n">
-        <v>1673</v>
+        <v>1680</v>
       </c>
       <c r="V16" t="n">
         <v>1452371.99</v>
@@ -12200,7 +12200,7 @@
         <v>44850</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>46154</v>
+        <v>46161</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -12264,10 +12264,10 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="U101" t="n">
-        <v>1305</v>
+        <v>1312</v>
       </c>
       <c r="V101" t="n">
         <v>1365885.84</v>
@@ -15827,7 +15827,7 @@
         <v>45026</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -15891,10 +15891,10 @@
         <v>510</v>
       </c>
       <c r="T132" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="U132" t="n">
-        <v>1132</v>
+        <v>1139</v>
       </c>
       <c r="V132" t="n">
         <v>19915653.29</v>
@@ -24017,7 +24017,7 @@
         <v>44767</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>46252</v>
+        <v>46259</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -24081,10 +24081,10 @@
         <v>0</v>
       </c>
       <c r="T202" t="n">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="U202" t="n">
-        <v>1486</v>
+        <v>1493</v>
       </c>
       <c r="V202" t="n">
         <v>2519553.4</v>
@@ -26819,7 +26819,7 @@
         <v>44810</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>46173</v>
+        <v>46180</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -26883,10 +26883,10 @@
         <v>0</v>
       </c>
       <c r="T226" t="n">
-        <v>1183</v>
+        <v>1190</v>
       </c>
       <c r="U226" t="n">
-        <v>1364</v>
+        <v>1371</v>
       </c>
       <c r="V226" t="n">
         <v>1559477.28</v>
@@ -28457,7 +28457,7 @@
         <v>44579</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>46369</v>
+        <v>46376</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -28521,10 +28521,10 @@
         <v>180</v>
       </c>
       <c r="T240" t="n">
-        <v>1251</v>
+        <v>1258</v>
       </c>
       <c r="U240" t="n">
-        <v>1791</v>
+        <v>1798</v>
       </c>
       <c r="V240" t="n">
         <v>1175120.88</v>
@@ -37097,7 +37097,7 @@
         <v>45384</v>
       </c>
       <c r="F314" s="3" t="n">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -37161,10 +37161,10 @@
         <v>330</v>
       </c>
       <c r="T314" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="U314" t="n">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="V314" t="n">
         <v>2816620.4</v>
@@ -40373,7 +40373,7 @@
         <v>45110</v>
       </c>
       <c r="F342" s="3" t="n">
-        <v>46172</v>
+        <v>46179</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -40437,10 +40437,10 @@
         <v>398</v>
       </c>
       <c r="T342" t="n">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="U342" t="n">
-        <v>1063</v>
+        <v>1070</v>
       </c>
       <c r="V342" t="n">
         <v>3655796.23</v>
@@ -41894,11 +41894,11 @@
         <v>45240</v>
       </c>
       <c r="F355" s="3" t="n">
-        <v>46152</v>
+        <v>46171</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Paralisado</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -41958,10 +41958,10 @@
         <v>510</v>
       </c>
       <c r="T355" t="n">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="U355" t="n">
-        <v>913</v>
+        <v>932</v>
       </c>
       <c r="V355" t="n">
         <v>3270756.85</v>
@@ -42479,7 +42479,7 @@
         <v>45236</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>46166</v>
+        <v>46173</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -42543,10 +42543,10 @@
         <v>480</v>
       </c>
       <c r="T360" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="U360" t="n">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="V360" t="n">
         <v>5042730.21</v>
@@ -43302,7 +43302,7 @@
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -43377,19 +43377,19 @@
         <v>2949000</v>
       </c>
       <c r="Y367" t="n">
-        <v>2586657.84</v>
+        <v>2677159.38</v>
       </c>
       <c r="Z367" t="n">
-        <v>612009.77</v>
+        <v>641902.42</v>
       </c>
       <c r="AA367" t="n">
-        <v>3198667.61</v>
+        <v>3319061.8</v>
       </c>
       <c r="AB367" t="n">
-        <v>362342.16</v>
+        <v>271840.62</v>
       </c>
       <c r="AC367" t="n">
-        <v>0.877130498474059</v>
+        <v>0.9078193896236012</v>
       </c>
     </row>
     <row r="368">
@@ -43649,7 +43649,7 @@
         <v>45236</v>
       </c>
       <c r="F370" s="3" t="n">
-        <v>46158</v>
+        <v>46165</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
@@ -43713,10 +43713,10 @@
         <v>510</v>
       </c>
       <c r="T370" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="U370" t="n">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="V370" t="n">
         <v>7889881.67</v>
@@ -45015,19 +45015,19 @@
         <v>7576922.1</v>
       </c>
       <c r="Y381" t="n">
-        <v>4239229.08</v>
+        <v>4365171.24</v>
       </c>
       <c r="Z381" t="n">
-        <v>423752.72</v>
+        <v>441674.27</v>
       </c>
       <c r="AA381" t="n">
-        <v>4662981.8</v>
+        <v>4806845.51</v>
       </c>
       <c r="AB381" t="n">
-        <v>3337693.02</v>
+        <v>3211750.86</v>
       </c>
       <c r="AC381" t="n">
-        <v>0.5594922349802171</v>
+        <v>0.5761140450421155</v>
       </c>
     </row>
     <row r="382">
@@ -45170,7 +45170,7 @@
         <v>45237</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>46159</v>
+        <v>46166</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -45234,10 +45234,10 @@
         <v>510</v>
       </c>
       <c r="T383" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="U383" t="n">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="V383" t="n">
         <v>4065559.6</v>
@@ -48870,19 +48870,19 @@
         <v>75282924.23</v>
       </c>
       <c r="Y414" t="n">
-        <v>50964371.23</v>
+        <v>53680846</v>
       </c>
       <c r="Z414" t="n">
-        <v>2994474.72</v>
+        <v>3211937.05</v>
       </c>
       <c r="AA414" t="n">
-        <v>53958845.95</v>
+        <v>56892783.05</v>
       </c>
       <c r="AB414" t="n">
-        <v>24318553</v>
+        <v>21602078.23</v>
       </c>
       <c r="AC414" t="n">
-        <v>0.6769711956764143</v>
+        <v>0.7130547404879944</v>
       </c>
     </row>
     <row r="415">
@@ -48987,19 +48987,19 @@
         <v>33826877.05</v>
       </c>
       <c r="Y415" t="n">
-        <v>29210734.29</v>
+        <v>29468214.18</v>
       </c>
       <c r="Z415" t="n">
-        <v>1346526.87</v>
+        <v>1364900.9</v>
       </c>
       <c r="AA415" t="n">
-        <v>30557261.16</v>
+        <v>30833115.08</v>
       </c>
       <c r="AB415" t="n">
-        <v>4616142.76</v>
+        <v>4358662.87</v>
       </c>
       <c r="AC415" t="n">
-        <v>0.8635362421078123</v>
+        <v>0.8711479376722422</v>
       </c>
     </row>
     <row r="416">
@@ -50970,19 +50970,19 @@
         <v>1413414.8</v>
       </c>
       <c r="Y432" t="n">
-        <v>1051152.96</v>
+        <v>1105927.68</v>
       </c>
       <c r="Z432" t="n">
-        <v>60859.04</v>
+        <v>66314.60000000001</v>
       </c>
       <c r="AA432" t="n">
-        <v>1112012</v>
+        <v>1172242.28</v>
       </c>
       <c r="AB432" t="n">
-        <v>362261.84</v>
+        <v>307487.12</v>
       </c>
       <c r="AC432" t="n">
-        <v>0.743697434044132</v>
+        <v>0.7824508983491612</v>
       </c>
     </row>
     <row r="433">
@@ -53118,7 +53118,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -53193,19 +53193,19 @@
         <v>33479427.94</v>
       </c>
       <c r="Y451" t="n">
-        <v>19221395.57</v>
+        <v>21822548.03</v>
       </c>
       <c r="Z451" t="n">
-        <v>1019396.32</v>
+        <v>1302114.23</v>
       </c>
       <c r="AA451" t="n">
-        <v>20240791.89</v>
+        <v>23124662.26</v>
       </c>
       <c r="AB451" t="n">
-        <v>14258032.37</v>
+        <v>11656879.91</v>
       </c>
       <c r="AC451" t="n">
-        <v>0.574125567630592</v>
+        <v>0.6518196209657219</v>
       </c>
     </row>
     <row r="452">
@@ -53661,19 +53661,19 @@
         <v>33721624.27</v>
       </c>
       <c r="Y455" t="n">
-        <v>17654827.84</v>
+        <v>18950254.07</v>
       </c>
       <c r="Z455" t="n">
-        <v>1026710.9</v>
+        <v>1139200.92</v>
       </c>
       <c r="AA455" t="n">
-        <v>18681538.74</v>
+        <v>20089454.99</v>
       </c>
       <c r="AB455" t="n">
-        <v>16066796.43</v>
+        <v>14771370.2</v>
       </c>
       <c r="AC455" t="n">
-        <v>0.5235461880081022</v>
+        <v>0.5619614855521311</v>
       </c>
     </row>
     <row r="456">
@@ -54012,19 +54012,19 @@
         <v>42788655.89</v>
       </c>
       <c r="Y458" t="n">
-        <v>27461062.39</v>
+        <v>28236307.03</v>
       </c>
       <c r="Z458" t="n">
-        <v>1481599.91</v>
+        <v>1562283.98</v>
       </c>
       <c r="AA458" t="n">
-        <v>28942662.3</v>
+        <v>29798591.01</v>
       </c>
       <c r="AB458" t="n">
-        <v>15327593.5</v>
+        <v>14552348.86</v>
       </c>
       <c r="AC458" t="n">
-        <v>0.6417837115658928</v>
+        <v>0.659901706251049</v>
       </c>
     </row>
     <row r="459">
@@ -55182,19 +55182,19 @@
         <v>45768946.45</v>
       </c>
       <c r="Y468" t="n">
-        <v>20394072.15</v>
+        <v>21326695.49</v>
       </c>
       <c r="Z468" t="n">
-        <v>967683.63</v>
+        <v>1049157.66</v>
       </c>
       <c r="AA468" t="n">
-        <v>21361755.78</v>
+        <v>22375853.15</v>
       </c>
       <c r="AB468" t="n">
-        <v>25374874.3</v>
+        <v>24442250.96</v>
       </c>
       <c r="AC468" t="n">
-        <v>0.4455875376611383</v>
+        <v>0.4659643086453436</v>
       </c>
     </row>
     <row r="469">
@@ -55884,19 +55884,19 @@
         <v>47005570.55</v>
       </c>
       <c r="Y474" t="n">
-        <v>23528643.71</v>
+        <v>24832214.04</v>
       </c>
       <c r="Z474" t="n">
-        <v>1104146.56</v>
+        <v>1179693.19</v>
       </c>
       <c r="AA474" t="n">
-        <v>24632790.27</v>
+        <v>26011907.23</v>
       </c>
       <c r="AB474" t="n">
-        <v>23476926.84</v>
+        <v>22173356.51</v>
       </c>
       <c r="AC474" t="n">
-        <v>0.5005501142672546</v>
+        <v>0.5282823663120072</v>
       </c>
     </row>
     <row r="475">
@@ -56150,7 +56150,7 @@
         <v>45573</v>
       </c>
       <c r="F477" s="3" t="n">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
@@ -56214,10 +56214,10 @@
         <v>0</v>
       </c>
       <c r="T477" t="n">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="U477" t="n">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="V477" t="n">
         <v>3876550</v>
@@ -56438,7 +56438,7 @@
       </c>
       <c r="Q479" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Rio Pardo de Minas, Santo Antônio do Retiro</t>
+          <t xml:space="preserve"> Obra 1 - Rio Pardo de Minas, Salinas, Santo Antônio do Retiro</t>
         </is>
       </c>
       <c r="R479" t="n">
@@ -57633,19 +57633,19 @@
         <v>61821473.21</v>
       </c>
       <c r="Y489" t="n">
-        <v>46257291.3</v>
+        <v>46331106.15</v>
       </c>
       <c r="Z489" t="n">
-        <v>1387864.19</v>
+        <v>1389985.11</v>
       </c>
       <c r="AA489" t="n">
-        <v>47645155.49</v>
+        <v>47721091.26</v>
       </c>
       <c r="AB489" t="n">
-        <v>15564181.91</v>
+        <v>15490367.06</v>
       </c>
       <c r="AC489" t="n">
-        <v>0.7482398735932679</v>
+        <v>0.7494338737709936</v>
       </c>
     </row>
     <row r="490">
@@ -59037,19 +59037,19 @@
         <v>2246097.6</v>
       </c>
       <c r="Y501" t="n">
-        <v>164119.62</v>
+        <v>171424.7</v>
       </c>
       <c r="Z501" t="n">
-        <v>6728.85</v>
+        <v>7270.88</v>
       </c>
       <c r="AA501" t="n">
-        <v>170848.47</v>
+        <v>178695.58</v>
       </c>
       <c r="AB501" t="n">
-        <v>2081977.98</v>
+        <v>2074672.9</v>
       </c>
       <c r="AC501" t="n">
-        <v>0.07306878383201157</v>
+        <v>0.07632112691808228</v>
       </c>
     </row>
     <row r="502">
@@ -59154,19 +59154,19 @@
         <v>5774752.44</v>
       </c>
       <c r="Y502" t="n">
-        <v>1912436.46</v>
+        <v>2080303.32</v>
       </c>
       <c r="Z502" t="n">
-        <v>77533.00999999999</v>
+        <v>88175.75999999999</v>
       </c>
       <c r="AA502" t="n">
-        <v>1989969.47</v>
+        <v>2168479.08</v>
       </c>
       <c r="AB502" t="n">
-        <v>3862315.98</v>
+        <v>3694449.12</v>
       </c>
       <c r="AC502" t="n">
-        <v>0.3311720250989668</v>
+        <v>0.360241125765038</v>
       </c>
     </row>
     <row r="503">
@@ -60090,19 +60090,19 @@
         <v>39334571.99</v>
       </c>
       <c r="Y510" t="n">
-        <v>10734557.59</v>
+        <v>17178308.35</v>
       </c>
       <c r="Z510" t="n">
-        <v>315285.64</v>
+        <v>492175.03</v>
       </c>
       <c r="AA510" t="n">
-        <v>11049843.23</v>
+        <v>17670483.38</v>
       </c>
       <c r="AB510" t="n">
-        <v>28600014.4</v>
+        <v>22156263.64</v>
       </c>
       <c r="AC510" t="n">
-        <v>0.2729038870113812</v>
+        <v>0.4367229000068242</v>
       </c>
     </row>
     <row r="511">
@@ -60675,19 +60675,19 @@
         <v>4776981.58</v>
       </c>
       <c r="Y515" t="n">
-        <v>3155692.55</v>
+        <v>3811147.4</v>
       </c>
       <c r="Z515" t="n">
-        <v>101679.28</v>
+        <v>125510.2</v>
       </c>
       <c r="AA515" t="n">
-        <v>3257371.83</v>
+        <v>3936657.6</v>
       </c>
       <c r="AB515" t="n">
-        <v>1621289.03</v>
+        <v>965834.1800000001</v>
       </c>
       <c r="AC515" t="n">
-        <v>0.6606038765592226</v>
+        <v>0.7978149666635307</v>
       </c>
     </row>
     <row r="516">
@@ -60792,19 +60792,19 @@
         <v>8415499.810000001</v>
       </c>
       <c r="Y516" t="n">
-        <v>2984135.57</v>
+        <v>3668445.77</v>
       </c>
       <c r="Z516" t="n">
-        <v>105011.73</v>
+        <v>133016.83</v>
       </c>
       <c r="AA516" t="n">
-        <v>3089147.3</v>
+        <v>3801462.6</v>
       </c>
       <c r="AB516" t="n">
-        <v>5431364.24</v>
+        <v>4747054.04</v>
       </c>
       <c r="AC516" t="n">
-        <v>0.3545999212612423</v>
+        <v>0.4359153767243683</v>
       </c>
     </row>
     <row r="517">
@@ -61611,19 +61611,19 @@
         <v>95661672.93000001</v>
       </c>
       <c r="Y523" t="n">
-        <v>15151232.48</v>
+        <v>19433859.66</v>
       </c>
       <c r="Z523" t="n">
-        <v>646825.62</v>
+        <v>817663.8100000001</v>
       </c>
       <c r="AA523" t="n">
-        <v>15798058.1</v>
+        <v>20251523.47</v>
       </c>
       <c r="AB523" t="n">
-        <v>80510440.45</v>
+        <v>76227813.27</v>
       </c>
       <c r="AC523" t="n">
-        <v>0.1583835199190678</v>
+        <v>0.2031519945738419</v>
       </c>
     </row>
     <row r="524">
@@ -61845,19 +61845,19 @@
         <v>13934048.38</v>
       </c>
       <c r="Y525" t="n">
-        <v>4685070</v>
+        <v>5255390.3</v>
       </c>
       <c r="Z525" t="n">
-        <v>1294868.36</v>
+        <v>1484860.68</v>
       </c>
       <c r="AA525" t="n">
-        <v>5979938.36</v>
+        <v>6740250.98</v>
       </c>
       <c r="AB525" t="n">
-        <v>9248978.380000001</v>
+        <v>8678658.08</v>
       </c>
       <c r="AC525" t="n">
-        <v>0.3362317879364217</v>
+        <v>0.3771617663925464</v>
       </c>
     </row>
     <row r="526">
@@ -61937,7 +61937,7 @@
       </c>
       <c r="Q526" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Obra 1 - Araguari, Araporã, Araxá, Augusto de Lima, Belo Horizonte, Bom Despacho, Campina Verde, Capinópolis, Carmo do Paranaíba, Carneirinho, Cascalho Rico, Corinto, Coromandel, Curvelo, Diamantina, Douradoquara, Estrela do Sul, Felixlândia, Frutal, Gouvea, Ibiá, Inimutaba, Iraí de Minas, Ituiutaba, Iturama, Lagamar, Lagoa Grande, Luz, Martinho Campos, Monte Carmelo, Nova Ponte, Paineiras, Paracatu, Passos, Patos de Minas, Patrocínio, Perdizes, Pompéu, Presidente Juscelino, Presidente Kubitschek, Presidente Olegário, Rio Paranaíba, Santa Juliana, Serra do Salitre, Serro, São Gotardo, Tapira, Tupaciguara, Uberaba, Uberlândia, Unaí, Vazante, Água Comprida</t>
+          <t xml:space="preserve"> Obra 1 - Araguari, Araporã, Araxá, Augusto de Lima, Belo Horizonte, Bom Despacho, Campina Verde, Capinópolis, Carmo do Paranaíba, Carneirinho, Cascalho Rico, Corinto, Coromandel, Curvelo, Diamantina, Douradoquara, Estrela do Sul, Felixlândia, Frutal, Gouvea, Ibiá, Inimutaba, Iraí de Minas, Ituiutaba, Iturama, Lagamar, Lagoa Grande, Luz, Martinho Campos, Monte Carmelo, Nova Ponte, Paineiras, Paracatu, Passos, Patos de Minas, Patrocínio, Perdizes, Pompéu, Presidente Juscelino, Presidente Kubitschek, Presidente Olegário, Rio Paranaíba, Romaria, Santa Juliana, Serra do Salitre, Serro, São Gotardo, Tapira, Tupaciguara, Uberaba, Uberlândia, Unaí, Vazante, Água Comprida</t>
         </is>
       </c>
       <c r="R526" t="n">
@@ -61962,19 +61962,19 @@
         <v>9104897.539999999</v>
       </c>
       <c r="Y526" t="n">
-        <v>2625143.15</v>
+        <v>2984078.68</v>
       </c>
       <c r="Z526" t="n">
-        <v>726351.11</v>
+        <v>846058.74</v>
       </c>
       <c r="AA526" t="n">
-        <v>3351494.26</v>
+        <v>3830137.42</v>
       </c>
       <c r="AB526" t="n">
-        <v>6479754.39</v>
+        <v>6120818.86</v>
       </c>
       <c r="AC526" t="n">
-        <v>0.2883220968129642</v>
+        <v>0.3277443449407559</v>
       </c>
     </row>
     <row r="527">
@@ -62079,19 +62079,19 @@
         <v>10364111.47</v>
       </c>
       <c r="Y527" t="n">
-        <v>2579642.02</v>
+        <v>2904800.14</v>
       </c>
       <c r="Z527" t="n">
-        <v>713477.2</v>
+        <v>821885.87</v>
       </c>
       <c r="AA527" t="n">
-        <v>3293119.22</v>
+        <v>3726686.01</v>
       </c>
       <c r="AB527" t="n">
-        <v>7784469.45</v>
+        <v>7459311.33</v>
       </c>
       <c r="AC527" t="n">
-        <v>0.2489014159551489</v>
+        <v>0.2802748839983289</v>
       </c>
     </row>
     <row r="528">
@@ -62196,19 +62196,19 @@
         <v>15276741.09</v>
       </c>
       <c r="Y528" t="n">
-        <v>4187262.13</v>
+        <v>4700012.81</v>
       </c>
       <c r="Z528" t="n">
-        <v>1157069.81</v>
+        <v>1327844.46</v>
       </c>
       <c r="AA528" t="n">
-        <v>5344331.94</v>
+        <v>6027857.27</v>
       </c>
       <c r="AB528" t="n">
-        <v>11089478.96</v>
+        <v>10576728.28</v>
       </c>
       <c r="AC528" t="n">
-        <v>0.2740939383165261</v>
+        <v>0.3076580785332927</v>
       </c>
     </row>
     <row r="529">
@@ -64179,19 +64179,19 @@
         <v>53573999.99</v>
       </c>
       <c r="Y545" t="n">
-        <v>6093202.3</v>
+        <v>7700082.26</v>
       </c>
       <c r="Z545" t="n">
-        <v>63545.71</v>
+        <v>95028.74000000001</v>
       </c>
       <c r="AA545" t="n">
-        <v>6156748.01</v>
+        <v>7795111</v>
       </c>
       <c r="AB545" t="n">
-        <v>47480797.69</v>
+        <v>45873917.73</v>
       </c>
       <c r="AC545" t="n">
-        <v>0.1137343170406791</v>
+        <v>0.1437279699376056</v>
       </c>
     </row>
     <row r="546">
@@ -64407,19 +64407,19 @@
         <v>1655673.22</v>
       </c>
       <c r="Y547" t="n">
-        <v>375709.28</v>
+        <v>485335.3</v>
       </c>
       <c r="Z547" t="n">
-        <v>8141.11</v>
+        <v>12098.6</v>
       </c>
       <c r="AA547" t="n">
-        <v>383850.39</v>
+        <v>497433.9</v>
       </c>
       <c r="AB547" t="n">
-        <v>1279963.94</v>
+        <v>1170337.92</v>
       </c>
       <c r="AC547" t="n">
-        <v>0.2269223633393068</v>
+        <v>0.2931347165233487</v>
       </c>
     </row>
     <row r="548">
@@ -64641,19 +64641,19 @@
         <v>9284408.859999999</v>
       </c>
       <c r="Y549" t="n">
-        <v>1544810.85</v>
+        <v>1879558.63</v>
       </c>
       <c r="Z549" t="n">
-        <v>41876.47</v>
+        <v>53960.85</v>
       </c>
       <c r="AA549" t="n">
-        <v>1586687.32</v>
+        <v>1933519.48</v>
       </c>
       <c r="AB549" t="n">
-        <v>7739598.01</v>
+        <v>7404850.23</v>
       </c>
       <c r="AC549" t="n">
-        <v>0.1663876368753541</v>
+        <v>0.2024424665416986</v>
       </c>
     </row>
     <row r="550">
@@ -65109,19 +65109,19 @@
         <v>21429526.4</v>
       </c>
       <c r="Y553" t="n">
-        <v>2750527.43</v>
+        <v>3127943.52</v>
       </c>
       <c r="Z553" t="n">
         <v>0</v>
       </c>
       <c r="AA553" t="n">
-        <v>2750527.43</v>
+        <v>3127943.52</v>
       </c>
       <c r="AB553" t="n">
-        <v>18678998.97</v>
+        <v>18301582.88</v>
       </c>
       <c r="AC553" t="n">
-        <v>0.1283522266735675</v>
+        <v>0.1459641926570995</v>
       </c>
     </row>
     <row r="554">
@@ -65694,19 +65694,19 @@
         <v>9410345.890000001</v>
       </c>
       <c r="Y558" t="n">
-        <v>1006178.54</v>
+        <v>1228299.11</v>
       </c>
       <c r="Z558" t="n">
-        <v>29316.14</v>
+        <v>37334.68</v>
       </c>
       <c r="AA558" t="n">
-        <v>1035494.68</v>
+        <v>1265633.79</v>
       </c>
       <c r="AB558" t="n">
-        <v>8404167.35</v>
+        <v>8182046.78</v>
       </c>
       <c r="AC558" t="n">
-        <v>0.1069225883683219</v>
+        <v>0.1305264571948694</v>
       </c>
     </row>
     <row r="559">
@@ -66162,19 +66162,19 @@
         <v>21860486.4</v>
       </c>
       <c r="Y562" t="n">
-        <v>3570546.1</v>
+        <v>4299228.98</v>
       </c>
       <c r="Z562" t="n">
-        <v>46489.96</v>
+        <v>69734.94</v>
       </c>
       <c r="AA562" t="n">
-        <v>3617036.06</v>
+        <v>4368963.92</v>
       </c>
       <c r="AB562" t="n">
-        <v>18289940.3</v>
+        <v>17561257.42</v>
       </c>
       <c r="AC562" t="n">
-        <v>0.1633333327843977</v>
+        <v>0.196666666117731</v>
       </c>
     </row>
     <row r="563">
@@ -66630,19 +66630,19 @@
         <v>41984578.11</v>
       </c>
       <c r="Y566" t="n">
-        <v>3794113.75</v>
+        <v>15624439.46</v>
       </c>
       <c r="Z566" t="n">
         <v>0</v>
       </c>
       <c r="AA566" t="n">
-        <v>3794113.75</v>
+        <v>15624439.46</v>
       </c>
       <c r="AB566" t="n">
-        <v>38190464.36</v>
+        <v>26360138.65</v>
       </c>
       <c r="AC566" t="n">
-        <v>0.09036922414843339</v>
+        <v>0.3721471112336491</v>
       </c>
     </row>
     <row r="567">
@@ -67098,19 +67098,19 @@
         <v>12585961.98</v>
       </c>
       <c r="Y570" t="n">
-        <v>1511276.19</v>
+        <v>2076298.69</v>
       </c>
       <c r="Z570" t="n">
-        <v>138325.23</v>
+        <v>192219.5</v>
       </c>
       <c r="AA570" t="n">
-        <v>1649601.42</v>
+        <v>2268518.19</v>
       </c>
       <c r="AB570" t="n">
-        <v>11074685.79</v>
+        <v>10509663.29</v>
       </c>
       <c r="AC570" t="n">
-        <v>0.1200763352377456</v>
+        <v>0.1649694074477095</v>
       </c>
     </row>
     <row r="571">
@@ -67215,19 +67215,19 @@
         <v>22167830.47</v>
       </c>
       <c r="Y571" t="n">
-        <v>2304211.64</v>
+        <v>3149597.47</v>
       </c>
       <c r="Z571" t="n">
-        <v>491722.4</v>
+        <v>672167.05</v>
       </c>
       <c r="AA571" t="n">
-        <v>2795934.04</v>
+        <v>3821764.52</v>
       </c>
       <c r="AB571" t="n">
-        <v>19863618.83</v>
+        <v>19018233</v>
       </c>
       <c r="AC571" t="n">
-        <v>0.1039439399862931</v>
+        <v>0.1420796443865984</v>
       </c>
     </row>
     <row r="572">
@@ -67332,19 +67332,19 @@
         <v>12403029.87</v>
       </c>
       <c r="Y572" t="n">
-        <v>1614142.18</v>
+        <v>2671611.78</v>
       </c>
       <c r="Z572" t="n">
-        <v>134082.77</v>
+        <v>207169.47</v>
       </c>
       <c r="AA572" t="n">
-        <v>1748224.95</v>
+        <v>2878781.25</v>
       </c>
       <c r="AB572" t="n">
-        <v>10788887.69</v>
+        <v>9731418.09</v>
       </c>
       <c r="AC572" t="n">
-        <v>0.1301409572433772</v>
+        <v>0.2153999311460176</v>
       </c>
     </row>
     <row r="573">
@@ -68268,19 +68268,19 @@
         <v>59889999.58</v>
       </c>
       <c r="Y580" t="n">
-        <v>897085.83</v>
+        <v>1361505.52</v>
       </c>
       <c r="Z580" t="n">
-        <v>47341.54</v>
+        <v>60143.35</v>
       </c>
       <c r="AA580" t="n">
-        <v>944427.37</v>
+        <v>1421648.87</v>
       </c>
       <c r="AB580" t="n">
-        <v>58992913.75</v>
+        <v>58528494.06</v>
       </c>
       <c r="AC580" t="n">
-        <v>0.01497889190668116</v>
+        <v>0.02273343679325502</v>
       </c>
     </row>
     <row r="581">
@@ -68385,19 +68385,19 @@
         <v>64984305.34</v>
       </c>
       <c r="Y581" t="n">
-        <v>2647093.02</v>
+        <v>4375479.93</v>
       </c>
       <c r="Z581" t="n">
-        <v>76958.82000000001</v>
+        <v>117451.13</v>
       </c>
       <c r="AA581" t="n">
-        <v>2724051.84</v>
+        <v>4492931.06</v>
       </c>
       <c r="AB581" t="n">
-        <v>62337212.32</v>
+        <v>60608825.41</v>
       </c>
       <c r="AC581" t="n">
-        <v>0.04073434356419328</v>
+        <v>0.06733133342131375</v>
       </c>
     </row>
     <row r="582">
@@ -69081,19 +69081,19 @@
         <v>13190992.89</v>
       </c>
       <c r="Y587" t="n">
-        <v>1124617.17</v>
+        <v>2020033.16</v>
       </c>
       <c r="Z587" t="n">
-        <v>126675.2</v>
+        <v>254120.31</v>
       </c>
       <c r="AA587" t="n">
-        <v>1251292.37</v>
+        <v>2274153.47</v>
       </c>
       <c r="AB587" t="n">
-        <v>12066375.72</v>
+        <v>11170959.73</v>
       </c>
       <c r="AC587" t="n">
-        <v>0.08525644577161166</v>
+        <v>0.1531373094387287</v>
       </c>
     </row>
     <row r="588">
@@ -69315,19 +69315,19 @@
         <v>14398046.07</v>
       </c>
       <c r="Y589" t="n">
-        <v>647838.1</v>
+        <v>1555371.56</v>
       </c>
       <c r="Z589" t="n">
-        <v>75894.34</v>
+        <v>190823.62</v>
       </c>
       <c r="AA589" t="n">
-        <v>723732.4399999999</v>
+        <v>1746195.18</v>
       </c>
       <c r="AB589" t="n">
-        <v>13750207.97</v>
+        <v>12842674.51</v>
       </c>
       <c r="AC589" t="n">
-        <v>0.04499486227855917</v>
+        <v>0.1080265719694283</v>
       </c>
     </row>
     <row r="590">
@@ -71637,19 +71637,19 @@
         <v>30603197.87</v>
       </c>
       <c r="Y609" t="n">
-        <v>0</v>
+        <v>1284027.29</v>
       </c>
       <c r="Z609" t="n">
-        <v>0</v>
+        <v>108112.79</v>
       </c>
       <c r="AA609" t="n">
-        <v>0</v>
+        <v>1392140.08</v>
       </c>
       <c r="AB609" t="n">
-        <v>30603197.87</v>
+        <v>29319170.58</v>
       </c>
       <c r="AC609" t="n">
-        <v>0</v>
+        <v>0.04195729137374623</v>
       </c>
     </row>
     <row r="610">

--- a/upload/contratos.xlsx
+++ b/upload/contratos.xlsx
@@ -2273,7 +2273,7 @@
         <v>44524</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46203</v>
+        <v>46209</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1320</v>
+        <v>1326</v>
       </c>
       <c r="U16" t="n">
-        <v>1680</v>
+        <v>1686</v>
       </c>
       <c r="V16" t="n">
         <v>1452371.99</v>
@@ -12200,7 +12200,7 @@
         <v>44850</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>46161</v>
+        <v>46167</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -12264,10 +12264,10 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="U101" t="n">
-        <v>1312</v>
+        <v>1318</v>
       </c>
       <c r="V101" t="n">
         <v>1365885.84</v>
@@ -15827,7 +15827,7 @@
         <v>45026</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -15891,10 +15891,10 @@
         <v>510</v>
       </c>
       <c r="T132" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="U132" t="n">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="V132" t="n">
         <v>19915653.29</v>
@@ -15906,19 +15906,19 @@
         <v>24865514.03</v>
       </c>
       <c r="Y132" t="n">
-        <v>20353151.07</v>
+        <v>20427521.85</v>
       </c>
       <c r="Z132" t="n">
-        <v>2062875.33</v>
+        <v>2074335.86</v>
       </c>
       <c r="AA132" t="n">
-        <v>22416026.4</v>
+        <v>22501857.71</v>
       </c>
       <c r="AB132" t="n">
-        <v>4512362.96</v>
+        <v>4437992.18</v>
       </c>
       <c r="AC132" t="n">
-        <v>0.8185292709189169</v>
+        <v>0.8215201915936423</v>
       </c>
     </row>
     <row r="133">
@@ -24017,7 +24017,7 @@
         <v>44767</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -24081,10 +24081,10 @@
         <v>0</v>
       </c>
       <c r="T202" t="n">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="U202" t="n">
-        <v>1493</v>
+        <v>1499</v>
       </c>
       <c r="V202" t="n">
         <v>2519553.4</v>
@@ -24957,7 +24957,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -25032,19 +25032,19 @@
         <v>32501203.78</v>
       </c>
       <c r="Y210" t="n">
-        <v>28835459.69</v>
+        <v>29542276.22</v>
       </c>
       <c r="Z210" t="n">
-        <v>5158403.67</v>
+        <v>5286993.24</v>
       </c>
       <c r="AA210" t="n">
-        <v>33993863.36</v>
+        <v>34829269.46</v>
       </c>
       <c r="AB210" t="n">
-        <v>3665744.09</v>
+        <v>2958927.56</v>
       </c>
       <c r="AC210" t="n">
-        <v>0.8872120517500414</v>
+        <v>0.9089594471629752</v>
       </c>
     </row>
     <row r="211">
@@ -26819,11 +26819,11 @@
         <v>44810</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>46180</v>
+        <v>45164</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Paralisado</t>
+          <t>Rescindido</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -26883,10 +26883,10 @@
         <v>0</v>
       </c>
       <c r="T226" t="n">
-        <v>1190</v>
+        <v>174</v>
       </c>
       <c r="U226" t="n">
-        <v>1371</v>
+        <v>355</v>
       </c>
       <c r="V226" t="n">
         <v>1559477.28</v>
@@ -28457,7 +28457,7 @@
         <v>44579</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>46376</v>
+        <v>46382</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -28521,10 +28521,10 @@
         <v>180</v>
       </c>
       <c r="T240" t="n">
-        <v>1258</v>
+        <v>1264</v>
       </c>
       <c r="U240" t="n">
-        <v>1798</v>
+        <v>1804</v>
       </c>
       <c r="V240" t="n">
         <v>1175120.88</v>
@@ -37097,7 +37097,7 @@
         <v>45384</v>
       </c>
       <c r="F314" s="3" t="n">
-        <v>46174</v>
+        <v>46180</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -37161,10 +37161,10 @@
         <v>330</v>
       </c>
       <c r="T314" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="U314" t="n">
-        <v>791</v>
+        <v>797</v>
       </c>
       <c r="V314" t="n">
         <v>2816620.4</v>
@@ -40373,7 +40373,7 @@
         <v>45110</v>
       </c>
       <c r="F342" s="3" t="n">
-        <v>46179</v>
+        <v>46185</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -40437,10 +40437,10 @@
         <v>398</v>
       </c>
       <c r="T342" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="U342" t="n">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="V342" t="n">
         <v>3655796.23</v>
@@ -41894,7 +41894,7 @@
         <v>45240</v>
       </c>
       <c r="F355" s="3" t="n">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
@@ -41958,10 +41958,10 @@
         <v>510</v>
       </c>
       <c r="T355" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="U355" t="n">
-        <v>932</v>
+        <v>938</v>
       </c>
       <c r="V355" t="n">
         <v>3270756.85</v>
@@ -41973,19 +41973,19 @@
         <v>3270756.85</v>
       </c>
       <c r="Y355" t="n">
-        <v>743694.8199999999</v>
+        <v>753422.6899999999</v>
       </c>
       <c r="Z355" t="n">
-        <v>77898.14</v>
+        <v>79397.19</v>
       </c>
       <c r="AA355" t="n">
-        <v>821592.96</v>
+        <v>832819.88</v>
       </c>
       <c r="AB355" t="n">
-        <v>2527062.03</v>
+        <v>2517334.16</v>
       </c>
       <c r="AC355" t="n">
-        <v>0.2273769815692658</v>
+        <v>0.2303511769760568</v>
       </c>
     </row>
     <row r="356">
@@ -42479,7 +42479,7 @@
         <v>45236</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>46173</v>
+        <v>46179</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -42543,10 +42543,10 @@
         <v>480</v>
       </c>
       <c r="T360" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="U360" t="n">
-        <v>938</v>
+        <v>944</v>
       </c>
       <c r="V360" t="n">
         <v>5042730.21</v>
@@ -42909,19 +42909,19 @@
         <v>7053152.91</v>
       </c>
       <c r="Y363" t="n">
-        <v>2439684.98</v>
+        <v>2449917.58</v>
       </c>
       <c r="Z363" t="n">
-        <v>283837.74</v>
+        <v>285414.58</v>
       </c>
       <c r="AA363" t="n">
-        <v>2723522.72</v>
+        <v>2735332.16</v>
       </c>
       <c r="AB363" t="n">
-        <v>4613467.93</v>
+        <v>4603235.33</v>
       </c>
       <c r="AC363" t="n">
-        <v>0.345899913291402</v>
+        <v>0.3473506970941312</v>
       </c>
     </row>
     <row r="364">
@@ -43611,19 +43611,19 @@
         <v>6324008.13</v>
       </c>
       <c r="Y369" t="n">
-        <v>1593439.12</v>
+        <v>1615301.59</v>
       </c>
       <c r="Z369" t="n">
-        <v>169164.45</v>
+        <v>172533.45</v>
       </c>
       <c r="AA369" t="n">
-        <v>1762603.57</v>
+        <v>1787835.04</v>
       </c>
       <c r="AB369" t="n">
-        <v>4730569.01</v>
+        <v>4708706.54</v>
       </c>
       <c r="AC369" t="n">
-        <v>0.2519666463490141</v>
+        <v>0.2554237054720548</v>
       </c>
     </row>
     <row r="370">
@@ -43649,7 +43649,7 @@
         <v>45236</v>
       </c>
       <c r="F370" s="3" t="n">
-        <v>46165</v>
+        <v>46171</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
@@ -43713,10 +43713,10 @@
         <v>510</v>
       </c>
       <c r="T370" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="U370" t="n">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="V370" t="n">
         <v>7889881.67</v>
@@ -43728,19 +43728,19 @@
         <v>8240827.41</v>
       </c>
       <c r="Y370" t="n">
-        <v>1603853.4</v>
+        <v>1635689.86</v>
       </c>
       <c r="Z370" t="n">
-        <v>190003.52</v>
+        <v>194909.51</v>
       </c>
       <c r="AA370" t="n">
-        <v>1793856.92</v>
+        <v>1830599.37</v>
       </c>
       <c r="AB370" t="n">
-        <v>6636974.01</v>
+        <v>6605137.55</v>
       </c>
       <c r="AC370" t="n">
-        <v>0.194622860084871</v>
+        <v>0.198486120218358</v>
       </c>
     </row>
     <row r="371">
@@ -45170,7 +45170,7 @@
         <v>45237</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>46166</v>
+        <v>46172</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -45234,10 +45234,10 @@
         <v>510</v>
       </c>
       <c r="T383" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="U383" t="n">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="V383" t="n">
         <v>4065559.6</v>
@@ -51087,19 +51087,19 @@
         <v>5820891.54</v>
       </c>
       <c r="Y433" t="n">
-        <v>791900.24</v>
+        <v>849962.12</v>
       </c>
       <c r="Z433" t="n">
-        <v>99590.98</v>
+        <v>108538.3</v>
       </c>
       <c r="AA433" t="n">
-        <v>891491.22</v>
+        <v>958500.42</v>
       </c>
       <c r="AB433" t="n">
-        <v>5028991.3</v>
+        <v>4970929.42</v>
       </c>
       <c r="AC433" t="n">
-        <v>0.1360444932804915</v>
+        <v>0.1460192333355175</v>
       </c>
     </row>
     <row r="434">
@@ -51948,7 +51948,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -52023,19 +52023,19 @@
         <v>29715772.52</v>
       </c>
       <c r="Y441" t="n">
-        <v>23439872.67</v>
+        <v>24431837.74</v>
       </c>
       <c r="Z441" t="n">
-        <v>1224383.25</v>
+        <v>1332520.78</v>
       </c>
       <c r="AA441" t="n">
-        <v>24664255.92</v>
+        <v>25764358.52</v>
       </c>
       <c r="AB441" t="n">
-        <v>6275899.85</v>
+        <v>5283934.78</v>
       </c>
       <c r="AC441" t="n">
-        <v>0.7888023996086237</v>
+        <v>0.8221841691497779</v>
       </c>
     </row>
     <row r="442">
@@ -53001,7 +53001,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -53076,19 +53076,19 @@
         <v>37310856.76</v>
       </c>
       <c r="Y450" t="n">
-        <v>30828416.26</v>
+        <v>33571627.42</v>
       </c>
       <c r="Z450" t="n">
-        <v>1645889.91</v>
+        <v>1885811.92</v>
       </c>
       <c r="AA450" t="n">
-        <v>32474306.17</v>
+        <v>35457439.34</v>
       </c>
       <c r="AB450" t="n">
-        <v>6482440.5</v>
+        <v>3739229.34</v>
       </c>
       <c r="AC450" t="n">
-        <v>0.8262585996966531</v>
+        <v>0.8997817347360211</v>
       </c>
     </row>
     <row r="451">
@@ -53469,7 +53469,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -53544,19 +53544,19 @@
         <v>32023158.45</v>
       </c>
       <c r="Y454" t="n">
-        <v>27938707.57</v>
+        <v>29811640.98</v>
       </c>
       <c r="Z454" t="n">
-        <v>1300896.83</v>
+        <v>1478242.43</v>
       </c>
       <c r="AA454" t="n">
-        <v>29239604.4</v>
+        <v>31289883.41</v>
       </c>
       <c r="AB454" t="n">
-        <v>4084450.88</v>
+        <v>2211517.47</v>
       </c>
       <c r="AC454" t="n">
-        <v>0.8724532158070123</v>
+        <v>0.9309400578505397</v>
       </c>
     </row>
     <row r="455">
@@ -54129,19 +54129,19 @@
         <v>34984519.25</v>
       </c>
       <c r="Y459" t="n">
-        <v>30596587.45</v>
+        <v>32487325.6</v>
       </c>
       <c r="Z459" t="n">
-        <v>1638048.83</v>
+        <v>1803563.04</v>
       </c>
       <c r="AA459" t="n">
-        <v>32234636.28</v>
+        <v>34290888.64</v>
       </c>
       <c r="AB459" t="n">
-        <v>4387931.8</v>
+        <v>2497193.65</v>
       </c>
       <c r="AC459" t="n">
-        <v>0.874575043645912</v>
+        <v>0.9286200381330093</v>
       </c>
     </row>
     <row r="460">
@@ -54246,19 +54246,19 @@
         <v>3345699.13</v>
       </c>
       <c r="Y460" t="n">
-        <v>2386069.14</v>
+        <v>2485734.75</v>
       </c>
       <c r="Z460" t="n">
-        <v>196495.13</v>
+        <v>209371.92</v>
       </c>
       <c r="AA460" t="n">
-        <v>2582564.27</v>
+        <v>2695106.67</v>
       </c>
       <c r="AB460" t="n">
-        <v>959629.99</v>
+        <v>859964.38</v>
       </c>
       <c r="AC460" t="n">
-        <v>0.7131750487079811</v>
+        <v>0.7429642216513354</v>
       </c>
     </row>
     <row r="461">
@@ -54480,19 +54480,19 @@
         <v>50256753.54</v>
       </c>
       <c r="Y462" t="n">
-        <v>41981889.57</v>
+        <v>42740546.57</v>
       </c>
       <c r="Z462" t="n">
-        <v>1522076.2</v>
+        <v>1576940.53</v>
       </c>
       <c r="AA462" t="n">
-        <v>43503965.77</v>
+        <v>44317487.1</v>
       </c>
       <c r="AB462" t="n">
-        <v>8274863.97</v>
+        <v>7516206.97</v>
       </c>
       <c r="AC462" t="n">
-        <v>0.8353482191520005</v>
+        <v>0.8504438420595999</v>
       </c>
     </row>
     <row r="463">
@@ -55299,19 +55299,19 @@
         <v>48158605.21</v>
       </c>
       <c r="Y469" t="n">
-        <v>29856106.57</v>
+        <v>30474934.34</v>
       </c>
       <c r="Z469" t="n">
-        <v>1357169.26</v>
+        <v>1407677.98</v>
       </c>
       <c r="AA469" t="n">
-        <v>31213275.83</v>
+        <v>31882612.32</v>
       </c>
       <c r="AB469" t="n">
-        <v>18302498.64</v>
+        <v>17683670.87</v>
       </c>
       <c r="AC469" t="n">
-        <v>0.6199537224927865</v>
+        <v>0.6328035084718767</v>
       </c>
     </row>
     <row r="470">
@@ -55416,19 +55416,19 @@
         <v>49131721.25</v>
       </c>
       <c r="Y470" t="n">
-        <v>25075761.49</v>
+        <v>27091255.57</v>
       </c>
       <c r="Z470" t="n">
-        <v>984837.09</v>
+        <v>1108710.91</v>
       </c>
       <c r="AA470" t="n">
-        <v>26060598.58</v>
+        <v>28199966.48</v>
       </c>
       <c r="AB470" t="n">
-        <v>24055959.76</v>
+        <v>22040465.68</v>
       </c>
       <c r="AC470" t="n">
-        <v>0.5103782414299194</v>
+        <v>0.5514004981048776</v>
       </c>
     </row>
     <row r="471">
@@ -55533,19 +55533,19 @@
         <v>51333755.33</v>
       </c>
       <c r="Y471" t="n">
-        <v>23304932.85</v>
+        <v>25738126.27</v>
       </c>
       <c r="Z471" t="n">
-        <v>1252057.26</v>
+        <v>1396822.53</v>
       </c>
       <c r="AA471" t="n">
-        <v>24556990.11</v>
+        <v>27134948.8</v>
       </c>
       <c r="AB471" t="n">
-        <v>28028822.48</v>
+        <v>25595629.06</v>
       </c>
       <c r="AC471" t="n">
-        <v>0.4539884662671532</v>
+        <v>0.5013879484277348</v>
       </c>
     </row>
     <row r="472">
@@ -55650,19 +55650,19 @@
         <v>47758833.23</v>
       </c>
       <c r="Y472" t="n">
-        <v>29365376.04</v>
+        <v>30685601.38</v>
       </c>
       <c r="Z472" t="n">
-        <v>1263434.93</v>
+        <v>1357081.56</v>
       </c>
       <c r="AA472" t="n">
-        <v>30628810.97</v>
+        <v>32042682.94</v>
       </c>
       <c r="AB472" t="n">
-        <v>18393457.19</v>
+        <v>17073231.85</v>
       </c>
       <c r="AC472" t="n">
-        <v>0.6148679532973591</v>
+        <v>0.6425115377551698</v>
       </c>
     </row>
     <row r="473">
@@ -56150,7 +56150,7 @@
         <v>45573</v>
       </c>
       <c r="F477" s="3" t="n">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
@@ -56214,10 +56214,10 @@
         <v>0</v>
       </c>
       <c r="T477" t="n">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="U477" t="n">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="V477" t="n">
         <v>3876550</v>
@@ -56346,19 +56346,19 @@
         <v>859769.01</v>
       </c>
       <c r="Y478" t="n">
-        <v>688450.6899999999</v>
+        <v>694073.51</v>
       </c>
       <c r="Z478" t="n">
-        <v>26141.96</v>
+        <v>26559.17</v>
       </c>
       <c r="AA478" t="n">
-        <v>714592.65</v>
+        <v>720632.6800000001</v>
       </c>
       <c r="AB478" t="n">
-        <v>171318.32</v>
+        <v>165695.5</v>
       </c>
       <c r="AC478" t="n">
-        <v>0.8007391310835918</v>
+        <v>0.8072790504510042</v>
       </c>
     </row>
     <row r="479">
@@ -56814,19 +56814,19 @@
         <v>1484780.82</v>
       </c>
       <c r="Y482" t="n">
-        <v>923251.2</v>
+        <v>955292.0699999999</v>
       </c>
       <c r="Z482" t="n">
-        <v>38869.51</v>
+        <v>41246.94</v>
       </c>
       <c r="AA482" t="n">
-        <v>962120.71</v>
+        <v>996539.01</v>
       </c>
       <c r="AB482" t="n">
-        <v>561529.62</v>
+        <v>529488.75</v>
       </c>
       <c r="AC482" t="n">
-        <v>0.6218097564056626</v>
+        <v>0.6433892848912205</v>
       </c>
     </row>
     <row r="483">
@@ -57399,19 +57399,19 @@
         <v>24308955.5</v>
       </c>
       <c r="Y487" t="n">
-        <v>15133680.75</v>
+        <v>16100052.36</v>
       </c>
       <c r="Z487" t="n">
-        <v>170125.57</v>
+        <v>220109.24</v>
       </c>
       <c r="AA487" t="n">
-        <v>15303806.32</v>
+        <v>16320161.6</v>
       </c>
       <c r="AB487" t="n">
-        <v>9175274.75</v>
+        <v>8208903.14</v>
       </c>
       <c r="AC487" t="n">
-        <v>0.622555779905887</v>
+        <v>0.6623095081152294</v>
       </c>
     </row>
     <row r="488">
@@ -57633,19 +57633,19 @@
         <v>61821473.21</v>
       </c>
       <c r="Y489" t="n">
-        <v>46331106.15</v>
+        <v>46516423.88</v>
       </c>
       <c r="Z489" t="n">
-        <v>1389985.11</v>
+        <v>1395457.53</v>
       </c>
       <c r="AA489" t="n">
-        <v>47721091.26</v>
+        <v>47911881.41</v>
       </c>
       <c r="AB489" t="n">
-        <v>15490367.06</v>
+        <v>15305049.33</v>
       </c>
       <c r="AC489" t="n">
-        <v>0.7494338737709936</v>
+        <v>0.7524315009768432</v>
       </c>
     </row>
     <row r="490">
@@ -58920,19 +58920,19 @@
         <v>4917800.43</v>
       </c>
       <c r="Y500" t="n">
-        <v>208430.57</v>
+        <v>966914.63</v>
       </c>
       <c r="Z500" t="n">
-        <v>10175.13</v>
+        <v>43684.1</v>
       </c>
       <c r="AA500" t="n">
-        <v>218605.7</v>
+        <v>1010598.73</v>
       </c>
       <c r="AB500" t="n">
-        <v>4709369.86</v>
+        <v>3950885.8</v>
       </c>
       <c r="AC500" t="n">
-        <v>0.04238288498421234</v>
+        <v>0.1966152640317696</v>
       </c>
     </row>
     <row r="501">
@@ -60207,19 +60207,19 @@
         <v>924684.42</v>
       </c>
       <c r="Y511" t="n">
-        <v>664376.46</v>
+        <v>674271.65</v>
       </c>
       <c r="Z511" t="n">
-        <v>29892.55</v>
+        <v>30626.77</v>
       </c>
       <c r="AA511" t="n">
-        <v>694269.01</v>
+        <v>704898.42</v>
       </c>
       <c r="AB511" t="n">
-        <v>260307.96</v>
+        <v>250412.77</v>
       </c>
       <c r="AC511" t="n">
-        <v>0.7184899470891918</v>
+        <v>0.7291911006784347</v>
       </c>
     </row>
     <row r="512">
@@ -60558,19 +60558,19 @@
         <v>9659997.08</v>
       </c>
       <c r="Y514" t="n">
-        <v>206968.35</v>
+        <v>264833.81</v>
       </c>
       <c r="Z514" t="n">
-        <v>19144.55</v>
+        <v>24497.1</v>
       </c>
       <c r="AA514" t="n">
-        <v>226112.9</v>
+        <v>289330.91</v>
       </c>
       <c r="AB514" t="n">
-        <v>9453028.73</v>
+        <v>9395163.27</v>
       </c>
       <c r="AC514" t="n">
-        <v>0.02142530150744103</v>
+        <v>0.02741551656866546</v>
       </c>
     </row>
     <row r="515">
@@ -61026,19 +61026,19 @@
         <v>52239647.93</v>
       </c>
       <c r="Y518" t="n">
-        <v>17027419.71</v>
+        <v>30269209.55</v>
       </c>
       <c r="Z518" t="n">
-        <v>515574.38</v>
+        <v>919112.24</v>
       </c>
       <c r="AA518" t="n">
-        <v>17542994.09</v>
+        <v>31188321.79</v>
       </c>
       <c r="AB518" t="n">
-        <v>35212228.22</v>
+        <v>21970438.38</v>
       </c>
       <c r="AC518" t="n">
-        <v>0.325948209544145</v>
+        <v>0.5794298152728764</v>
       </c>
     </row>
     <row r="519">
@@ -61143,19 +61143,19 @@
         <v>803371.39</v>
       </c>
       <c r="Y519" t="n">
-        <v>307553.14</v>
+        <v>352010.15</v>
       </c>
       <c r="Z519" t="n">
-        <v>13149.72</v>
+        <v>15314.77</v>
       </c>
       <c r="AA519" t="n">
-        <v>320702.86</v>
+        <v>367324.92</v>
       </c>
       <c r="AB519" t="n">
-        <v>495818.25</v>
+        <v>451361.24</v>
       </c>
       <c r="AC519" t="n">
-        <v>0.3828280964797613</v>
+        <v>0.4381661512740702</v>
       </c>
     </row>
     <row r="520">
@@ -61728,19 +61728,19 @@
         <v>28955069.4</v>
       </c>
       <c r="Y524" t="n">
-        <v>14841369.03</v>
+        <v>15678020.81</v>
       </c>
       <c r="Z524" t="n">
-        <v>351155.7</v>
+        <v>371802.99</v>
       </c>
       <c r="AA524" t="n">
-        <v>15192524.73</v>
+        <v>16049823.8</v>
       </c>
       <c r="AB524" t="n">
-        <v>14113700.37</v>
+        <v>13277048.59</v>
       </c>
       <c r="AC524" t="n">
-        <v>0.5125654794666111</v>
+        <v>0.5414603085012809</v>
       </c>
     </row>
     <row r="525">
@@ -63009,19 +63009,19 @@
         <v>49093539.45</v>
       </c>
       <c r="Y535" t="n">
-        <v>5181810.35</v>
+        <v>5724611.63</v>
       </c>
       <c r="Z535" t="n">
-        <v>41982.04</v>
+        <v>49661.35</v>
       </c>
       <c r="AA535" t="n">
-        <v>5223792.39</v>
+        <v>5774272.98</v>
       </c>
       <c r="AB535" t="n">
-        <v>43911729.1</v>
+        <v>43368927.82</v>
       </c>
       <c r="AC535" t="n">
-        <v>0.1055497405168248</v>
+        <v>0.1166062112068801</v>
       </c>
     </row>
     <row r="536">
@@ -63126,19 +63126,19 @@
         <v>9522992.289999999</v>
       </c>
       <c r="Y536" t="n">
-        <v>2955353.01</v>
+        <v>3299582.84</v>
       </c>
       <c r="Z536" t="n">
-        <v>51034.6</v>
+        <v>60442.41</v>
       </c>
       <c r="AA536" t="n">
-        <v>3006387.61</v>
+        <v>3360025.25</v>
       </c>
       <c r="AB536" t="n">
-        <v>6567639.28</v>
+        <v>6223409.45</v>
       </c>
       <c r="AC536" t="n">
-        <v>0.3103386960738577</v>
+        <v>0.3464859300017348</v>
       </c>
     </row>
     <row r="537">
@@ -63360,19 +63360,19 @@
         <v>51814575.44</v>
       </c>
       <c r="Y538" t="n">
-        <v>6832001.61</v>
+        <v>8776447.58</v>
       </c>
       <c r="Z538" t="n">
-        <v>97809.87</v>
+        <v>157370.32</v>
       </c>
       <c r="AA538" t="n">
-        <v>6929811.48</v>
+        <v>8933817.9</v>
       </c>
       <c r="AB538" t="n">
-        <v>44982573.83</v>
+        <v>43038127.86</v>
       </c>
       <c r="AC538" t="n">
-        <v>0.1318548217752221</v>
+        <v>0.1693818294460969</v>
       </c>
     </row>
     <row r="539">
@@ -63477,19 +63477,19 @@
         <v>50960749.38</v>
       </c>
       <c r="Y539" t="n">
-        <v>5881370.48</v>
+        <v>6563149.56</v>
       </c>
       <c r="Z539" t="n">
-        <v>49202.31</v>
+        <v>60601.39</v>
       </c>
       <c r="AA539" t="n">
-        <v>5930572.79</v>
+        <v>6623750.95</v>
       </c>
       <c r="AB539" t="n">
-        <v>45079378.9</v>
+        <v>44397599.82</v>
       </c>
       <c r="AC539" t="n">
-        <v>0.1154098115030505</v>
+        <v>0.1287883251296098</v>
       </c>
     </row>
     <row r="540">
@@ -63828,19 +63828,19 @@
         <v>53356791.72</v>
       </c>
       <c r="Y542" t="n">
-        <v>9603132.49</v>
+        <v>11440004.49</v>
       </c>
       <c r="Z542" t="n">
-        <v>146432.54</v>
+        <v>195949.38</v>
       </c>
       <c r="AA542" t="n">
-        <v>9749565.029999999</v>
+        <v>11635953.87</v>
       </c>
       <c r="AB542" t="n">
-        <v>43753659.23</v>
+        <v>41916787.23</v>
       </c>
       <c r="AC542" t="n">
-        <v>0.1799795711180365</v>
+        <v>0.2144057789312674</v>
       </c>
     </row>
     <row r="543">
@@ -64062,19 +64062,19 @@
         <v>59299394.97</v>
       </c>
       <c r="Y544" t="n">
-        <v>24082394.71</v>
+        <v>25780749.1</v>
       </c>
       <c r="Z544" t="n">
-        <v>225294.14</v>
+        <v>259048.22</v>
       </c>
       <c r="AA544" t="n">
-        <v>24307688.85</v>
+        <v>26039797.32</v>
       </c>
       <c r="AB544" t="n">
-        <v>35217000.26</v>
+        <v>33518645.87</v>
       </c>
       <c r="AC544" t="n">
-        <v>0.4061153528157153</v>
+        <v>0.4347556853327537</v>
       </c>
     </row>
     <row r="545">
@@ -64524,19 +64524,19 @@
         <v>5978999.99</v>
       </c>
       <c r="Y548" t="n">
-        <v>3278560.72</v>
+        <v>4021883.98</v>
       </c>
       <c r="Z548" t="n">
-        <v>1944.54</v>
+        <v>2366.45</v>
       </c>
       <c r="AA548" t="n">
-        <v>3280505.26</v>
+        <v>4024250.43</v>
       </c>
       <c r="AB548" t="n">
-        <v>2700439.27</v>
+        <v>1957116.01</v>
       </c>
       <c r="AC548" t="n">
-        <v>0.5483459985755912</v>
+        <v>0.6726683369671657</v>
       </c>
     </row>
     <row r="549">
@@ -64875,19 +64875,19 @@
         <v>45918998.95</v>
       </c>
       <c r="Y551" t="n">
-        <v>2216386.72</v>
+        <v>3889704.5</v>
       </c>
       <c r="Z551" t="n">
-        <v>42264.81</v>
+        <v>80510.37</v>
       </c>
       <c r="AA551" t="n">
-        <v>2258651.53</v>
+        <v>3970214.87</v>
       </c>
       <c r="AB551" t="n">
-        <v>43702612.23</v>
+        <v>42029294.45</v>
       </c>
       <c r="AC551" t="n">
-        <v>0.04826731354517039</v>
+        <v>0.08470795507182981</v>
       </c>
     </row>
     <row r="552">
@@ -64992,19 +64992,19 @@
         <v>9218472.49</v>
       </c>
       <c r="Y552" t="n">
-        <v>1041486.75</v>
+        <v>1253158.75</v>
       </c>
       <c r="Z552" t="n">
-        <v>33055.91</v>
+        <v>40697.25</v>
       </c>
       <c r="AA552" t="n">
-        <v>1074542.66</v>
+        <v>1293856</v>
       </c>
       <c r="AB552" t="n">
-        <v>8176985.74</v>
+        <v>7965313.74</v>
       </c>
       <c r="AC552" t="n">
-        <v>0.1129782348572155</v>
+        <v>0.1359399565773396</v>
       </c>
     </row>
     <row r="553">
@@ -65343,19 +65343,19 @@
         <v>7056321.74</v>
       </c>
       <c r="Y555" t="n">
-        <v>474633.67</v>
+        <v>529957.73</v>
       </c>
       <c r="Z555" t="n">
-        <v>13056.15</v>
+        <v>15053.34</v>
       </c>
       <c r="AA555" t="n">
-        <v>487689.82</v>
+        <v>545011.0699999999</v>
       </c>
       <c r="AB555" t="n">
-        <v>6581688.07</v>
+        <v>6526364.01</v>
       </c>
       <c r="AC555" t="n">
-        <v>0.06726360949635497</v>
+        <v>0.07510396344257397</v>
       </c>
     </row>
     <row r="556">
@@ -65577,19 +65577,19 @@
         <v>14619000</v>
       </c>
       <c r="Y557" t="n">
-        <v>4429527.64</v>
+        <v>7635030.52</v>
       </c>
       <c r="Z557" t="n">
-        <v>20772.43</v>
+        <v>29661.44</v>
       </c>
       <c r="AA557" t="n">
-        <v>4450300.07</v>
+        <v>7664691.96</v>
       </c>
       <c r="AB557" t="n">
-        <v>10189472.36</v>
+        <v>6983969.48</v>
       </c>
       <c r="AC557" t="n">
-        <v>0.3029979916546959</v>
+        <v>0.522267632533005</v>
       </c>
     </row>
     <row r="558">
@@ -65811,19 +65811,19 @@
         <v>9200787.869999999</v>
       </c>
       <c r="Y559" t="n">
-        <v>1400596.05</v>
+        <v>1671073.29</v>
       </c>
       <c r="Z559" t="n">
-        <v>41123.86</v>
+        <v>50888.07</v>
       </c>
       <c r="AA559" t="n">
-        <v>1441719.91</v>
+        <v>1721961.36</v>
       </c>
       <c r="AB559" t="n">
-        <v>7800191.82</v>
+        <v>7529714.58</v>
       </c>
       <c r="AC559" t="n">
-        <v>0.1522256647788577</v>
+        <v>0.1816228472616661</v>
       </c>
     </row>
     <row r="560">
@@ -65928,19 +65928,19 @@
         <v>2086583.52</v>
       </c>
       <c r="Y560" t="n">
-        <v>152799.08</v>
+        <v>172556.71</v>
       </c>
       <c r="Z560" t="n">
-        <v>9641.6</v>
+        <v>10888.3</v>
       </c>
       <c r="AA560" t="n">
-        <v>162440.68</v>
+        <v>183445.01</v>
       </c>
       <c r="AB560" t="n">
-        <v>1933784.44</v>
+        <v>1914026.81</v>
       </c>
       <c r="AC560" t="n">
-        <v>0.07322931410864397</v>
+        <v>0.08269820419170185</v>
       </c>
     </row>
     <row r="561">
@@ -66279,19 +66279,19 @@
         <v>6199729.76</v>
       </c>
       <c r="Y563" t="n">
-        <v>289152.96</v>
+        <v>2369404.54</v>
       </c>
       <c r="Z563" t="n">
         <v>0</v>
       </c>
       <c r="AA563" t="n">
-        <v>289152.96</v>
+        <v>2369404.54</v>
       </c>
       <c r="AB563" t="n">
-        <v>5910576.8</v>
+        <v>3830325.22</v>
       </c>
       <c r="AC563" t="n">
-        <v>0.04663960707861563</v>
+        <v>0.3821786806397832</v>
       </c>
     </row>
     <row r="564">
@@ -67449,19 +67449,19 @@
         <v>14704896.91</v>
       </c>
       <c r="Y573" t="n">
-        <v>1937021.67</v>
+        <v>3334781.36</v>
       </c>
       <c r="Z573" t="n">
-        <v>213905.91</v>
+        <v>357089.45</v>
       </c>
       <c r="AA573" t="n">
-        <v>2150927.58</v>
+        <v>3691870.81</v>
       </c>
       <c r="AB573" t="n">
-        <v>12767875.24</v>
+        <v>11370115.55</v>
       </c>
       <c r="AC573" t="n">
-        <v>0.1317263005552074</v>
+        <v>0.2267803290570637</v>
       </c>
     </row>
     <row r="574">
@@ -67566,19 +67566,19 @@
         <v>14929346.95</v>
       </c>
       <c r="Y574" t="n">
-        <v>833120.1899999999</v>
+        <v>1095630.47</v>
       </c>
       <c r="Z574" t="n">
-        <v>178892.04</v>
+        <v>235452.45</v>
       </c>
       <c r="AA574" t="n">
-        <v>1012012.23</v>
+        <v>1331082.92</v>
       </c>
       <c r="AB574" t="n">
-        <v>14096226.76</v>
+        <v>13833716.48</v>
       </c>
       <c r="AC574" t="n">
-        <v>0.05580419510580133</v>
+        <v>0.07338770233349021</v>
       </c>
     </row>
     <row r="575">
@@ -67800,19 +67800,19 @@
         <v>57467603.75</v>
       </c>
       <c r="Y576" t="n">
-        <v>0</v>
+        <v>1225033.21</v>
       </c>
       <c r="Z576" t="n">
-        <v>0</v>
+        <v>54549.02</v>
       </c>
       <c r="AA576" t="n">
-        <v>0</v>
+        <v>1279582.23</v>
       </c>
       <c r="AB576" t="n">
-        <v>57467603.75</v>
+        <v>56242570.54</v>
       </c>
       <c r="AC576" t="n">
-        <v>0</v>
+        <v>0.02131693563088578</v>
       </c>
     </row>
     <row r="577">
@@ -67917,19 +67917,19 @@
         <v>3187539.16</v>
       </c>
       <c r="Y577" t="n">
-        <v>191808.12</v>
+        <v>333054.32</v>
       </c>
       <c r="Z577" t="n">
-        <v>6118.67</v>
+        <v>10624.42</v>
       </c>
       <c r="AA577" t="n">
-        <v>197926.79</v>
+        <v>343678.74</v>
       </c>
       <c r="AB577" t="n">
-        <v>2995731.04</v>
+        <v>2854484.84</v>
       </c>
       <c r="AC577" t="n">
-        <v>0.06017435719911281</v>
+        <v>0.1044863461379405</v>
       </c>
     </row>
     <row r="578">
@@ -68034,19 +68034,19 @@
         <v>4324285.68</v>
       </c>
       <c r="Y578" t="n">
-        <v>170016.64</v>
+        <v>269098.43</v>
       </c>
       <c r="Z578" t="n">
-        <v>5423.52</v>
+        <v>8584.219999999999</v>
       </c>
       <c r="AA578" t="n">
-        <v>175440.16</v>
+        <v>277682.65</v>
       </c>
       <c r="AB578" t="n">
-        <v>4154269.04</v>
+        <v>4055187.25</v>
       </c>
       <c r="AC578" t="n">
-        <v>0.03931669935368377</v>
+        <v>0.0622295680520349</v>
       </c>
     </row>
     <row r="579">
@@ -68619,19 +68619,19 @@
         <v>3028048.96</v>
       </c>
       <c r="Y583" t="n">
-        <v>317502.27</v>
+        <v>484650.83</v>
       </c>
       <c r="Z583" t="n">
-        <v>10128.32</v>
+        <v>15460.35</v>
       </c>
       <c r="AA583" t="n">
-        <v>327630.59</v>
+        <v>500111.18</v>
       </c>
       <c r="AB583" t="n">
-        <v>2710546.69</v>
+        <v>2543398.13</v>
       </c>
       <c r="AC583" t="n">
-        <v>0.1048537438443532</v>
+        <v>0.1600538288522257</v>
       </c>
     </row>
     <row r="584">
@@ -70233,19 +70233,19 @@
         <v>32998445.8</v>
       </c>
       <c r="Y597" t="n">
-        <v>604883.63</v>
+        <v>1085396</v>
       </c>
       <c r="Z597" t="n">
-        <v>62432.08</v>
+        <v>123110.02</v>
       </c>
       <c r="AA597" t="n">
-        <v>667315.71</v>
+        <v>1208506.02</v>
       </c>
       <c r="AB597" t="n">
-        <v>32393562.17</v>
+        <v>31913049.8</v>
       </c>
       <c r="AC597" t="n">
-        <v>0.01833067028872008</v>
+        <v>0.03289233700818722</v>
       </c>
     </row>
     <row r="598">
@@ -70584,19 +70584,19 @@
         <v>77898894.3</v>
       </c>
       <c r="Y600" t="n">
-        <v>0</v>
+        <v>84001.16</v>
       </c>
       <c r="Z600" t="n">
-        <v>0</v>
+        <v>2679.63</v>
       </c>
       <c r="AA600" t="n">
-        <v>0</v>
+        <v>86680.78999999999</v>
       </c>
       <c r="AB600" t="n">
-        <v>77898894.3</v>
+        <v>77814893.14</v>
       </c>
       <c r="AC600" t="n">
-        <v>0</v>
+        <v>0.001078335716505799</v>
       </c>
     </row>
     <row r="601">
@@ -70818,19 +70818,19 @@
         <v>31699998.96</v>
       </c>
       <c r="Y602" t="n">
-        <v>0</v>
+        <v>29454.44</v>
       </c>
       <c r="Z602" t="n">
-        <v>0</v>
+        <v>939.59</v>
       </c>
       <c r="AA602" t="n">
-        <v>0</v>
+        <v>30394.03</v>
       </c>
       <c r="AB602" t="n">
-        <v>31699998.96</v>
+        <v>31670544.52</v>
       </c>
       <c r="AC602" t="n">
-        <v>0</v>
+        <v>0.0009291621755939642</v>
       </c>
     </row>
     <row r="603">
@@ -70935,19 +70935,19 @@
         <v>35989998.13</v>
       </c>
       <c r="Y603" t="n">
-        <v>0</v>
+        <v>99429.13</v>
       </c>
       <c r="Z603" t="n">
-        <v>0</v>
+        <v>3171.78</v>
       </c>
       <c r="AA603" t="n">
-        <v>0</v>
+        <v>102600.91</v>
       </c>
       <c r="AB603" t="n">
-        <v>35989998.13</v>
+        <v>35890569</v>
       </c>
       <c r="AC603" t="n">
-        <v>0</v>
+        <v>0.002762687834571443</v>
       </c>
     </row>
     <row r="604">
@@ -71052,19 +71052,19 @@
         <v>23434999.8</v>
       </c>
       <c r="Y604" t="n">
-        <v>0</v>
+        <v>49098.49</v>
       </c>
       <c r="Z604" t="n">
-        <v>0</v>
+        <v>1566.24</v>
       </c>
       <c r="AA604" t="n">
-        <v>0</v>
+        <v>50664.73</v>
       </c>
       <c r="AB604" t="n">
-        <v>23434999.8</v>
+        <v>23385901.31</v>
       </c>
       <c r="AC604" t="n">
-        <v>0</v>
+        <v>0.002095092401067569</v>
       </c>
     </row>
     <row r="605">
@@ -71169,19 +71169,19 @@
         <v>32097999.96</v>
       </c>
       <c r="Y605" t="n">
-        <v>0</v>
+        <v>100813.18</v>
       </c>
       <c r="Z605" t="n">
-        <v>0</v>
+        <v>3215.93</v>
       </c>
       <c r="AA605" t="n">
-        <v>0</v>
+        <v>104029.11</v>
       </c>
       <c r="AB605" t="n">
-        <v>32097999.96</v>
+        <v>31997186.78</v>
       </c>
       <c r="AC605" t="n">
-        <v>0</v>
+        <v>0.003140793199751752</v>
       </c>
     </row>
     <row r="606">
@@ -71286,19 +71286,19 @@
         <v>47349998.43</v>
       </c>
       <c r="Y606" t="n">
-        <v>0</v>
+        <v>98942.17999999999</v>
       </c>
       <c r="Z606" t="n">
-        <v>0</v>
+        <v>3156.24</v>
       </c>
       <c r="AA606" t="n">
-        <v>0</v>
+        <v>102098.42</v>
       </c>
       <c r="AB606" t="n">
-        <v>47349998.43</v>
+        <v>47251056.25</v>
       </c>
       <c r="AC606" t="n">
-        <v>0</v>
+        <v>0.002089592043942123</v>
       </c>
     </row>
     <row r="607">
@@ -71520,19 +71520,19 @@
         <v>24832463.21</v>
       </c>
       <c r="Y608" t="n">
-        <v>0</v>
+        <v>706164.05</v>
       </c>
       <c r="Z608" t="n">
-        <v>0</v>
+        <v>69286.32000000001</v>
       </c>
       <c r="AA608" t="n">
-        <v>0</v>
+        <v>775450.37</v>
       </c>
       <c r="AB608" t="n">
-        <v>24832463.21</v>
+        <v>24126299.16</v>
       </c>
       <c r="AC608" t="n">
-        <v>0</v>
+        <v>0.02843713263675062</v>
       </c>
     </row>
     <row r="609">
@@ -71871,19 +71871,19 @@
         <v>29302939.12</v>
       </c>
       <c r="Y611" t="n">
-        <v>0</v>
+        <v>430460.69</v>
       </c>
       <c r="Z611" t="n">
-        <v>0</v>
+        <v>45845.08</v>
       </c>
       <c r="AA611" t="n">
-        <v>0</v>
+        <v>476305.77</v>
       </c>
       <c r="AB611" t="n">
-        <v>29302939.12</v>
+        <v>28872478.43</v>
       </c>
       <c r="AC611" t="n">
-        <v>0</v>
+        <v>0.01469001755206868</v>
       </c>
     </row>
     <row r="612">
@@ -72222,19 +72222,19 @@
         <v>33205062.4</v>
       </c>
       <c r="Y614" t="n">
-        <v>0</v>
+        <v>598527.91</v>
       </c>
       <c r="Z614" t="n">
-        <v>0</v>
+        <v>66572.00999999999</v>
       </c>
       <c r="AA614" t="n">
-        <v>0</v>
+        <v>665099.92</v>
       </c>
       <c r="AB614" t="n">
-        <v>33205062.4</v>
+        <v>32606534.49</v>
       </c>
       <c r="AC614" t="n">
-        <v>0</v>
+        <v>0.01802520057905387</v>
       </c>
     </row>
     <row r="615">
@@ -72362,9 +72362,15 @@
       <c r="D616" s="3" t="n">
         <v>46125</v>
       </c>
+      <c r="E616" s="3" t="n">
+        <v>46160</v>
+      </c>
+      <c r="F616" s="3" t="n">
+        <v>46459</v>
+      </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
@@ -72418,7 +72424,7 @@
         </is>
       </c>
       <c r="R616" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="S616" t="n">
         <v>0</v>
@@ -72427,7 +72433,7 @@
         <v>0</v>
       </c>
       <c r="U616" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="V616" t="n">
         <v>9814000</v>
@@ -73135,19 +73141,19 @@
         <v>36033198.22</v>
       </c>
       <c r="Y622" t="n">
-        <v>0</v>
+        <v>204666.13</v>
       </c>
       <c r="Z622" t="n">
-        <v>0</v>
+        <v>6528.84</v>
       </c>
       <c r="AA622" t="n">
-        <v>0</v>
+        <v>211194.97</v>
       </c>
       <c r="AB622" t="n">
-        <v>36033198.22</v>
+        <v>35828532.09</v>
       </c>
       <c r="AC622" t="n">
-        <v>0</v>
+        <v>0.005679932398740041</v>
       </c>
     </row>
     <row r="623">

--- a/upload/contratos.xlsx
+++ b/upload/contratos.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AC$625</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$AC$627</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC625"/>
+  <dimension ref="A1:AC627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2273,7 +2273,7 @@
         <v>44524</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2337,10 +2337,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="U16" t="n">
-        <v>1686</v>
+        <v>1690</v>
       </c>
       <c r="V16" t="n">
         <v>1452371.99</v>
@@ -12200,7 +12200,7 @@
         <v>44850</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>46167</v>
+        <v>46171</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -12264,10 +12264,10 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="U101" t="n">
-        <v>1318</v>
+        <v>1322</v>
       </c>
       <c r="V101" t="n">
         <v>1365885.84</v>
@@ -15827,7 +15827,7 @@
         <v>45026</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>46170</v>
+        <v>46354</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -15888,13 +15888,13 @@
         <v>610</v>
       </c>
       <c r="S132" t="n">
-        <v>510</v>
+        <v>690</v>
       </c>
       <c r="T132" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="U132" t="n">
-        <v>1145</v>
+        <v>1329</v>
       </c>
       <c r="V132" t="n">
         <v>19915653.29</v>
@@ -24017,7 +24017,7 @@
         <v>44767</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -24081,10 +24081,10 @@
         <v>0</v>
       </c>
       <c r="T202" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="U202" t="n">
-        <v>1499</v>
+        <v>1503</v>
       </c>
       <c r="V202" t="n">
         <v>2519553.4</v>
@@ -28457,7 +28457,7 @@
         <v>44579</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>46382</v>
+        <v>46386</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -28521,10 +28521,10 @@
         <v>180</v>
       </c>
       <c r="T240" t="n">
-        <v>1264</v>
+        <v>1268</v>
       </c>
       <c r="U240" t="n">
-        <v>1804</v>
+        <v>1808</v>
       </c>
       <c r="V240" t="n">
         <v>1175120.88</v>
@@ -37097,7 +37097,7 @@
         <v>45384</v>
       </c>
       <c r="F314" s="3" t="n">
-        <v>46180</v>
+        <v>46184</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
@@ -37161,10 +37161,10 @@
         <v>330</v>
       </c>
       <c r="T314" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="U314" t="n">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="V314" t="n">
         <v>2816620.4</v>
@@ -38042,7 +38042,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>TAMASA ENGENHARIA SA</t>
+          <t>TAMASA ENGENHARIA S/A</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -38580,19 +38580,19 @@
         <v>70591515.05</v>
       </c>
       <c r="Y326" t="n">
-        <v>31711324.65</v>
+        <v>33423438.1</v>
       </c>
       <c r="Z326" t="n">
-        <v>1632147.35</v>
+        <v>1771504.04</v>
       </c>
       <c r="AA326" t="n">
-        <v>33343472</v>
+        <v>35194942.14</v>
       </c>
       <c r="AB326" t="n">
-        <v>38880190.4</v>
+        <v>37168076.95</v>
       </c>
       <c r="AC326" t="n">
-        <v>0.4492228935381095</v>
+        <v>0.4734767071697805</v>
       </c>
     </row>
     <row r="327">
@@ -40373,7 +40373,7 @@
         <v>45110</v>
       </c>
       <c r="F342" s="3" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -40437,10 +40437,10 @@
         <v>398</v>
       </c>
       <c r="T342" t="n">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="U342" t="n">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="V342" t="n">
         <v>3655796.23</v>
@@ -41894,7 +41894,7 @@
         <v>45240</v>
       </c>
       <c r="F355" s="3" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="G355" t="inlineStr">
         <is>
@@ -41958,10 +41958,10 @@
         <v>510</v>
       </c>
       <c r="T355" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="U355" t="n">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="V355" t="n">
         <v>3270756.85</v>
@@ -42479,7 +42479,7 @@
         <v>45236</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>46179</v>
+        <v>46177</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
@@ -42543,10 +42543,10 @@
         <v>480</v>
       </c>
       <c r="T360" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="U360" t="n">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="V360" t="n">
         <v>5042730.21</v>
@@ -43143,19 +43143,19 @@
         <v>6173972.84</v>
       </c>
       <c r="Y365" t="n">
-        <v>2784645.93</v>
+        <v>2868752.43</v>
       </c>
       <c r="Z365" t="n">
-        <v>358574.71</v>
+        <v>371535.51</v>
       </c>
       <c r="AA365" t="n">
-        <v>3143220.64</v>
+        <v>3240287.94</v>
       </c>
       <c r="AB365" t="n">
-        <v>3389326.91</v>
+        <v>3305220.41</v>
       </c>
       <c r="AC365" t="n">
-        <v>0.4510298315468456</v>
+        <v>0.464652583408514</v>
       </c>
     </row>
     <row r="366">
@@ -43649,7 +43649,7 @@
         <v>45236</v>
       </c>
       <c r="F370" s="3" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
@@ -43713,10 +43713,10 @@
         <v>510</v>
       </c>
       <c r="T370" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="U370" t="n">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="V370" t="n">
         <v>7889881.67</v>
@@ -45170,7 +45170,7 @@
         <v>45237</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>46172</v>
+        <v>46176</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -45234,10 +45234,10 @@
         <v>510</v>
       </c>
       <c r="T383" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="U383" t="n">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="V383" t="n">
         <v>4065559.6</v>
@@ -54948,19 +54948,19 @@
         <v>47634588.04</v>
       </c>
       <c r="Y466" t="n">
-        <v>26881215.87</v>
+        <v>31846402.08</v>
       </c>
       <c r="Z466" t="n">
-        <v>1223574.14</v>
+        <v>1523518.61</v>
       </c>
       <c r="AA466" t="n">
-        <v>28104790.01</v>
+        <v>33369920.69</v>
       </c>
       <c r="AB466" t="n">
-        <v>20753372.17</v>
+        <v>15788185.96</v>
       </c>
       <c r="AC466" t="n">
-        <v>0.5643213676462814</v>
+        <v>0.6685562611197089</v>
       </c>
     </row>
     <row r="467">
@@ -56001,19 +56001,19 @@
         <v>50062054.28</v>
       </c>
       <c r="Y475" t="n">
-        <v>26145936.44</v>
+        <v>27333370.56</v>
       </c>
       <c r="Z475" t="n">
-        <v>1281115.95</v>
+        <v>1363482.96</v>
       </c>
       <c r="AA475" t="n">
-        <v>27427052.39</v>
+        <v>28696853.52</v>
       </c>
       <c r="AB475" t="n">
-        <v>23916117.84</v>
+        <v>22728683.72</v>
       </c>
       <c r="AC475" t="n">
-        <v>0.5222705463456263</v>
+        <v>0.5459897911324785</v>
       </c>
     </row>
     <row r="476">
@@ -56150,7 +56150,7 @@
         <v>45573</v>
       </c>
       <c r="F477" s="3" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="G477" t="inlineStr">
         <is>
@@ -56214,10 +56214,10 @@
         <v>0</v>
       </c>
       <c r="T477" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="U477" t="n">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="V477" t="n">
         <v>3876550</v>
@@ -56388,7 +56388,7 @@
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>Andamento</t>
+          <t>Execução concluída</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
@@ -56463,19 +56463,19 @@
         <v>28277547.59</v>
       </c>
       <c r="Y479" t="n">
-        <v>24320830.23</v>
+        <v>25098078.47</v>
       </c>
       <c r="Z479" t="n">
-        <v>970501.73</v>
+        <v>1046950.04</v>
       </c>
       <c r="AA479" t="n">
-        <v>25291331.96</v>
+        <v>26145028.51</v>
       </c>
       <c r="AB479" t="n">
-        <v>3956717.36</v>
+        <v>3179469.12</v>
       </c>
       <c r="AC479" t="n">
-        <v>0.860075653752971</v>
+        <v>0.8875620628033395</v>
       </c>
     </row>
     <row r="480">
@@ -57393,10 +57393,10 @@
         <v>24308955.5</v>
       </c>
       <c r="W487" t="n">
-        <v>0</v>
+        <v>97125</v>
       </c>
       <c r="X487" t="n">
-        <v>24308955.5</v>
+        <v>24406080.5</v>
       </c>
       <c r="Y487" t="n">
         <v>16100052.36</v>
@@ -57408,10 +57408,10 @@
         <v>16320161.6</v>
       </c>
       <c r="AB487" t="n">
-        <v>8208903.14</v>
+        <v>8306028.14</v>
       </c>
       <c r="AC487" t="n">
-        <v>0.6623095081152294</v>
+        <v>0.6596738202186951</v>
       </c>
     </row>
     <row r="488">
@@ -58803,19 +58803,19 @@
         <v>8742912.960000001</v>
       </c>
       <c r="Y499" t="n">
-        <v>0</v>
+        <v>365496.06</v>
       </c>
       <c r="Z499" t="n">
-        <v>0</v>
+        <v>21299.64</v>
       </c>
       <c r="AA499" t="n">
-        <v>0</v>
+        <v>386795.7</v>
       </c>
       <c r="AB499" t="n">
-        <v>8742912.960000001</v>
+        <v>8377416.9</v>
       </c>
       <c r="AC499" t="n">
-        <v>0</v>
+        <v>0.04180483800675971</v>
       </c>
     </row>
     <row r="500">
@@ -60324,19 +60324,19 @@
         <v>31648004.35</v>
       </c>
       <c r="Y512" t="n">
-        <v>27221408.52</v>
+        <v>27438666.59</v>
       </c>
       <c r="Z512" t="n">
-        <v>335837.84</v>
+        <v>343426.89</v>
       </c>
       <c r="AA512" t="n">
-        <v>27557246.36</v>
+        <v>27782093.48</v>
       </c>
       <c r="AB512" t="n">
-        <v>4426595.83</v>
+        <v>4209337.76</v>
       </c>
       <c r="AC512" t="n">
-        <v>0.8601303329889108</v>
+        <v>0.8669951598385697</v>
       </c>
     </row>
     <row r="513">
@@ -60441,19 +60441,19 @@
         <v>7109673.15</v>
       </c>
       <c r="Y513" t="n">
-        <v>134831.17</v>
+        <v>2179552.55</v>
       </c>
       <c r="Z513" t="n">
-        <v>4696.72</v>
+        <v>60976.47</v>
       </c>
       <c r="AA513" t="n">
-        <v>139527.89</v>
+        <v>2240529.02</v>
       </c>
       <c r="AB513" t="n">
-        <v>6974841.98</v>
+        <v>4930120.6</v>
       </c>
       <c r="AC513" t="n">
-        <v>0.01896446814858149</v>
+        <v>0.3065615681643536</v>
       </c>
     </row>
     <row r="514">
@@ -61260,19 +61260,19 @@
         <v>29576179.41</v>
       </c>
       <c r="Y520" t="n">
-        <v>1373835.81</v>
+        <v>2282985.62</v>
       </c>
       <c r="Z520" t="n">
-        <v>73245.00999999999</v>
+        <v>102303.87</v>
       </c>
       <c r="AA520" t="n">
-        <v>1447080.82</v>
+        <v>2385289.49</v>
       </c>
       <c r="AB520" t="n">
-        <v>28202343.6</v>
+        <v>27293193.79</v>
       </c>
       <c r="AC520" t="n">
-        <v>0.04645075318739419</v>
+        <v>0.07719001120300548</v>
       </c>
     </row>
     <row r="521">
@@ -61377,19 +61377,19 @@
         <v>43789355.88</v>
       </c>
       <c r="Y521" t="n">
-        <v>34319619.39</v>
+        <v>36978458.24</v>
       </c>
       <c r="Z521" t="n">
-        <v>452643.71</v>
+        <v>521464.11</v>
       </c>
       <c r="AA521" t="n">
-        <v>34772263.1</v>
+        <v>37499922.35</v>
       </c>
       <c r="AB521" t="n">
-        <v>9469736.49</v>
+        <v>6810897.64</v>
       </c>
       <c r="AC521" t="n">
-        <v>0.7837434166432868</v>
+        <v>0.8444622556526172</v>
       </c>
     </row>
     <row r="522">
@@ -61649,7 +61649,7 @@
         <v>45812</v>
       </c>
       <c r="F524" s="3" t="n">
-        <v>46171</v>
+        <v>46231</v>
       </c>
       <c r="G524" t="inlineStr">
         <is>
@@ -61710,13 +61710,13 @@
         <v>360</v>
       </c>
       <c r="S524" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="T524" t="n">
         <v>0</v>
       </c>
       <c r="U524" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="V524" t="n">
         <v>24981452.5</v>
@@ -62664,19 +62664,19 @@
         <v>9147934.25</v>
       </c>
       <c r="Y532" t="n">
-        <v>1867887.53</v>
+        <v>2228969.36</v>
       </c>
       <c r="Z532" t="n">
-        <v>45682.96</v>
+        <v>58718</v>
       </c>
       <c r="AA532" t="n">
-        <v>1913570.49</v>
+        <v>2287687.36</v>
       </c>
       <c r="AB532" t="n">
-        <v>7280046.72</v>
+        <v>6918964.89</v>
       </c>
       <c r="AC532" t="n">
-        <v>0.2041868119023702</v>
+        <v>0.2436582182474694</v>
       </c>
     </row>
     <row r="533">
@@ -63945,19 +63945,19 @@
         <v>53241874.38</v>
       </c>
       <c r="Y543" t="n">
-        <v>11593843.28</v>
+        <v>13376312.96</v>
       </c>
       <c r="Z543" t="n">
-        <v>129819.98</v>
+        <v>189993.16</v>
       </c>
       <c r="AA543" t="n">
-        <v>11723663.26</v>
+        <v>13566306.12</v>
       </c>
       <c r="AB543" t="n">
-        <v>41648031.1</v>
+        <v>39865561.42</v>
       </c>
       <c r="AC543" t="n">
-        <v>0.2177579849509423</v>
+        <v>0.2512367026098678</v>
       </c>
     </row>
     <row r="544">
@@ -64758,19 +64758,19 @@
         <v>207490000</v>
       </c>
       <c r="Y550" t="n">
-        <v>29767388.25</v>
+        <v>35575898.64</v>
       </c>
       <c r="Z550" t="n">
-        <v>444200.11</v>
+        <v>556313.03</v>
       </c>
       <c r="AA550" t="n">
-        <v>30211588.36</v>
+        <v>36132211.67</v>
       </c>
       <c r="AB550" t="n">
-        <v>177722611.75</v>
+        <v>171914101.36</v>
       </c>
       <c r="AC550" t="n">
-        <v>0.143464206708757</v>
+        <v>0.1714583769820232</v>
       </c>
     </row>
     <row r="551">
@@ -66981,19 +66981,19 @@
         <v>2624909.09</v>
       </c>
       <c r="Y569" t="n">
-        <v>258309.25</v>
+        <v>366122.67</v>
       </c>
       <c r="Z569" t="n">
-        <v>6344.56</v>
+        <v>9783.799999999999</v>
       </c>
       <c r="AA569" t="n">
-        <v>264653.81</v>
+        <v>375906.47</v>
       </c>
       <c r="AB569" t="n">
-        <v>2366599.84</v>
+        <v>2258786.42</v>
       </c>
       <c r="AC569" t="n">
-        <v>0.09840693187587689</v>
+        <v>0.1394801333862576</v>
       </c>
     </row>
     <row r="570">
@@ -67683,19 +67683,19 @@
         <v>18749931.77</v>
       </c>
       <c r="Y575" t="n">
-        <v>2951267.99</v>
+        <v>3731967.69</v>
       </c>
       <c r="Z575" t="n">
-        <v>626313.58</v>
+        <v>792028.13</v>
       </c>
       <c r="AA575" t="n">
-        <v>3577581.57</v>
+        <v>4523995.82</v>
       </c>
       <c r="AB575" t="n">
-        <v>15798663.78</v>
+        <v>15017964.08</v>
       </c>
       <c r="AC575" t="n">
-        <v>0.1574015322403491</v>
+        <v>0.1990390010896557</v>
       </c>
     </row>
     <row r="576">
@@ -70865,12 +70865,12 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>TALENTECH TECNOLOGIA LTDA.</t>
+          <t>CONSORCIO TRILHA REAL DE FISCALIZAÇÃO</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>15773416000110</t>
+          <t>63637380000190</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
@@ -71754,19 +71754,19 @@
         <v>34422078.35</v>
       </c>
       <c r="Y610" t="n">
-        <v>0</v>
+        <v>442302.76</v>
       </c>
       <c r="Z610" t="n">
-        <v>0</v>
+        <v>51291.02</v>
       </c>
       <c r="AA610" t="n">
-        <v>0</v>
+        <v>493593.78</v>
       </c>
       <c r="AB610" t="n">
-        <v>34422078.35</v>
+        <v>33979775.59</v>
       </c>
       <c r="AC610" t="n">
-        <v>0</v>
+        <v>0.01284939147202888</v>
       </c>
     </row>
     <row r="611">
@@ -73159,27 +73159,27 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>PO</t>
+          <t>DM-020/2024-A</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Não Disponível</t>
+          <t>230176205123</t>
         </is>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>SERVIÇOS ESPECIAIS DE APOIO À COORDENAÇÃO E APOIO TÉCNICO NO PLANEJAMENTO, MONITORAMENTO E AVALIAÇÃO DO PORTIFÓLIO DE EMPREENDIMENTOS DO DER-MG</t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 28ª URG</t>
         </is>
       </c>
       <c r="D623" s="3" t="n">
-        <v>45589</v>
+        <v>46141</v>
       </c>
       <c r="E623" s="3" t="n">
-        <v>45628</v>
+        <v>46157</v>
       </c>
       <c r="F623" s="3" t="n">
-        <v>46722</v>
+        <v>46887</v>
       </c>
       <c r="G623" t="inlineStr">
         <is>
@@ -73188,12 +73188,12 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t xml:space="preserve">SYSTRA ENGENHARIA E  CONSULTORIA LTDA </t>
+          <t>CONSÓRCIO IPÊ/ABRIL - CONSERVAÇÃO</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>52635422000307</t>
+          <t>55060514000124</t>
         </is>
       </c>
       <c r="J623" t="inlineStr">
@@ -73203,12 +73203,12 @@
       </c>
       <c r="K623" t="inlineStr">
         <is>
-          <t>ASSESSORIA DE GESTÃO ESTRATÉGICA</t>
+          <t>DIRETORIA DE OPERAÇÕES</t>
         </is>
       </c>
       <c r="L623" t="inlineStr">
         <is>
-          <t>CONCORRÊNCIA ELETRÔNICA</t>
+          <t>RDC</t>
         </is>
       </c>
       <c r="M623" t="inlineStr">
@@ -73218,16 +73218,26 @@
       </c>
       <c r="N623" t="inlineStr">
         <is>
-          <t>Consultoria</t>
+          <t>Manutenção e Conservação</t>
         </is>
       </c>
       <c r="O623" t="inlineStr">
         <is>
-          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - MANUTENÇÃO E CONSERVAÇÃO - 28ª URG</t>
+        </is>
+      </c>
+      <c r="Q623" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Ataléia, Campanário, Caraí, Carlos Chagas, Catuji, Crisólita, Franciscópolis, Frei Gaspar, Itaipé, Itambacuri, Ladainha, Malacacheta, Nanuque, Novo Cruzeiro, Novo Oriente de Minas, Ouro Verde de Minas, Padre Paraíso, Pavão, Poté, Serra dos Aimorés, Teófilo Otoni, Água Boa, Águas Formosas</t>
         </is>
       </c>
       <c r="R623" t="n">
-        <v>1095</v>
+        <v>731</v>
       </c>
       <c r="S623" t="n">
         <v>0</v>
@@ -73236,16 +73246,16 @@
         <v>0</v>
       </c>
       <c r="U623" t="n">
-        <v>1095</v>
+        <v>731</v>
       </c>
       <c r="V623" t="n">
-        <v>5774752.44</v>
+        <v>34497775.12</v>
       </c>
       <c r="W623" t="n">
         <v>0</v>
       </c>
       <c r="X623" t="n">
-        <v>5774752.44</v>
+        <v>34497775.12</v>
       </c>
       <c r="Y623" t="n">
         <v>0</v>
@@ -73257,7 +73267,7 @@
         <v>0</v>
       </c>
       <c r="AB623" t="n">
-        <v>5774752.44</v>
+        <v>34497775.12</v>
       </c>
       <c r="AC623" t="n">
         <v>0</v>
@@ -73266,35 +73276,41 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>DO009482014/2025</t>
+          <t>DM-022/2024-A</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>230190100125</t>
+          <t>230176205123</t>
         </is>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇO DE ENGENHARIA DE TRANSITO - LOTE 01 </t>
+          <t>MANUTENÇÃO E CONSERVAÇÃO - 16ª URG</t>
         </is>
       </c>
       <c r="D624" s="3" t="n">
-        <v>45974</v>
+        <v>46149</v>
+      </c>
+      <c r="E624" s="3" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F624" s="3" t="n">
+        <v>46888</v>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>A Iniciar</t>
+          <t>Andamento</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+          <t>PAVIDEZ ENGENHARIA LTDA</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>16502551000193</t>
+          <t>01744153000106</t>
         </is>
       </c>
       <c r="J624" t="inlineStr">
@@ -73304,12 +73320,12 @@
       </c>
       <c r="K624" t="inlineStr">
         <is>
-          <t>GERÊNCIA DE TRÂFEGO E SEGURANÇA VIÁRIA</t>
+          <t>DIRETORIA DE OPERAÇÕES</t>
         </is>
       </c>
       <c r="L624" t="inlineStr">
         <is>
-          <t>CONCORRÊNCIA ELETRÔNICA</t>
+          <t>RDC</t>
         </is>
       </c>
       <c r="M624" t="inlineStr">
@@ -73317,13 +73333,28 @@
           <t>EMPREITADA POR PREÇO UNITÁRIO</t>
         </is>
       </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>Manutenção e Conservação</t>
+        </is>
+      </c>
       <c r="O624" t="inlineStr">
         <is>
           <t>Natureza continuada e/ou conserva</t>
         </is>
       </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - MANUTENÇÃO E CONSERVAÇÃO - 16ª URG</t>
+        </is>
+      </c>
+      <c r="Q624" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Obra 1 - Aguanil, Bom Sucesso, Campo Belo, Cana Verde, Candeias, Carmópolis de Minas, Carrancas, Cláudio, Cristais, Desterro de Entre Rios, Entre Rios de Minas, Ibituruna, Ijaci, Ingaí, Itaguara, Itapecerica, Itumirim, Itutinga, Lavras, Luminárias, Nazareno, Oliveira, Passa Tempo, Perdões, Piracema, Resende Costa, Ribeirão Vermelho, Santana do Jacaré, Santo Antônio do Amparo, São Francisco de Paula, São Tiago</t>
+        </is>
+      </c>
       <c r="R624" t="n">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="S624" t="n">
         <v>0</v>
@@ -73332,16 +73363,16 @@
         <v>0</v>
       </c>
       <c r="U624" t="n">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="V624" t="n">
-        <v>77898894.3</v>
+        <v>42542200.39</v>
       </c>
       <c r="W624" t="n">
         <v>0</v>
       </c>
       <c r="X624" t="n">
-        <v>77898894.3</v>
+        <v>42542200.39</v>
       </c>
       <c r="Y624" t="n">
         <v>0</v>
@@ -73353,7 +73384,7 @@
         <v>0</v>
       </c>
       <c r="AB624" t="n">
-        <v>77898894.3</v>
+        <v>42542200.39</v>
       </c>
       <c r="AC624" t="n">
         <v>0</v>
@@ -73362,106 +73393,309 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
+          <t>PO</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Não Disponível</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>SERVIÇOS ESPECIAIS DE APOIO À COORDENAÇÃO E APOIO TÉCNICO NO PLANEJAMENTO, MONITORAMENTO E AVALIAÇÃO DO PORTIFÓLIO DE EMPREENDIMENTOS DO DER-MG</t>
+        </is>
+      </c>
+      <c r="D625" s="3" t="n">
+        <v>45589</v>
+      </c>
+      <c r="E625" s="3" t="n">
+        <v>45628</v>
+      </c>
+      <c r="F625" s="3" t="n">
+        <v>46722</v>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>Andamento</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SYSTRA ENGENHARIA E  CONSULTORIA LTDA </t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>52635422000307</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>ASSESSORIA DE GESTÃO ESTRATÉGICA</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>Consultoria</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
+        </is>
+      </c>
+      <c r="R625" t="n">
+        <v>1095</v>
+      </c>
+      <c r="S625" t="n">
+        <v>0</v>
+      </c>
+      <c r="T625" t="n">
+        <v>0</v>
+      </c>
+      <c r="U625" t="n">
+        <v>1095</v>
+      </c>
+      <c r="V625" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="W625" t="n">
+        <v>0</v>
+      </c>
+      <c r="X625" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="Y625" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z625" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA625" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB625" t="n">
+        <v>5774752.44</v>
+      </c>
+      <c r="AC625" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>DO009482014/2025</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>230190100125</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PRESTAÇÃO DE SERVIÇO DE ENGENHARIA DE TRANSITO - LOTE 01 </t>
+        </is>
+      </c>
+      <c r="D626" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>A Iniciar</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>SITRAN SINALIZACAO DE TRANSITO INDUSTRIAL LTDA</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>16502551000193</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>GERÊNCIA DE TRÂFEGO E SEGURANÇA VIÁRIA</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>CONCORRÊNCIA ELETRÔNICA</t>
+        </is>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>EMPREITADA POR PREÇO UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>Natureza continuada e/ou conserva</t>
+        </is>
+      </c>
+      <c r="R626" t="n">
+        <v>0</v>
+      </c>
+      <c r="S626" t="n">
+        <v>0</v>
+      </c>
+      <c r="T626" t="n">
+        <v>0</v>
+      </c>
+      <c r="U626" t="n">
+        <v>0</v>
+      </c>
+      <c r="V626" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="W626" t="n">
+        <v>0</v>
+      </c>
+      <c r="X626" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="Y626" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z626" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA626" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB626" t="n">
+        <v>77898894.3</v>
+      </c>
+      <c r="AC626" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
           <t>DP-001/2023</t>
         </is>
       </c>
-      <c r="B625" t="inlineStr">
+      <c r="B627" t="inlineStr">
         <is>
           <t>2301601000022020</t>
         </is>
       </c>
-      <c r="C625" t="inlineStr">
+      <c r="C627" t="inlineStr">
         <is>
           <t>ELABORAÇÃO DE PROJETO DE ENGENHARIA RODOVIÁRIA DE MELHORAMENTOS, PAVIMENTAÇÃO E OAE - LOTE 2</t>
         </is>
       </c>
-      <c r="D625" s="3" t="n">
+      <c r="D627" s="3" t="n">
         <v>45166</v>
       </c>
-      <c r="G625" t="inlineStr">
+      <c r="G627" t="inlineStr">
         <is>
           <t>A Iniciar</t>
         </is>
       </c>
-      <c r="H625" t="inlineStr">
+      <c r="H627" t="inlineStr">
         <is>
           <t>STRATA ENGENHARIA LTDA</t>
         </is>
       </c>
-      <c r="I625" t="inlineStr">
+      <c r="I627" t="inlineStr">
         <is>
           <t>38743357000132</t>
         </is>
       </c>
-      <c r="J625" t="inlineStr">
+      <c r="J627" t="inlineStr">
         <is>
           <t>DEPARTAMENTO DE ESTRADAS DE RODAGEM DO ESTADO DE MINAS GERAIS</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr">
+      <c r="K627" t="inlineStr">
         <is>
           <t>DIRETORIA DE PROJETOS</t>
         </is>
       </c>
-      <c r="L625" t="inlineStr">
+      <c r="L627" t="inlineStr">
         <is>
           <t>RDC</t>
         </is>
       </c>
-      <c r="M625" t="inlineStr">
+      <c r="M627" t="inlineStr">
         <is>
           <t>EMPREITADA POR PREÇO UNITÁRIO</t>
         </is>
       </c>
-      <c r="N625" t="inlineStr">
+      <c r="N627" t="inlineStr">
         <is>
           <t>Consultoria para Projetos</t>
         </is>
       </c>
-      <c r="O625" t="inlineStr">
+      <c r="O627" t="inlineStr">
         <is>
           <t>Obra Rodoviária - Consultoria , Fiscalização e Projeto de Obras</t>
         </is>
       </c>
-      <c r="R625" t="n">
-        <v>0</v>
-      </c>
-      <c r="S625" t="n">
-        <v>0</v>
-      </c>
-      <c r="T625" t="n">
-        <v>0</v>
-      </c>
-      <c r="U625" t="n">
-        <v>0</v>
-      </c>
-      <c r="V625" t="n">
+      <c r="R627" t="n">
+        <v>0</v>
+      </c>
+      <c r="S627" t="n">
+        <v>0</v>
+      </c>
+      <c r="T627" t="n">
+        <v>0</v>
+      </c>
+      <c r="U627" t="n">
+        <v>0</v>
+      </c>
+      <c r="V627" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="W625" t="n">
-        <v>0</v>
-      </c>
-      <c r="X625" t="n">
+      <c r="W627" t="n">
+        <v>0</v>
+      </c>
+      <c r="X627" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="Y625" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z625" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA625" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB625" t="n">
+      <c r="Y627" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z627" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA627" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB627" t="n">
         <v>3270756.85</v>
       </c>
-      <c r="AC625" t="n">
+      <c r="AC627" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC625"/>
+  <autoFilter ref="A1:AC627"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>